--- a/TORNEO-2026.xlsx
+++ b/TORNEO-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javif\Downloads\MUNDIALITO - 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Mundialito-WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E8F006-8BA4-4F06-9875-FEBD05472E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0235332B-723E-4C48-BB37-A312F32E8E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" activeTab="2" xr2:uid="{5D8C40F9-B180-4AD9-A109-1285E937C9AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" xr2:uid="{5D8C40F9-B180-4AD9-A109-1285E937C9AC}"/>
   </bookViews>
   <sheets>
     <sheet name="ESCUELITAS" sheetId="4" r:id="rId1"/>
@@ -1613,7 +1613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1988,6 +1988,17 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2003,15 +2014,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2024,10 +2026,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2640,11 +2638,11 @@
       </c>
       <c r="D9" s="180">
         <f t="shared" ref="D9:P9" si="0">SUM(D12:D44)</f>
-        <v>1297</v>
+        <v>1382</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="0"/>
-        <v>1287</v>
+        <v>1372</v>
       </c>
       <c r="F9" s="60">
         <f t="shared" si="0"/>
@@ -2701,44 +2699,44 @@
       <c r="D10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="206" t="s">
+      <c r="E10" s="211" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="206"/>
+      <c r="F10" s="211"/>
       <c r="G10" s="37" t="s">
         <v>115</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="I10" s="205" t="s">
+      <c r="I10" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="J10" s="205"/>
-      <c r="K10" s="205" t="s">
+      <c r="J10" s="210"/>
+      <c r="K10" s="210" t="s">
         <v>218</v>
       </c>
-      <c r="L10" s="205"/>
-      <c r="M10" s="205" t="s">
+      <c r="L10" s="210"/>
+      <c r="M10" s="210" t="s">
         <v>128</v>
       </c>
-      <c r="N10" s="205"/>
+      <c r="N10" s="210"/>
       <c r="O10" s="37" t="s">
         <v>112</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="Q10" s="202" t="s">
+      <c r="Q10" s="207" t="s">
         <v>15</v>
       </c>
-      <c r="R10" s="203"/>
-      <c r="S10" s="203"/>
-      <c r="T10" s="203"/>
-      <c r="U10" s="203"/>
-      <c r="V10" s="203"/>
-      <c r="W10" s="203"/>
-      <c r="X10" s="204"/>
+      <c r="R10" s="208"/>
+      <c r="S10" s="208"/>
+      <c r="T10" s="208"/>
+      <c r="U10" s="208"/>
+      <c r="V10" s="208"/>
+      <c r="W10" s="208"/>
+      <c r="X10" s="209"/>
       <c r="Z10" s="19" t="s">
         <v>16</v>
       </c>
@@ -2832,9 +2830,11 @@
       </c>
       <c r="D12" s="45">
         <f>+E12</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="63"/>
+        <v>85</v>
+      </c>
+      <c r="E12" s="63">
+        <v>85</v>
+      </c>
       <c r="F12" s="65"/>
       <c r="G12" s="45"/>
       <c r="H12" s="89"/>
@@ -5105,20 +5105,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:17">
-      <c r="N1" s="211">
+      <c r="N1" s="213">
         <f>+N2-O2</f>
         <v>12620000</v>
       </c>
-      <c r="O1" s="210"/>
+      <c r="O1" s="212"/>
     </row>
     <row r="2" spans="3:17">
       <c r="N2" s="4">
         <f>+N4+N9+N15+N29+N35</f>
-        <v>146398160</v>
+        <v>146795960</v>
       </c>
       <c r="O2" s="4">
         <f>+O4+O9+O15+O29+O35</f>
-        <v>133778160</v>
+        <v>134175960</v>
       </c>
     </row>
     <row r="3" spans="3:17">
@@ -5339,11 +5339,11 @@
       </c>
       <c r="O15" s="193">
         <f>SUM(O16:O23)</f>
-        <v>49223160</v>
+        <v>49620960</v>
       </c>
       <c r="P15" s="187">
         <f>+O15-N15</f>
-        <v>49223160</v>
+        <v>49620960</v>
       </c>
     </row>
     <row r="16" spans="3:17">
@@ -5431,7 +5431,7 @@
       <c r="F20" s="160"/>
       <c r="G20" s="161">
         <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="L20" t="s">
         <v>45</v>
@@ -5439,7 +5439,7 @@
       <c r="N20" s="160"/>
       <c r="O20" s="161">
         <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
     </row>
     <row r="21" spans="3:17">
@@ -5651,7 +5651,7 @@
       <c r="M35" s="188"/>
       <c r="N35" s="194">
         <f>SUM(N36:N43)</f>
-        <v>71377160</v>
+        <v>71774960</v>
       </c>
       <c r="O35" s="195">
         <f>SUM(O36:O43)</f>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="P35" s="198">
         <f>+N35-O35</f>
-        <v>71377160</v>
+        <v>71774960</v>
       </c>
     </row>
     <row r="36" spans="3:16">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="F37" s="160">
         <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="G37" s="161"/>
       <c r="L37" t="s">
@@ -5737,18 +5737,18 @@
       </c>
       <c r="N40" s="160">
         <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="O40" s="161"/>
     </row>
     <row r="41" spans="3:16">
       <c r="F41" s="181">
         <f>SUM(F5:F38)</f>
-        <v>124063160</v>
+        <v>124460960</v>
       </c>
       <c r="G41" s="182">
         <f>SUM(G5:G38)</f>
-        <v>125404160</v>
+        <v>125801960</v>
       </c>
       <c r="L41" t="s">
         <v>235</v>
@@ -5771,11 +5771,11 @@
       <c r="O42" s="161"/>
     </row>
     <row r="43" spans="3:16">
-      <c r="F43" s="212">
+      <c r="F43" s="214">
         <f>+F41-G41</f>
         <v>-1341000</v>
       </c>
-      <c r="G43" s="213"/>
+      <c r="G43" s="215"/>
       <c r="L43" t="s">
         <v>236</v>
       </c>
@@ -7911,7 +7911,7 @@
       <c r="D105" s="2"/>
       <c r="E105" s="101">
         <f>SUM(E107:E111)</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="F105" s="101">
         <f t="shared" ref="F105:G105" si="23">SUM(F107:F111)</f>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="G105" s="101">
         <f t="shared" si="23"/>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="I105"/>
       <c r="J105"/>
@@ -7965,16 +7965,16 @@
       </c>
       <c r="D107" s="2">
         <f>+ESCUELITAS!E9</f>
-        <v>1287</v>
+        <v>1372</v>
       </c>
       <c r="E107" s="8">
         <f>+D107*B107</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="8">
         <f>+E107-F107</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
       <c r="H107" s="69"/>
       <c r="I107" s="70"/>
@@ -8491,13 +8491,13 @@
     <row r="1" spans="2:10" ht="42" customHeight="1">
       <c r="B1" s="143"/>
       <c r="C1" s="15"/>
-      <c r="D1" s="207" t="s">
+      <c r="D1" s="204" t="s">
         <v>198</v>
       </c>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
       <c r="I1" s="15"/>
       <c r="J1" s="16"/>
     </row>
@@ -8526,13 +8526,13 @@
     <row r="4" spans="2:10" ht="28.2" customHeight="1">
       <c r="B4" s="82"/>
       <c r="C4" s="81"/>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="205" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
       <c r="I4" s="70"/>
       <c r="J4" s="11"/>
     </row>
@@ -8982,13 +8982,13 @@
     <row r="42" spans="2:10" ht="28.2">
       <c r="B42" s="82"/>
       <c r="C42" s="81"/>
-      <c r="D42" s="208" t="s">
+      <c r="D42" s="205" t="s">
         <v>190</v>
       </c>
-      <c r="E42" s="208"/>
-      <c r="F42" s="208"/>
-      <c r="G42" s="208"/>
-      <c r="H42" s="208"/>
+      <c r="E42" s="205"/>
+      <c r="F42" s="205"/>
+      <c r="G42" s="205"/>
+      <c r="H42" s="205"/>
       <c r="I42" s="70"/>
       <c r="J42" s="11"/>
     </row>
@@ -9446,13 +9446,13 @@
     <row r="80" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1">
       <c r="B80" s="138"/>
       <c r="C80" s="95"/>
-      <c r="D80" s="208" t="s">
+      <c r="D80" s="205" t="s">
         <v>194</v>
       </c>
-      <c r="E80" s="208"/>
-      <c r="F80" s="208"/>
-      <c r="G80" s="208"/>
-      <c r="H80" s="208"/>
+      <c r="E80" s="205"/>
+      <c r="F80" s="205"/>
+      <c r="G80" s="205"/>
+      <c r="H80" s="205"/>
       <c r="I80" s="97"/>
       <c r="J80" s="139"/>
     </row>
@@ -9580,13 +9580,13 @@
     <row r="92" spans="2:10">
       <c r="B92" s="82"/>
       <c r="C92" s="81"/>
-      <c r="D92" s="209" t="s">
+      <c r="D92" s="206" t="s">
         <v>196</v>
       </c>
-      <c r="E92" s="209"/>
-      <c r="F92" s="209"/>
-      <c r="G92" s="209"/>
-      <c r="H92" s="209"/>
+      <c r="E92" s="206"/>
+      <c r="F92" s="206"/>
+      <c r="G92" s="206"/>
+      <c r="H92" s="206"/>
       <c r="I92" s="70"/>
       <c r="J92" s="11"/>
     </row>
@@ -9671,28 +9671,28 @@
       <c r="G114" t="s">
         <v>222</v>
       </c>
-      <c r="L114" s="214" t="s">
+      <c r="L114" s="202" t="s">
         <v>252</v>
       </c>
-      <c r="M114" s="214" t="s">
+      <c r="M114" s="202" t="s">
         <v>253</v>
       </c>
-      <c r="N114" s="216" t="s">
+      <c r="N114" t="s">
         <v>254</v>
       </c>
-      <c r="O114" s="216" t="s">
+      <c r="O114" t="s">
         <v>253</v>
       </c>
-      <c r="P114" s="214" t="s">
+      <c r="P114" s="202" t="s">
         <v>255</v>
       </c>
-      <c r="Q114" s="214" t="s">
+      <c r="Q114" s="202" t="s">
         <v>253</v>
       </c>
-      <c r="R114" s="216" t="s">
+      <c r="R114" t="s">
         <v>256</v>
       </c>
-      <c r="S114" s="216" t="s">
+      <c r="S114" t="s">
         <v>253</v>
       </c>
     </row>
@@ -9704,14 +9704,10 @@
         <f>+E116-H116</f>
         <v>4200000</v>
       </c>
-      <c r="L115" s="214"/>
-      <c r="M115" s="214"/>
-      <c r="N115" s="216"/>
-      <c r="O115" s="216"/>
-      <c r="P115" s="214"/>
-      <c r="Q115" s="214"/>
-      <c r="R115" s="216"/>
-      <c r="S115" s="216"/>
+      <c r="L115" s="202"/>
+      <c r="M115" s="202"/>
+      <c r="P115" s="202"/>
+      <c r="Q115" s="202"/>
     </row>
     <row r="116" spans="4:19">
       <c r="D116" t="s">
@@ -9733,36 +9729,30 @@
         <f>+E116-H49</f>
         <v>12310000</v>
       </c>
-      <c r="L116" s="215">
+      <c r="L116" s="203">
         <f>+E82+E83</f>
         <v>4950000</v>
       </c>
-      <c r="M116" s="214"/>
-      <c r="N116" s="217">
+      <c r="M116" s="202"/>
+      <c r="N116" s="8">
         <f>+G82+G83</f>
         <v>0</v>
       </c>
-      <c r="O116" s="216"/>
-      <c r="P116" s="215">
+      <c r="P116" s="203">
         <f>+I82+I83</f>
         <v>0</v>
       </c>
-      <c r="Q116" s="214"/>
-      <c r="R116" s="217">
+      <c r="Q116" s="202"/>
+      <c r="R116" s="8">
         <f>+K82+K83</f>
         <v>0</v>
       </c>
-      <c r="S116" s="216"/>
     </row>
     <row r="117" spans="4:19">
-      <c r="L117" s="214"/>
-      <c r="M117" s="214"/>
-      <c r="N117" s="216"/>
-      <c r="O117" s="216"/>
-      <c r="P117" s="214"/>
-      <c r="Q117" s="214"/>
-      <c r="R117" s="216"/>
-      <c r="S117" s="216"/>
+      <c r="L117" s="202"/>
+      <c r="M117" s="202"/>
+      <c r="P117" s="202"/>
+      <c r="Q117" s="202"/>
     </row>
     <row r="118" spans="4:19">
       <c r="D118" t="s">
@@ -9779,24 +9769,16 @@
         <f>+E118-F118</f>
         <v>1651000</v>
       </c>
-      <c r="L118" s="214"/>
-      <c r="M118" s="214"/>
-      <c r="N118" s="216"/>
-      <c r="O118" s="216"/>
-      <c r="P118" s="214"/>
-      <c r="Q118" s="214"/>
-      <c r="R118" s="216"/>
-      <c r="S118" s="216"/>
+      <c r="L118" s="202"/>
+      <c r="M118" s="202"/>
+      <c r="P118" s="202"/>
+      <c r="Q118" s="202"/>
     </row>
     <row r="119" spans="4:19">
-      <c r="L119" s="214"/>
-      <c r="M119" s="214"/>
-      <c r="N119" s="216"/>
-      <c r="O119" s="216"/>
-      <c r="P119" s="214"/>
-      <c r="Q119" s="214"/>
-      <c r="R119" s="216"/>
-      <c r="S119" s="216"/>
+      <c r="L119" s="202"/>
+      <c r="M119" s="202"/>
+      <c r="P119" s="202"/>
+      <c r="Q119" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9873,7 +9855,7 @@
       </c>
       <c r="G12" s="56">
         <f>SUM(E14:E17)</f>
-        <v>45023160</v>
+        <v>45420960</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -9905,7 +9887,7 @@
       </c>
       <c r="E17" s="8">
         <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -9951,7 +9933,7 @@
       </c>
       <c r="G26" s="56">
         <f>SUM(D27:D32)</f>
-        <v>67177160</v>
+        <v>67574960</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -10004,7 +9986,7 @@
       </c>
       <c r="D32" s="8">
         <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6023160</v>
+        <v>6420960</v>
       </c>
     </row>
   </sheetData>
@@ -10874,11 +10856,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="212" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="210"/>
-      <c r="C2" s="210"/>
+      <c r="B2" s="212"/>
+      <c r="C2" s="212"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">

--- a/TORNEO-2026.xlsx
+++ b/TORNEO-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Mundialito-WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0235332B-723E-4C48-BB37-A312F32E8E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1122D02-1E8E-424B-B0F3-C3281647769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" xr2:uid="{5D8C40F9-B180-4AD9-A109-1285E937C9AC}"/>
   </bookViews>
@@ -1990,15 +1990,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2012,6 +2003,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2638,11 +2638,11 @@
       </c>
       <c r="D9" s="180">
         <f t="shared" ref="D9:P9" si="0">SUM(D12:D44)</f>
-        <v>1382</v>
+        <v>1297</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="0"/>
-        <v>1372</v>
+        <v>1287</v>
       </c>
       <c r="F9" s="60">
         <f t="shared" si="0"/>
@@ -2699,44 +2699,44 @@
       <c r="D10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="211" t="s">
+      <c r="E10" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="211"/>
+      <c r="F10" s="208"/>
       <c r="G10" s="37" t="s">
         <v>115</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="I10" s="210" t="s">
+      <c r="I10" s="207" t="s">
         <v>219</v>
       </c>
-      <c r="J10" s="210"/>
-      <c r="K10" s="210" t="s">
+      <c r="J10" s="207"/>
+      <c r="K10" s="207" t="s">
         <v>218</v>
       </c>
-      <c r="L10" s="210"/>
-      <c r="M10" s="210" t="s">
+      <c r="L10" s="207"/>
+      <c r="M10" s="207" t="s">
         <v>128</v>
       </c>
-      <c r="N10" s="210"/>
+      <c r="N10" s="207"/>
       <c r="O10" s="37" t="s">
         <v>112</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="Q10" s="207" t="s">
+      <c r="Q10" s="204" t="s">
         <v>15</v>
       </c>
-      <c r="R10" s="208"/>
-      <c r="S10" s="208"/>
-      <c r="T10" s="208"/>
-      <c r="U10" s="208"/>
-      <c r="V10" s="208"/>
-      <c r="W10" s="208"/>
-      <c r="X10" s="209"/>
+      <c r="R10" s="205"/>
+      <c r="S10" s="205"/>
+      <c r="T10" s="205"/>
+      <c r="U10" s="205"/>
+      <c r="V10" s="205"/>
+      <c r="W10" s="205"/>
+      <c r="X10" s="206"/>
       <c r="Z10" s="19" t="s">
         <v>16</v>
       </c>
@@ -2830,10 +2830,10 @@
       </c>
       <c r="D12" s="45">
         <f>+E12</f>
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E12" s="63">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F12" s="65"/>
       <c r="G12" s="45"/>
@@ -2884,7 +2884,9 @@
         <f>+E13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="63"/>
+      <c r="E13" s="63">
+        <v>0</v>
+      </c>
       <c r="F13" s="65"/>
       <c r="G13" s="45"/>
       <c r="H13" s="89"/>
@@ -5114,11 +5116,11 @@
     <row r="2" spans="3:17">
       <c r="N2" s="4">
         <f>+N4+N9+N15+N29+N35</f>
-        <v>146795960</v>
+        <v>146398160</v>
       </c>
       <c r="O2" s="4">
         <f>+O4+O9+O15+O29+O35</f>
-        <v>134175960</v>
+        <v>133778160</v>
       </c>
     </row>
     <row r="3" spans="3:17">
@@ -5339,11 +5341,11 @@
       </c>
       <c r="O15" s="193">
         <f>SUM(O16:O23)</f>
-        <v>49620960</v>
+        <v>49223160</v>
       </c>
       <c r="P15" s="187">
         <f>+O15-N15</f>
-        <v>49620960</v>
+        <v>49223160</v>
       </c>
     </row>
     <row r="16" spans="3:17">
@@ -5431,7 +5433,7 @@
       <c r="F20" s="160"/>
       <c r="G20" s="161">
         <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="L20" t="s">
         <v>45</v>
@@ -5439,7 +5441,7 @@
       <c r="N20" s="160"/>
       <c r="O20" s="161">
         <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
     </row>
     <row r="21" spans="3:17">
@@ -5651,7 +5653,7 @@
       <c r="M35" s="188"/>
       <c r="N35" s="194">
         <f>SUM(N36:N43)</f>
-        <v>71774960</v>
+        <v>71377160</v>
       </c>
       <c r="O35" s="195">
         <f>SUM(O36:O43)</f>
@@ -5659,7 +5661,7 @@
       </c>
       <c r="P35" s="198">
         <f>+N35-O35</f>
-        <v>71774960</v>
+        <v>71377160</v>
       </c>
     </row>
     <row r="36" spans="3:16">
@@ -5687,7 +5689,7 @@
       </c>
       <c r="F37" s="160">
         <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="G37" s="161"/>
       <c r="L37" t="s">
@@ -5737,18 +5739,18 @@
       </c>
       <c r="N40" s="160">
         <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="O40" s="161"/>
     </row>
     <row r="41" spans="3:16">
       <c r="F41" s="181">
         <f>SUM(F5:F38)</f>
-        <v>124460960</v>
+        <v>124063160</v>
       </c>
       <c r="G41" s="182">
         <f>SUM(G5:G38)</f>
-        <v>125801960</v>
+        <v>125404160</v>
       </c>
       <c r="L41" t="s">
         <v>235</v>
@@ -7911,7 +7913,7 @@
       <c r="D105" s="2"/>
       <c r="E105" s="101">
         <f>SUM(E107:E111)</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="F105" s="101">
         <f t="shared" ref="F105:G105" si="23">SUM(F107:F111)</f>
@@ -7919,7 +7921,7 @@
       </c>
       <c r="G105" s="101">
         <f t="shared" si="23"/>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="I105"/>
       <c r="J105"/>
@@ -7965,16 +7967,16 @@
       </c>
       <c r="D107" s="2">
         <f>+ESCUELITAS!E9</f>
-        <v>1372</v>
+        <v>1287</v>
       </c>
       <c r="E107" s="8">
         <f>+D107*B107</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="8">
         <f>+E107-F107</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
       <c r="H107" s="69"/>
       <c r="I107" s="70"/>
@@ -8491,13 +8493,13 @@
     <row r="1" spans="2:10" ht="42" customHeight="1">
       <c r="B1" s="143"/>
       <c r="C1" s="15"/>
-      <c r="D1" s="204" t="s">
+      <c r="D1" s="209" t="s">
         <v>198</v>
       </c>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
+      <c r="E1" s="209"/>
+      <c r="F1" s="209"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="209"/>
       <c r="I1" s="15"/>
       <c r="J1" s="16"/>
     </row>
@@ -8526,13 +8528,13 @@
     <row r="4" spans="2:10" ht="28.2" customHeight="1">
       <c r="B4" s="82"/>
       <c r="C4" s="81"/>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="210" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="205"/>
+      <c r="E4" s="210"/>
+      <c r="F4" s="210"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="210"/>
       <c r="I4" s="70"/>
       <c r="J4" s="11"/>
     </row>
@@ -8982,13 +8984,13 @@
     <row r="42" spans="2:10" ht="28.2">
       <c r="B42" s="82"/>
       <c r="C42" s="81"/>
-      <c r="D42" s="205" t="s">
+      <c r="D42" s="210" t="s">
         <v>190</v>
       </c>
-      <c r="E42" s="205"/>
-      <c r="F42" s="205"/>
-      <c r="G42" s="205"/>
-      <c r="H42" s="205"/>
+      <c r="E42" s="210"/>
+      <c r="F42" s="210"/>
+      <c r="G42" s="210"/>
+      <c r="H42" s="210"/>
       <c r="I42" s="70"/>
       <c r="J42" s="11"/>
     </row>
@@ -9446,13 +9448,13 @@
     <row r="80" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1">
       <c r="B80" s="138"/>
       <c r="C80" s="95"/>
-      <c r="D80" s="205" t="s">
+      <c r="D80" s="210" t="s">
         <v>194</v>
       </c>
-      <c r="E80" s="205"/>
-      <c r="F80" s="205"/>
-      <c r="G80" s="205"/>
-      <c r="H80" s="205"/>
+      <c r="E80" s="210"/>
+      <c r="F80" s="210"/>
+      <c r="G80" s="210"/>
+      <c r="H80" s="210"/>
       <c r="I80" s="97"/>
       <c r="J80" s="139"/>
     </row>
@@ -9580,13 +9582,13 @@
     <row r="92" spans="2:10">
       <c r="B92" s="82"/>
       <c r="C92" s="81"/>
-      <c r="D92" s="206" t="s">
+      <c r="D92" s="211" t="s">
         <v>196</v>
       </c>
-      <c r="E92" s="206"/>
-      <c r="F92" s="206"/>
-      <c r="G92" s="206"/>
-      <c r="H92" s="206"/>
+      <c r="E92" s="211"/>
+      <c r="F92" s="211"/>
+      <c r="G92" s="211"/>
+      <c r="H92" s="211"/>
       <c r="I92" s="70"/>
       <c r="J92" s="11"/>
     </row>
@@ -9855,7 +9857,7 @@
       </c>
       <c r="G12" s="56">
         <f>SUM(E14:E17)</f>
-        <v>45420960</v>
+        <v>45023160</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -9887,7 +9889,7 @@
       </c>
       <c r="E17" s="8">
         <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -9933,7 +9935,7 @@
       </c>
       <c r="G26" s="56">
         <f>SUM(D27:D32)</f>
-        <v>67574960</v>
+        <v>67177160</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -9986,7 +9988,7 @@
       </c>
       <c r="D32" s="8">
         <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6420960</v>
+        <v>6023160</v>
       </c>
     </row>
   </sheetData>

--- a/TORNEO-2026.xlsx
+++ b/TORNEO-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Mundialito-WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1122D02-1E8E-424B-B0F3-C3281647769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A20EBC3-6521-4FB9-9813-487F7EEA6C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" xr2:uid="{5D8C40F9-B180-4AD9-A109-1285E937C9AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="831" activeTab="1" xr2:uid="{5D8C40F9-B180-4AD9-A109-1285E937C9AC}"/>
   </bookViews>
   <sheets>
     <sheet name="ESCUELITAS" sheetId="4" r:id="rId1"/>
@@ -58,7 +58,7 @@
     <author>tc={CBC74050-1956-4076-AE2E-7C6922D7268C}</author>
   </authors>
   <commentList>
-    <comment ref="Q28" authorId="0" shapeId="0" xr:uid="{53E0BCEE-A55F-448D-8020-2154FD7FDF86}">
+    <comment ref="Q29" authorId="0" shapeId="0" xr:uid="{53E0BCEE-A55F-448D-8020-2154FD7FDF86}">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R28" authorId="0" shapeId="0" xr:uid="{F34E7549-8448-405C-8FBE-34FDF3FB6A3D}">
+    <comment ref="R29" authorId="0" shapeId="0" xr:uid="{F34E7549-8448-405C-8FBE-34FDF3FB6A3D}">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q39" authorId="1" shapeId="0" xr:uid="{CBC74050-1956-4076-AE2E-7C6922D7268C}">
+    <comment ref="Q40" authorId="1" shapeId="0" xr:uid="{CBC74050-1956-4076-AE2E-7C6922D7268C}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="260">
   <si>
     <t>Escuela de Futbol</t>
   </si>
@@ -889,6 +889,15 @@
   </si>
   <si>
     <t>PAGO 4</t>
+  </si>
+  <si>
+    <t>BANFIELD</t>
+  </si>
+  <si>
+    <t>TICKETS P/EMNTRADAS</t>
+  </si>
+  <si>
+    <t>FLETE CARTEL</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2026,6 +2035,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2493,7 +2504,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Q39" dT="2026-08-07T11:22:23.94" personId="{CFD82165-E186-4AD7-98A8-6C1DEE06CBF1}" id="{CBC74050-1956-4076-AE2E-7C6922D7268C}">
+  <threadedComment ref="Q40" dT="2026-08-07T11:22:23.94" personId="{CFD82165-E186-4AD7-98A8-6C1DEE06CBF1}" id="{CBC74050-1956-4076-AE2E-7C6922D7268C}">
     <text>1.560.000 eft + 2.000.000 tra</text>
   </threadedComment>
 </ThreadedComments>
@@ -2501,7 +2512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5793D5D-C0F4-4F64-9D5A-A8B352024822}">
-  <dimension ref="A1:AB58"/>
+  <dimension ref="A1:AB59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2563,7 +2574,7 @@
       </c>
       <c r="F5" s="162">
         <f>+F9</f>
-        <v>77220000</v>
+        <v>77400000</v>
       </c>
       <c r="H5" s="163">
         <f>-H9</f>
@@ -2586,7 +2597,7 @@
       <c r="L7" s="163"/>
       <c r="M7" s="4"/>
       <c r="N7" s="163">
-        <f>SUM(N12:N44)</f>
+        <f>SUM(N12:N45)</f>
         <v>0</v>
       </c>
       <c r="O7" s="4"/>
@@ -2637,16 +2648,16 @@
         <v>143</v>
       </c>
       <c r="D9" s="180">
-        <f t="shared" ref="D9:P9" si="0">SUM(D12:D44)</f>
-        <v>1297</v>
+        <f t="shared" ref="D9:P9" si="0">SUM(D12:D45)</f>
+        <v>1300</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="0"/>
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="F9" s="60">
         <f t="shared" si="0"/>
-        <v>77220000</v>
+        <v>77400000</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
@@ -2682,11 +2693,11 @@
       </c>
       <c r="O9" s="28">
         <f t="shared" si="0"/>
-        <v>89090000</v>
+        <v>89270000</v>
       </c>
       <c r="P9" s="28">
         <f t="shared" si="0"/>
-        <v>39330000</v>
+        <v>31750000</v>
       </c>
       <c r="Q9" s="28"/>
     </row>
@@ -2858,20 +2869,21 @@
       <c r="W12" s="155"/>
       <c r="X12" s="30"/>
       <c r="Z12" s="8">
-        <f>+SUMIFS(Q12:Q44,R12:R44,Z10)+SUMIFS(S12:S44,T12:T44,Z10)+SUMIFS(U12:U44,V12:V44,Z10)+SUMIFS(W12:W44,X12:X44,Z10)</f>
-        <v>17220000</v>
+        <f>+SUMIFS(Q12:Q45,R12:R45,Z10)+SUMIFS(S12:S45,T12:T45,Z10)+SUMIFS(U12:U45,V12:V45,Z10)+SUMIFS(W12:W45,X12:X45,Z10)</f>
+        <v>21220000</v>
       </c>
       <c r="AA12" s="8">
-        <f>+SUMIFS(Q12:Q44,R12:R44,AA10)+SUMIFS(S12:S44,T12:T44,AA10)+SUMIFS(U12:U44,V12:V44,AA10)+SUMIFS(W12:W44,X12:X44,AA10)</f>
-        <v>11810000</v>
+        <f>+SUMIFS(Q12:Q45,R12:R45,AA10)+SUMIFS(S12:S45,T12:T45,AA10)+SUMIFS(U12:U45,V12:V45,AA10)+SUMIFS(W12:W45,X12:X45,AA10)</f>
+        <v>13810000</v>
       </c>
       <c r="AB12" s="8">
-        <f>+SUMIFS(Q12:Q44,R12:R44,AB10)+SUMIFS(S12:S44,T12:T44,AB10)+SUMIFS(U12:U44,V12:V44,AB10)+SUMIFS(W12:W44,X12:X44,AB10)</f>
-        <v>3320000</v>
+        <f>+SUMIFS(Q12:Q45,R12:R45,AB10)+SUMIFS(S12:S45,T12:T45,AB10)+SUMIFS(U12:U45,V12:V45,AB10)+SUMIFS(W12:W45,X12:X45,AB10)</f>
+        <v>5080000</v>
       </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="43">
+        <f>+A12+1</f>
         <v>2</v>
       </c>
       <c r="B13" s="44">
@@ -2915,6 +2927,7 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="43">
+        <f t="shared" ref="A14:A45" si="1">+A13+1</f>
         <v>3</v>
       </c>
       <c r="B14" s="48">
@@ -2956,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="178">
-        <f t="shared" ref="O14:O34" si="1">+F14+J14+L14+N14-H14</f>
+        <f t="shared" ref="O14:O35" si="2">+F14+J14+L14+N14-H14</f>
         <v>5100000</v>
       </c>
       <c r="P14" s="168">
@@ -2985,6 +2998,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="43">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B15" s="48">
@@ -2994,7 +3008,7 @@
         <v>65</v>
       </c>
       <c r="D15" s="49">
-        <f t="shared" ref="D15:D44" si="2">+E15+G15</f>
+        <f t="shared" ref="D15:D45" si="3">+E15+G15</f>
         <v>47</v>
       </c>
       <c r="E15" s="64">
@@ -3024,11 +3038,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2820000</v>
       </c>
       <c r="P15" s="168">
-        <f t="shared" ref="P15:P44" si="3">+O15-(Q15+S15+W15+U15)</f>
+        <f t="shared" ref="P15:P45" si="4">+O15-(Q15+S15+W15+U15)</f>
         <v>-60000</v>
       </c>
       <c r="Q15" s="52">
@@ -3050,6 +3064,7 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="43">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B16" s="48">
@@ -3059,7 +3074,7 @@
         <v>77</v>
       </c>
       <c r="D16" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="E16" s="64">
@@ -3089,11 +3104,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2640000</v>
       </c>
       <c r="P16" s="168">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2640000</v>
       </c>
       <c r="Q16" s="52">
@@ -3114,6 +3129,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="43">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B17" s="48">
@@ -3123,7 +3139,7 @@
         <v>61</v>
       </c>
       <c r="D17" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="E17" s="64">
@@ -3155,11 +3171,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3600000</v>
       </c>
       <c r="P17" s="168">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q17" s="52">
@@ -3182,6 +3198,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="43">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B18" s="48">
@@ -3191,7 +3208,7 @@
         <v>70</v>
       </c>
       <c r="D18" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
       <c r="E18" s="64">
@@ -3223,11 +3240,11 @@
         <v>0</v>
       </c>
       <c r="O18" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7020000</v>
       </c>
       <c r="P18" s="168">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3020000</v>
       </c>
       <c r="Q18" s="52">
@@ -3250,16 +3267,17 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="43">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B19" s="48">
         <v>2</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="D19" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D19" si="5">+E19+G19</f>
         <v>0</v>
       </c>
       <c r="E19" s="64"/>
@@ -3287,26 +3305,23 @@
         <v>0</v>
       </c>
       <c r="O19" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="O19" si="6">+F19+J19+L19+N19-H19</f>
         <v>0</v>
       </c>
       <c r="P19" s="168">
-        <f t="shared" si="3"/>
-        <v>-1740000</v>
+        <f t="shared" ref="P19" si="7">+O19-(Q19+S19+W19+U19)</f>
+        <v>-2000000</v>
       </c>
       <c r="Q19" s="52">
-        <f>260000+630000+470000</f>
-        <v>1360000</v>
+        <v>2000000</v>
       </c>
       <c r="R19" s="44" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="S19" s="47">
-        <v>380000</v>
-      </c>
-      <c r="T19" s="48" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T19" s="48"/>
       <c r="U19" s="47"/>
       <c r="V19" s="153"/>
       <c r="W19" s="156">
@@ -3317,24 +3332,23 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="43">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B20" s="48">
         <v>2</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D20" s="49">
-        <f t="shared" si="2"/>
-        <v>141</v>
-      </c>
-      <c r="E20" s="64">
-        <v>141</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="64"/>
       <c r="F20" s="66">
         <f>+E20*Precios!$C$5</f>
-        <v>8460000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="49"/>
       <c r="H20" s="90"/>
@@ -3356,49 +3370,55 @@
         <v>0</v>
       </c>
       <c r="O20" s="178">
-        <f t="shared" si="1"/>
-        <v>8460000</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="P20" s="168">
-        <f t="shared" si="3"/>
-        <v>8460000</v>
+        <f t="shared" si="4"/>
+        <v>-1740000</v>
       </c>
       <c r="Q20" s="52">
-        <v>0</v>
-      </c>
-      <c r="R20" s="48"/>
+        <f>260000+630000+470000</f>
+        <v>1360000</v>
+      </c>
+      <c r="R20" s="44" t="s">
+        <v>39</v>
+      </c>
       <c r="S20" s="47">
-        <v>0</v>
-      </c>
-      <c r="T20" s="48"/>
+        <v>380000</v>
+      </c>
+      <c r="T20" s="48" t="s">
+        <v>16</v>
+      </c>
       <c r="U20" s="47"/>
       <c r="V20" s="153"/>
       <c r="W20" s="156">
         <v>0</v>
       </c>
-      <c r="X20" s="31"/>
+      <c r="X20" s="30"/>
       <c r="Y20" s="23"/>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="43">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B21" s="48">
         <v>2</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D21" s="49">
-        <f t="shared" si="2"/>
-        <v>49</v>
+        <f t="shared" si="3"/>
+        <v>141</v>
       </c>
       <c r="E21" s="64">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="F21" s="66">
         <f>+E21*Precios!$C$5</f>
-        <v>2940000</v>
+        <v>8460000</v>
       </c>
       <c r="G21" s="49"/>
       <c r="H21" s="90"/>
@@ -3407,12 +3427,10 @@
         <f>+I21*Precios!$C$6</f>
         <v>0</v>
       </c>
-      <c r="K21" s="48">
-        <v>49</v>
-      </c>
+      <c r="K21" s="48"/>
       <c r="L21" s="50">
         <f>+K21*Precios!$C$7</f>
-        <v>4900000</v>
+        <v>0</v>
       </c>
       <c r="M21" s="34">
         <v>0</v>
@@ -3422,19 +3440,17 @@
         <v>0</v>
       </c>
       <c r="O21" s="178">
-        <f t="shared" si="1"/>
-        <v>7840000</v>
+        <f t="shared" si="2"/>
+        <v>8460000</v>
       </c>
       <c r="P21" s="168">
-        <f t="shared" si="3"/>
-        <v>4840000</v>
+        <f t="shared" si="4"/>
+        <v>8460000</v>
       </c>
       <c r="Q21" s="52">
-        <v>3000000</v>
-      </c>
-      <c r="R21" s="48" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R21" s="48"/>
       <c r="S21" s="47">
         <v>0</v>
       </c>
@@ -3449,25 +3465,25 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="43">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B22" s="48">
         <v>2</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D22" s="49">
-        <f t="shared" si="2"/>
-        <v>25</v>
+        <f t="shared" si="3"/>
+        <v>49</v>
       </c>
       <c r="E22" s="64">
-        <f>9+16</f>
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F22" s="66">
         <f>+E22*Precios!$C$5</f>
-        <v>1500000</v>
+        <v>2940000</v>
       </c>
       <c r="G22" s="49"/>
       <c r="H22" s="90"/>
@@ -3477,11 +3493,11 @@
         <v>0</v>
       </c>
       <c r="K22" s="48">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L22" s="50">
         <f>+K22*Precios!$C$7</f>
-        <v>900000</v>
+        <v>4900000</v>
       </c>
       <c r="M22" s="34">
         <v>0</v>
@@ -3491,25 +3507,23 @@
         <v>0</v>
       </c>
       <c r="O22" s="178">
-        <f t="shared" si="1"/>
-        <v>2400000</v>
+        <f t="shared" si="2"/>
+        <v>7840000</v>
       </c>
       <c r="P22" s="168">
-        <f t="shared" si="3"/>
-        <v>-410000</v>
+        <f t="shared" si="4"/>
+        <v>4840000</v>
       </c>
       <c r="Q22" s="52">
-        <v>1350000</v>
+        <v>3000000</v>
       </c>
       <c r="R22" s="48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S22" s="47">
-        <v>1460000</v>
-      </c>
-      <c r="T22" s="48" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T22" s="48"/>
       <c r="U22" s="47"/>
       <c r="V22" s="153"/>
       <c r="W22" s="156">
@@ -3520,25 +3534,26 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="43">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B23" s="48">
         <v>2</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D23" s="49">
-        <f t="shared" si="2"/>
-        <v>66</v>
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="E23" s="64">
-        <f>13*4+14</f>
-        <v>66</v>
+        <f>9+16</f>
+        <v>25</v>
       </c>
       <c r="F23" s="66">
         <f>+E23*Precios!$C$5</f>
-        <v>3960000</v>
+        <v>1500000</v>
       </c>
       <c r="G23" s="49"/>
       <c r="H23" s="90"/>
@@ -3547,10 +3562,12 @@
         <f>+I23*Precios!$C$6</f>
         <v>0</v>
       </c>
-      <c r="K23" s="48"/>
+      <c r="K23" s="48">
+        <v>9</v>
+      </c>
       <c r="L23" s="50">
         <f>+K23*Precios!$C$7</f>
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="M23" s="34">
         <v>0</v>
@@ -3560,24 +3577,25 @@
         <v>0</v>
       </c>
       <c r="O23" s="178">
-        <f t="shared" si="1"/>
-        <v>3960000</v>
+        <f t="shared" si="2"/>
+        <v>2400000</v>
       </c>
       <c r="P23" s="168">
-        <f t="shared" si="3"/>
-        <v>240000</v>
+        <f t="shared" si="4"/>
+        <v>-410000</v>
       </c>
       <c r="Q23" s="52">
-        <f>1200000+2520000</f>
-        <v>3720000</v>
+        <v>1350000</v>
       </c>
       <c r="R23" s="48" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="S23" s="47">
-        <v>0</v>
-      </c>
-      <c r="T23" s="48"/>
+        <v>1460000</v>
+      </c>
+      <c r="T23" s="48" t="s">
+        <v>16</v>
+      </c>
       <c r="U23" s="47"/>
       <c r="V23" s="153"/>
       <c r="W23" s="156">
@@ -3588,24 +3606,26 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="43">
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B24" s="48">
         <v>2</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D24" s="49">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f t="shared" si="3"/>
+        <v>66</v>
       </c>
       <c r="E24" s="64">
-        <v>15</v>
+        <f>13*4+14</f>
+        <v>66</v>
       </c>
       <c r="F24" s="66">
         <f>+E24*Precios!$C$5</f>
-        <v>900000</v>
+        <v>3960000</v>
       </c>
       <c r="G24" s="49"/>
       <c r="H24" s="90"/>
@@ -3627,18 +3647,19 @@
         <v>0</v>
       </c>
       <c r="O24" s="178">
-        <f t="shared" si="1"/>
-        <v>900000</v>
+        <f t="shared" si="2"/>
+        <v>3960000</v>
       </c>
       <c r="P24" s="168">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>240000</v>
       </c>
       <c r="Q24" s="52">
-        <v>900000</v>
-      </c>
-      <c r="R24" s="44" t="s">
-        <v>38</v>
+        <f>1200000+2520000</f>
+        <v>3720000</v>
+      </c>
+      <c r="R24" s="48" t="s">
+        <v>213</v>
       </c>
       <c r="S24" s="47">
         <v>0</v>
@@ -3654,24 +3675,25 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="43">
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B25" s="48">
         <v>2</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D25" s="49">
-        <f t="shared" si="2"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="E25" s="64">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F25" s="66">
         <f>+E25*Precios!$C$5</f>
-        <v>3600000</v>
+        <v>900000</v>
       </c>
       <c r="G25" s="49"/>
       <c r="H25" s="90"/>
@@ -3693,18 +3715,18 @@
         <v>0</v>
       </c>
       <c r="O25" s="178">
-        <f t="shared" si="1"/>
-        <v>3600000</v>
+        <f t="shared" si="2"/>
+        <v>900000</v>
       </c>
       <c r="P25" s="168">
-        <f t="shared" si="3"/>
-        <v>600000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q25" s="52">
-        <v>3000000</v>
+        <v>900000</v>
       </c>
       <c r="R25" s="44" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="S25" s="47">
         <v>0</v>
@@ -3720,24 +3742,25 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="43">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B26" s="48">
         <v>2</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>237</v>
+        <v>68</v>
       </c>
       <c r="D26" s="49">
-        <f t="shared" ref="D26" si="4">+E26+G26</f>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="E26" s="64">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F26" s="66">
         <f>+E26*Precios!$C$5</f>
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="G26" s="49"/>
       <c r="H26" s="90"/>
@@ -3759,18 +3782,18 @@
         <v>0</v>
       </c>
       <c r="O26" s="178">
-        <f t="shared" ref="O26" si="5">+F26+J26+L26+N26-H26</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>3600000</v>
       </c>
       <c r="P26" s="168">
-        <f t="shared" ref="P26" si="6">+O26-(Q26+S26+W26+U26)</f>
-        <v>-1000000</v>
+        <f t="shared" si="4"/>
+        <v>600000</v>
       </c>
       <c r="Q26" s="52">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="R26" s="44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S26" s="47">
         <v>0</v>
@@ -3786,31 +3809,28 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="43">
-        <f>+A26+1</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B27" s="48">
         <v>2</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="D27" s="49">
-        <f t="shared" si="2"/>
-        <v>60</v>
+        <f t="shared" ref="D27" si="8">+E27+G27</f>
+        <v>0</v>
       </c>
       <c r="E27" s="64">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F27" s="66">
         <f>+E27*Precios!$C$5</f>
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="49"/>
-      <c r="H27" s="90">
-        <f>5*60000</f>
-        <v>300000</v>
-      </c>
+      <c r="H27" s="90"/>
       <c r="I27" s="34"/>
       <c r="J27" s="35">
         <f>+I27*Precios!$C$6</f>
@@ -3829,18 +3849,18 @@
         <v>0</v>
       </c>
       <c r="O27" s="178">
-        <f t="shared" si="1"/>
-        <v>3300000</v>
+        <f t="shared" ref="O27" si="9">+F27+J27+L27+N27-H27</f>
+        <v>0</v>
       </c>
       <c r="P27" s="168">
-        <f t="shared" si="3"/>
-        <v>660000</v>
+        <f t="shared" ref="P27" si="10">+O27-(Q27+S27+W27+U27)</f>
+        <v>-1000000</v>
       </c>
       <c r="Q27" s="52">
-        <v>2640000</v>
-      </c>
-      <c r="R27" s="48" t="s">
-        <v>45</v>
+        <v>1000000</v>
+      </c>
+      <c r="R27" s="44" t="s">
+        <v>16</v>
       </c>
       <c r="S27" s="47">
         <v>0</v>
@@ -3856,28 +3876,31 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="43">
-        <f t="shared" ref="A28:A44" si="7">+A27+1</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B28" s="48">
         <v>2</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D28" s="49">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="E28" s="64">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F28" s="66">
         <f>+E28*Precios!$C$5</f>
-        <v>900000</v>
+        <v>3600000</v>
       </c>
       <c r="G28" s="49"/>
-      <c r="H28" s="90"/>
+      <c r="H28" s="90">
+        <f>5*60000</f>
+        <v>300000</v>
+      </c>
       <c r="I28" s="34"/>
       <c r="J28" s="35">
         <f>+I28*Precios!$C$6</f>
@@ -3896,19 +3919,18 @@
         <v>0</v>
       </c>
       <c r="O28" s="178">
-        <f t="shared" si="1"/>
-        <v>900000</v>
+        <f t="shared" si="2"/>
+        <v>3300000</v>
       </c>
       <c r="P28" s="168">
-        <f t="shared" si="3"/>
-        <v>240000</v>
+        <f t="shared" si="4"/>
+        <v>660000</v>
       </c>
       <c r="Q28" s="52">
-        <f>260000+400000</f>
-        <v>660000</v>
-      </c>
-      <c r="R28" s="201" t="s">
-        <v>17</v>
+        <v>2640000</v>
+      </c>
+      <c r="R28" s="48" t="s">
+        <v>45</v>
       </c>
       <c r="S28" s="47">
         <v>0</v>
@@ -3924,23 +3946,25 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B29" s="48">
         <v>2</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D29" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="64"/>
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="E29" s="64">
+        <v>15</v>
+      </c>
       <c r="F29" s="66">
         <f>+E29*Precios!$C$5</f>
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="G29" s="49"/>
       <c r="H29" s="90"/>
@@ -3962,18 +3986,18 @@
         <v>0</v>
       </c>
       <c r="O29" s="178">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>900000</v>
       </c>
       <c r="P29" s="168">
-        <f t="shared" si="3"/>
-        <v>-2000000</v>
+        <f t="shared" si="4"/>
+        <v>240000</v>
       </c>
       <c r="Q29" s="52">
-        <f>1000000+1000000</f>
-        <v>2000000</v>
-      </c>
-      <c r="R29" s="48" t="s">
+        <f>260000+400000</f>
+        <v>660000</v>
+      </c>
+      <c r="R29" s="201" t="s">
         <v>17</v>
       </c>
       <c r="S29" s="47">
@@ -3990,25 +4014,23 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B30" s="48">
         <v>2</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D30" s="49">
-        <f t="shared" si="2"/>
-        <v>95</v>
-      </c>
-      <c r="E30" s="64">
-        <v>95</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="64"/>
       <c r="F30" s="66">
         <f>+E30*Precios!$C$5</f>
-        <v>5700000</v>
+        <v>0</v>
       </c>
       <c r="G30" s="49"/>
       <c r="H30" s="90"/>
@@ -4030,17 +4052,20 @@
         <v>0</v>
       </c>
       <c r="O30" s="178">
-        <f t="shared" si="1"/>
-        <v>5700000</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="P30" s="168">
-        <f t="shared" si="3"/>
-        <v>5700000</v>
+        <f t="shared" si="4"/>
+        <v>-2000000</v>
       </c>
       <c r="Q30" s="52">
-        <v>0</v>
-      </c>
-      <c r="R30" s="48"/>
+        <f>1000000+1000000</f>
+        <v>2000000</v>
+      </c>
+      <c r="R30" s="48" t="s">
+        <v>17</v>
+      </c>
       <c r="S30" s="47">
         <v>0</v>
       </c>
@@ -4055,23 +4080,25 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B31" s="48">
         <v>2</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D31" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="64"/>
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+      <c r="E31" s="64">
+        <v>95</v>
+      </c>
       <c r="F31" s="66">
         <f>+E31*Precios!$C$5</f>
-        <v>0</v>
+        <v>5700000</v>
       </c>
       <c r="G31" s="49"/>
       <c r="H31" s="90"/>
@@ -4093,12 +4120,12 @@
         <v>0</v>
       </c>
       <c r="O31" s="178">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5700000</v>
       </c>
       <c r="P31" s="168">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>5700000</v>
       </c>
       <c r="Q31" s="52">
         <v>0</v>
@@ -4118,17 +4145,17 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B32" s="48">
         <v>2</v>
       </c>
       <c r="C32" s="48" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D32" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E32" s="64"/>
@@ -4156,11 +4183,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P32" s="168">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q32" s="52">
@@ -4181,17 +4208,17 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B33" s="48">
         <v>2</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D33" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E33" s="64"/>
@@ -4219,19 +4246,17 @@
         <v>0</v>
       </c>
       <c r="O33" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P33" s="168">
-        <f t="shared" si="3"/>
-        <v>-180000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q33" s="52">
-        <v>180000</v>
-      </c>
-      <c r="R33" s="48" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R33" s="48"/>
       <c r="S33" s="47">
         <v>0</v>
       </c>
@@ -4246,25 +4271,23 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B34" s="48">
         <v>2</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D34" s="49">
-        <f t="shared" si="2"/>
-        <v>67</v>
-      </c>
-      <c r="E34" s="64">
-        <v>67</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="64"/>
       <c r="F34" s="66">
         <f>+E34*Precios!$C$5</f>
-        <v>4020000</v>
+        <v>0</v>
       </c>
       <c r="G34" s="49"/>
       <c r="H34" s="90"/>
@@ -4286,17 +4309,19 @@
         <v>0</v>
       </c>
       <c r="O34" s="178">
-        <f t="shared" si="1"/>
-        <v>4020000</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="P34" s="168">
-        <f t="shared" si="3"/>
-        <v>4020000</v>
+        <f t="shared" si="4"/>
+        <v>-180000</v>
       </c>
       <c r="Q34" s="52">
-        <v>0</v>
-      </c>
-      <c r="R34" s="48"/>
+        <v>180000</v>
+      </c>
+      <c r="R34" s="48" t="s">
+        <v>45</v>
+      </c>
       <c r="S34" s="47">
         <v>0</v>
       </c>
@@ -4311,30 +4336,28 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B35" s="48">
         <v>2</v>
       </c>
       <c r="C35" s="48" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D35" s="49">
-        <f t="shared" si="2"/>
-        <v>49</v>
+        <f t="shared" si="3"/>
+        <v>67</v>
       </c>
       <c r="E35" s="64">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F35" s="66">
         <f>+E35*Precios!$C$5</f>
-        <v>2940000</v>
+        <v>4020000</v>
       </c>
       <c r="G35" s="49"/>
-      <c r="H35" s="90">
-        <v>140000</v>
-      </c>
+      <c r="H35" s="90"/>
       <c r="I35" s="34"/>
       <c r="J35" s="35">
         <f>+I35*Precios!$C$6</f>
@@ -4353,19 +4376,17 @@
         <v>0</v>
       </c>
       <c r="O35" s="178">
-        <f>+F35+J35+L35+N35-H35</f>
-        <v>2800000</v>
+        <f t="shared" si="2"/>
+        <v>4020000</v>
       </c>
       <c r="P35" s="168">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>4020000</v>
       </c>
       <c r="Q35" s="52">
-        <v>2800000</v>
-      </c>
-      <c r="R35" s="44" t="s">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R35" s="48"/>
       <c r="S35" s="47">
         <v>0</v>
       </c>
@@ -4380,26 +4401,30 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B36" s="48">
         <v>2</v>
       </c>
       <c r="C36" s="48" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="D36" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="64"/>
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="E36" s="64">
+        <v>49</v>
+      </c>
       <c r="F36" s="66">
         <f>+E36*Precios!$C$5</f>
-        <v>0</v>
+        <v>2940000</v>
       </c>
       <c r="G36" s="49"/>
-      <c r="H36" s="90"/>
+      <c r="H36" s="90">
+        <v>140000</v>
+      </c>
       <c r="I36" s="34"/>
       <c r="J36" s="35">
         <f>+I36*Precios!$C$6</f>
@@ -4418,18 +4443,18 @@
         <v>0</v>
       </c>
       <c r="O36" s="178">
-        <f t="shared" ref="O36:O44" si="8">+F36+J36+L36+N36-H36</f>
-        <v>0</v>
+        <f>+F36+J36+L36+N36-H36</f>
+        <v>2800000</v>
       </c>
       <c r="P36" s="168">
-        <f t="shared" si="3"/>
-        <v>-200000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q36" s="52">
-        <v>200000</v>
-      </c>
-      <c r="R36" s="48" t="s">
-        <v>45</v>
+        <v>2800000</v>
+      </c>
+      <c r="R36" s="44" t="s">
+        <v>6</v>
       </c>
       <c r="S36" s="47">
         <v>0</v>
@@ -4445,17 +4470,17 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B37" s="48">
         <v>2</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="D37" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E37" s="64"/>
@@ -4483,17 +4508,19 @@
         <v>0</v>
       </c>
       <c r="O37" s="178">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="O37:O45" si="11">+F37+J37+L37+N37-H37</f>
         <v>0</v>
       </c>
       <c r="P37" s="168">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-200000</v>
       </c>
       <c r="Q37" s="52">
-        <v>0</v>
-      </c>
-      <c r="R37" s="48"/>
+        <v>200000</v>
+      </c>
+      <c r="R37" s="48" t="s">
+        <v>45</v>
+      </c>
       <c r="S37" s="47">
         <v>0</v>
       </c>
@@ -4508,17 +4535,17 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B38" s="48">
         <v>2</v>
       </c>
       <c r="C38" s="48" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D38" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E38" s="64"/>
@@ -4546,11 +4573,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="178">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P38" s="168">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q38" s="52">
@@ -4571,34 +4598,30 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B39" s="48">
         <v>2</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D39" s="49">
-        <f t="shared" si="2"/>
-        <v>75</v>
-      </c>
-      <c r="E39" s="64">
-        <v>75</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="64"/>
       <c r="F39" s="66">
         <f>+E39*Precios!$C$5</f>
-        <v>4500000</v>
+        <v>0</v>
       </c>
       <c r="G39" s="49"/>
       <c r="H39" s="90"/>
-      <c r="I39" s="34">
-        <v>75</v>
-      </c>
+      <c r="I39" s="34"/>
       <c r="J39" s="35">
         <f>+I39*Precios!$C$6</f>
-        <v>2250000</v>
+        <v>0</v>
       </c>
       <c r="K39" s="48"/>
       <c r="L39" s="50">
@@ -4613,19 +4636,17 @@
         <v>0</v>
       </c>
       <c r="O39" s="178">
-        <f t="shared" si="8"/>
-        <v>6750000</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="P39" s="168">
-        <f t="shared" si="3"/>
-        <v>3190000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q39" s="52">
-        <v>3560000</v>
-      </c>
-      <c r="R39" s="48" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R39" s="48"/>
       <c r="S39" s="47">
         <v>0</v>
       </c>
@@ -4640,35 +4661,34 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="B40" s="48">
         <v>2</v>
       </c>
       <c r="C40" s="48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D40" s="49">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="E40" s="64">
-        <f>23+12</f>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F40" s="66">
         <f>+E40*Precios!$C$5</f>
-        <v>2100000</v>
+        <v>4500000</v>
       </c>
       <c r="G40" s="49"/>
       <c r="H40" s="90"/>
       <c r="I40" s="34">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="J40" s="35">
         <f>+I40*Precios!$C$6</f>
-        <v>720000</v>
+        <v>2250000</v>
       </c>
       <c r="K40" s="48"/>
       <c r="L40" s="50">
@@ -4683,26 +4703,23 @@
         <v>0</v>
       </c>
       <c r="O40" s="178">
-        <f t="shared" si="8"/>
-        <v>2820000</v>
+        <f t="shared" si="11"/>
+        <v>6750000</v>
       </c>
       <c r="P40" s="168">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3190000</v>
       </c>
       <c r="Q40" s="52">
-        <v>300000</v>
+        <v>3560000</v>
       </c>
       <c r="R40" s="48" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="S40" s="47">
-        <f>990000+1500000+30000</f>
-        <v>2520000</v>
-      </c>
-      <c r="T40" s="48" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T40" s="48"/>
       <c r="U40" s="47"/>
       <c r="V40" s="153"/>
       <c r="W40" s="156">
@@ -4713,32 +4730,35 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B41" s="48">
         <v>2</v>
       </c>
       <c r="C41" s="48" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D41" s="49">
-        <f t="shared" si="2"/>
-        <v>95</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="E41" s="64">
-        <v>95</v>
+        <f>23+12</f>
+        <v>35</v>
       </c>
       <c r="F41" s="66">
         <f>+E41*Precios!$C$5</f>
-        <v>5700000</v>
+        <v>2100000</v>
       </c>
       <c r="G41" s="49"/>
       <c r="H41" s="90"/>
-      <c r="I41" s="34"/>
+      <c r="I41" s="34">
+        <v>24</v>
+      </c>
       <c r="J41" s="35">
         <f>+I41*Precios!$C$6</f>
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="K41" s="48"/>
       <c r="L41" s="50">
@@ -4753,21 +4773,26 @@
         <v>0</v>
       </c>
       <c r="O41" s="178">
-        <f t="shared" si="8"/>
-        <v>5700000</v>
+        <f t="shared" si="11"/>
+        <v>2820000</v>
       </c>
       <c r="P41" s="168">
-        <f t="shared" si="3"/>
-        <v>5700000</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="Q41" s="52">
-        <v>0</v>
-      </c>
-      <c r="R41" s="48"/>
+        <v>300000</v>
+      </c>
+      <c r="R41" s="48" t="s">
+        <v>45</v>
+      </c>
       <c r="S41" s="47">
-        <v>0</v>
-      </c>
-      <c r="T41" s="48"/>
+        <f>990000+1500000+30000</f>
+        <v>2520000</v>
+      </c>
+      <c r="T41" s="48" t="s">
+        <v>16</v>
+      </c>
       <c r="U41" s="47"/>
       <c r="V41" s="153"/>
       <c r="W41" s="156">
@@ -4778,25 +4803,25 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B42" s="48">
         <v>2</v>
       </c>
       <c r="C42" s="48" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D42" s="49">
-        <f t="shared" si="2"/>
-        <v>61</v>
+        <f t="shared" si="3"/>
+        <v>98</v>
       </c>
       <c r="E42" s="64">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="F42" s="66">
         <f>+E42*Precios!$C$5</f>
-        <v>3660000</v>
+        <v>5880000</v>
       </c>
       <c r="G42" s="49"/>
       <c r="H42" s="90"/>
@@ -4818,21 +4843,25 @@
         <v>0</v>
       </c>
       <c r="O42" s="178">
-        <f t="shared" si="8"/>
-        <v>3660000</v>
+        <f t="shared" si="11"/>
+        <v>5880000</v>
       </c>
       <c r="P42" s="168">
-        <f t="shared" si="3"/>
-        <v>3660000</v>
+        <f t="shared" si="4"/>
+        <v>120000</v>
       </c>
       <c r="Q42" s="52">
-        <v>0</v>
-      </c>
-      <c r="R42" s="48"/>
+        <v>4000000</v>
+      </c>
+      <c r="R42" s="217" t="s">
+        <v>16</v>
+      </c>
       <c r="S42" s="47">
-        <v>0</v>
-      </c>
-      <c r="T42" s="48"/>
+        <v>1760000</v>
+      </c>
+      <c r="T42" s="217" t="s">
+        <v>45</v>
+      </c>
       <c r="U42" s="47"/>
       <c r="V42" s="153"/>
       <c r="W42" s="156">
@@ -4843,23 +4872,25 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B43" s="48">
         <v>2</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D43" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="64"/>
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="E43" s="64">
+        <v>61</v>
+      </c>
       <c r="F43" s="66">
         <f>+E43*Precios!$C$5</f>
-        <v>0</v>
+        <v>3660000</v>
       </c>
       <c r="G43" s="49"/>
       <c r="H43" s="90"/>
@@ -4881,25 +4912,21 @@
         <v>0</v>
       </c>
       <c r="O43" s="178">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>3660000</v>
       </c>
       <c r="P43" s="168">
-        <f t="shared" si="3"/>
-        <v>-2500000</v>
+        <f t="shared" si="4"/>
+        <v>3660000</v>
       </c>
       <c r="Q43" s="52">
-        <v>800000</v>
-      </c>
-      <c r="R43" s="48" t="s">
-        <v>213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R43" s="48"/>
       <c r="S43" s="47">
-        <v>1700000</v>
-      </c>
-      <c r="T43" s="48" t="s">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T43" s="48"/>
       <c r="U43" s="47"/>
       <c r="V43" s="153"/>
       <c r="W43" s="156">
@@ -4908,31 +4935,27 @@
       <c r="X43" s="31"/>
       <c r="Y43" s="23"/>
     </row>
-    <row r="44" spans="1:25" ht="14.4" thickBot="1">
+    <row r="44" spans="1:25">
       <c r="A44" s="43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="B44" s="48">
         <v>2</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D44" s="49">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="E44" s="64">
-        <v>85</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="64"/>
       <c r="F44" s="66">
         <f>+E44*Precios!$C$5</f>
-        <v>5100000</v>
-      </c>
-      <c r="G44" s="49">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G44" s="49"/>
       <c r="H44" s="90"/>
       <c r="I44" s="34"/>
       <c r="J44" s="35">
@@ -4951,35 +4974,102 @@
         <f>+M44*Precios!$C$8</f>
         <v>0</v>
       </c>
-      <c r="O44" s="179">
-        <f t="shared" si="8"/>
+      <c r="O44" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="168">
+        <f t="shared" si="4"/>
+        <v>-2500000</v>
+      </c>
+      <c r="Q44" s="52">
+        <v>800000</v>
+      </c>
+      <c r="R44" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="S44" s="47">
+        <v>1700000</v>
+      </c>
+      <c r="T44" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="U44" s="47"/>
+      <c r="V44" s="153"/>
+      <c r="W44" s="156">
+        <v>0</v>
+      </c>
+      <c r="X44" s="31"/>
+      <c r="Y44" s="23"/>
+    </row>
+    <row r="45" spans="1:25" ht="14.4" thickBot="1">
+      <c r="A45" s="43">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B45" s="48">
+        <v>2</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="49">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+      <c r="E45" s="64">
+        <v>85</v>
+      </c>
+      <c r="F45" s="66">
+        <f>+E45*Precios!$C$5</f>
         <v>5100000</v>
       </c>
-      <c r="P44" s="169">
-        <f t="shared" si="3"/>
+      <c r="G45" s="49">
+        <v>5</v>
+      </c>
+      <c r="H45" s="90"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="35">
+        <f>+I45*Precios!$C$6</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="48"/>
+      <c r="L45" s="50">
+        <f>+K45*Precios!$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="34">
+        <v>0</v>
+      </c>
+      <c r="N45" s="165">
+        <f>+M45*Precios!$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="O45" s="179">
+        <f t="shared" si="11"/>
+        <v>5100000</v>
+      </c>
+      <c r="P45" s="169">
+        <f t="shared" si="4"/>
         <v>4300000</v>
       </c>
-      <c r="Q44" s="53">
+      <c r="Q45" s="53">
         <v>800000</v>
       </c>
-      <c r="R44" s="54" t="s">
+      <c r="R45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="S44" s="55">
-        <v>0</v>
-      </c>
-      <c r="T44" s="54"/>
-      <c r="U44" s="55"/>
-      <c r="V44" s="154"/>
-      <c r="W44" s="157">
-        <v>0</v>
-      </c>
-      <c r="X44" s="32"/>
-      <c r="Y44" s="23"/>
-    </row>
-    <row r="45" spans="1:25">
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
+      <c r="S45" s="55">
+        <v>0</v>
+      </c>
+      <c r="T45" s="54"/>
+      <c r="U45" s="55"/>
+      <c r="V45" s="154"/>
+      <c r="W45" s="157">
+        <v>0</v>
+      </c>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="23"/>
     </row>
     <row r="46" spans="1:25">
       <c r="O46" s="8"/>
@@ -5006,66 +5096,70 @@
       <c r="P51" s="8"/>
     </row>
     <row r="52" spans="6:16">
-      <c r="G52" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J52" t="s">
-        <v>113</v>
-      </c>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
     </row>
     <row r="53" spans="6:16">
-      <c r="F53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="162">
-        <f>+F9-H9</f>
-        <v>76780000</v>
-      </c>
-      <c r="H53" s="162">
-        <f>+P9-H54</f>
-        <v>27020000</v>
-      </c>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8">
-        <f>+G53-H53</f>
-        <v>49760000</v>
-      </c>
-      <c r="K53" s="8"/>
+      <c r="G53" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J53" t="s">
+        <v>113</v>
+      </c>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
     </row>
     <row r="54" spans="6:16">
       <c r="F54" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G54" s="162">
-        <f>+J9+L9+N9</f>
-        <v>12310000</v>
+        <f>+F9-H9</f>
+        <v>76960000</v>
       </c>
       <c r="H54" s="162">
-        <f>+IF(P9&gt;G54,G54)</f>
-        <v>12310000</v>
+        <f>+P9-H55</f>
+        <v>19440000</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8">
         <f>+G54-H54</f>
-        <v>0</v>
+        <v>57520000</v>
       </c>
       <c r="K54" s="8"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
     </row>
-    <row r="58" spans="6:16">
-      <c r="H58" s="162"/>
+    <row r="55" spans="6:16">
+      <c r="F55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="162">
+        <f>+J9+L9+N9</f>
+        <v>12310000</v>
+      </c>
+      <c r="H55" s="162">
+        <f>+IF(P9&gt;G55,G55)</f>
+        <v>12310000</v>
+      </c>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8">
+        <f>+G55-H55</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+    </row>
+    <row r="59" spans="6:16">
+      <c r="H59" s="162"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B14:R44">
-    <sortCondition ref="C14:C44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B14:R45">
+    <sortCondition ref="C14:C45"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="Q10:X10"/>
@@ -5074,7 +5168,7 @@
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="K10:L10"/>
   </mergeCells>
-  <conditionalFormatting sqref="P14:P44">
+  <conditionalFormatting sqref="P14:P45">
     <cfRule type="cellIs" dxfId="16" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -5116,11 +5210,11 @@
     <row r="2" spans="3:17">
       <c r="N2" s="4">
         <f>+N4+N9+N15+N29+N35</f>
-        <v>146398160</v>
+        <v>146992200</v>
       </c>
       <c r="O2" s="4">
         <f>+O4+O9+O15+O29+O35</f>
-        <v>133778160</v>
+        <v>134372200</v>
       </c>
     </row>
     <row r="3" spans="3:17">
@@ -5153,15 +5247,15 @@
       <c r="M4" s="188"/>
       <c r="N4" s="194">
         <f>SUM(N5:N7)</f>
-        <v>32400000</v>
+        <v>40160000</v>
       </c>
       <c r="O4" s="195">
         <f>SUM(O5:O7)</f>
-        <v>4484000</v>
+        <v>4884000</v>
       </c>
       <c r="P4" s="184">
         <f>+N4-O4</f>
-        <v>27916000</v>
+        <v>35276000</v>
       </c>
     </row>
     <row r="5" spans="3:17">
@@ -5170,7 +5264,7 @@
       </c>
       <c r="F5" s="160">
         <f>+DIVIDENDOS!E4</f>
-        <v>14421000</v>
+        <v>18421000</v>
       </c>
       <c r="G5" s="161"/>
       <c r="L5" t="s">
@@ -5178,7 +5272,7 @@
       </c>
       <c r="N5" s="160">
         <f>+DIVIDENDOS!C4</f>
-        <v>17270000</v>
+        <v>21270000</v>
       </c>
       <c r="O5" s="161">
         <f>+DIVIDENDOS!D4</f>
@@ -5191,7 +5285,7 @@
       </c>
       <c r="F6" s="160">
         <f>+DIVIDENDOS!E9</f>
-        <v>10175000</v>
+        <v>11775000</v>
       </c>
       <c r="G6" s="161"/>
       <c r="L6" t="s">
@@ -5199,11 +5293,11 @@
       </c>
       <c r="N6" s="160">
         <f>+DIVIDENDOS!C9</f>
-        <v>11810000</v>
+        <v>13810000</v>
       </c>
       <c r="O6" s="161">
         <f>+DIVIDENDOS!D9</f>
-        <v>1635000</v>
+        <v>2035000</v>
       </c>
     </row>
     <row r="7" spans="3:17">
@@ -5212,7 +5306,7 @@
       </c>
       <c r="F7" s="160">
         <f>+DIVIDENDOS!E16</f>
-        <v>3320000</v>
+        <v>5080000</v>
       </c>
       <c r="G7" s="161"/>
       <c r="L7" t="s">
@@ -5220,7 +5314,7 @@
       </c>
       <c r="N7" s="160">
         <f>+DIVIDENDOS!C16</f>
-        <v>3320000</v>
+        <v>5080000</v>
       </c>
       <c r="O7" s="161">
         <f>+DIVIDENDOS!D16</f>
@@ -5246,7 +5340,7 @@
       <c r="M9" s="188"/>
       <c r="N9" s="194">
         <f>SUM(N10:N12)</f>
-        <v>42181000</v>
+        <v>34601000</v>
       </c>
       <c r="O9" s="195">
         <f>SUM(O10:O12)</f>
@@ -5254,7 +5348,7 @@
       </c>
       <c r="P9" s="198">
         <f>+N9-O9</f>
-        <v>42181000</v>
+        <v>34601000</v>
       </c>
     </row>
     <row r="10" spans="3:17">
@@ -5263,7 +5357,7 @@
       </c>
       <c r="F10" s="160">
         <f>+ESCUELITAS!P9</f>
-        <v>39330000</v>
+        <v>31750000</v>
       </c>
       <c r="G10" s="161"/>
       <c r="L10" t="s">
@@ -5271,7 +5365,7 @@
       </c>
       <c r="N10" s="160">
         <f>+ESCUELITAS!P9</f>
-        <v>39330000</v>
+        <v>31750000</v>
       </c>
       <c r="O10" s="161"/>
     </row>
@@ -5341,11 +5435,11 @@
       </c>
       <c r="O15" s="193">
         <f>SUM(O16:O23)</f>
-        <v>49223160</v>
+        <v>49237200</v>
       </c>
       <c r="P15" s="187">
         <f>+O15-N15</f>
-        <v>49223160</v>
+        <v>49237200</v>
       </c>
     </row>
     <row r="16" spans="3:17">
@@ -5375,7 +5469,7 @@
       </c>
       <c r="F17" s="160"/>
       <c r="G17" s="161">
-        <f>+'INGRESOS-EGRESOS'!G74</f>
+        <f>+'INGRESOS-EGRESOS'!G76</f>
         <v>4030000</v>
       </c>
       <c r="K17" s="21"/>
@@ -5384,7 +5478,7 @@
       </c>
       <c r="N17" s="160"/>
       <c r="O17" s="161">
-        <f>+'INGRESOS-EGRESOS'!G74</f>
+        <f>+'INGRESOS-EGRESOS'!G76</f>
         <v>4030000</v>
       </c>
     </row>
@@ -5395,7 +5489,7 @@
       </c>
       <c r="F18" s="160"/>
       <c r="G18" s="161">
-        <f>+'INGRESOS-EGRESOS'!G60</f>
+        <f>+'INGRESOS-EGRESOS'!G61</f>
         <v>0</v>
       </c>
       <c r="K18" s="21"/>
@@ -5404,7 +5498,7 @@
       </c>
       <c r="N18" s="160"/>
       <c r="O18" s="161">
-        <f>+'INGRESOS-EGRESOS'!G60</f>
+        <f>+'INGRESOS-EGRESOS'!G61</f>
         <v>0</v>
       </c>
     </row>
@@ -5414,7 +5508,7 @@
       </c>
       <c r="F19" s="160"/>
       <c r="G19" s="161">
-        <f>+'INGRESOS-EGRESOS'!G90</f>
+        <f>+'INGRESOS-EGRESOS'!G92</f>
         <v>0</v>
       </c>
       <c r="L19" t="s">
@@ -5422,7 +5516,7 @@
       </c>
       <c r="N19" s="160"/>
       <c r="O19" s="161">
-        <f>+'INGRESOS-EGRESOS'!G90</f>
+        <f>+'INGRESOS-EGRESOS'!G92</f>
         <v>0</v>
       </c>
     </row>
@@ -5432,16 +5526,16 @@
       </c>
       <c r="F20" s="160"/>
       <c r="G20" s="161">
-        <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6023160</v>
+        <f>+'INGRESOS-EGRESOS'!G107</f>
+        <v>6037200</v>
       </c>
       <c r="L20" t="s">
         <v>45</v>
       </c>
       <c r="N20" s="160"/>
       <c r="O20" s="161">
-        <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6023160</v>
+        <f>+'INGRESOS-EGRESOS'!G107</f>
+        <v>6037200</v>
       </c>
     </row>
     <row r="21" spans="3:17">
@@ -5512,7 +5606,7 @@
       <c r="F27" s="160"/>
       <c r="G27" s="161">
         <f>+ESCUELITAS!O9</f>
-        <v>89090000</v>
+        <v>89270000</v>
       </c>
       <c r="N27" s="160"/>
       <c r="O27" s="161"/>
@@ -5551,11 +5645,11 @@
       </c>
       <c r="O29" s="193">
         <f>SUM(O30:O33)</f>
-        <v>80071000</v>
+        <v>80251000</v>
       </c>
       <c r="P29" s="197">
         <f>+O29-N29</f>
-        <v>79631000</v>
+        <v>79811000</v>
       </c>
       <c r="Q29" s="4"/>
     </row>
@@ -5577,7 +5671,7 @@
       </c>
       <c r="O30" s="161">
         <f>+ESCUELITAS!F9</f>
-        <v>77220000</v>
+        <v>77400000</v>
       </c>
     </row>
     <row r="31" spans="3:17">
@@ -5614,7 +5708,7 @@
       </c>
       <c r="F33" s="160">
         <f>+'INGRESOS-EGRESOS'!E19</f>
-        <v>36594000</v>
+        <v>36729000</v>
       </c>
       <c r="G33" s="161"/>
       <c r="L33" t="s">
@@ -5630,7 +5724,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="160">
-        <f>+'INGRESOS-EGRESOS'!E74</f>
+        <f>+'INGRESOS-EGRESOS'!E76</f>
         <v>7217000</v>
       </c>
       <c r="G34" s="161"/>
@@ -5642,8 +5736,8 @@
         <v>153</v>
       </c>
       <c r="F35" s="160">
-        <f>+'INGRESOS-EGRESOS'!E60</f>
-        <v>793000</v>
+        <f>+'INGRESOS-EGRESOS'!E61</f>
+        <v>998000</v>
       </c>
       <c r="G35" s="161"/>
       <c r="K35" s="183" t="s">
@@ -5653,7 +5747,7 @@
       <c r="M35" s="188"/>
       <c r="N35" s="194">
         <f>SUM(N36:N43)</f>
-        <v>71377160</v>
+        <v>71791200</v>
       </c>
       <c r="O35" s="195">
         <f>SUM(O36:O43)</f>
@@ -5661,7 +5755,7 @@
       </c>
       <c r="P35" s="198">
         <f>+N35-O35</f>
-        <v>71377160</v>
+        <v>71791200</v>
       </c>
     </row>
     <row r="36" spans="3:16">
@@ -5669,8 +5763,8 @@
         <v>154</v>
       </c>
       <c r="F36" s="160">
-        <f>+'INGRESOS-EGRESOS'!E90</f>
-        <v>40000</v>
+        <f>+'INGRESOS-EGRESOS'!E92</f>
+        <v>100000</v>
       </c>
       <c r="G36" s="161"/>
       <c r="K36" s="21"/>
@@ -5679,7 +5773,7 @@
       </c>
       <c r="N36" s="160">
         <f>+'INGRESOS-EGRESOS'!E19</f>
-        <v>36594000</v>
+        <v>36729000</v>
       </c>
       <c r="O36" s="161"/>
     </row>
@@ -5688,15 +5782,15 @@
         <v>45</v>
       </c>
       <c r="F37" s="160">
-        <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6023160</v>
+        <f>+'INGRESOS-EGRESOS'!E107</f>
+        <v>6037200</v>
       </c>
       <c r="G37" s="161"/>
       <c r="L37" t="s">
         <v>8</v>
       </c>
       <c r="N37" s="160">
-        <f>+'INGRESOS-EGRESOS'!E74</f>
+        <f>+'INGRESOS-EGRESOS'!E76</f>
         <v>7217000</v>
       </c>
       <c r="O37" s="161"/>
@@ -5711,8 +5805,8 @@
         <v>153</v>
       </c>
       <c r="N38" s="160">
-        <f>+'INGRESOS-EGRESOS'!E60</f>
-        <v>793000</v>
+        <f>+'INGRESOS-EGRESOS'!E61</f>
+        <v>998000</v>
       </c>
       <c r="O38" s="161"/>
     </row>
@@ -5726,8 +5820,8 @@
         <v>154</v>
       </c>
       <c r="N39" s="160">
-        <f>+'INGRESOS-EGRESOS'!E90</f>
-        <v>40000</v>
+        <f>+'INGRESOS-EGRESOS'!E92</f>
+        <v>100000</v>
       </c>
       <c r="O39" s="161"/>
     </row>
@@ -5738,19 +5832,19 @@
         <v>45</v>
       </c>
       <c r="N40" s="160">
-        <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6023160</v>
+        <f>+'INGRESOS-EGRESOS'!E107</f>
+        <v>6037200</v>
       </c>
       <c r="O40" s="161"/>
     </row>
     <row r="41" spans="3:16">
       <c r="F41" s="181">
         <f>SUM(F5:F38)</f>
-        <v>124063160</v>
+        <v>124257200</v>
       </c>
       <c r="G41" s="182">
         <f>SUM(G5:G38)</f>
-        <v>125404160</v>
+        <v>125598200</v>
       </c>
       <c r="L41" t="s">
         <v>235</v>
@@ -5842,7 +5936,7 @@
     <row r="4" spans="2:5">
       <c r="C4" s="8">
         <f>+ESCUELITAS!Z12+DUPLEX!O11</f>
-        <v>17270000</v>
+        <v>21270000</v>
       </c>
       <c r="D4" s="8">
         <f>+'INGRESOS-EGRESOS'!Q22</f>
@@ -5850,7 +5944,7 @@
       </c>
       <c r="E4" s="8">
         <f>+C4-D4</f>
-        <v>14421000</v>
+        <v>18421000</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -5870,15 +5964,15 @@
     <row r="9" spans="2:5">
       <c r="C9" s="8">
         <f>+ESCUELITAS!AA12+DUPLEX!P11</f>
-        <v>11810000</v>
+        <v>13810000</v>
       </c>
       <c r="D9" s="8">
         <f>+'INGRESOS-EGRESOS'!R22</f>
-        <v>1635000</v>
+        <v>2035000</v>
       </c>
       <c r="E9" s="8">
         <f>+C9-D9</f>
-        <v>10175000</v>
+        <v>11775000</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -5898,7 +5992,7 @@
     <row r="16" spans="2:5">
       <c r="C16" s="8">
         <f>+ESCUELITAS!AB12+DUPLEX!Q11</f>
-        <v>3320000</v>
+        <v>5080000</v>
       </c>
       <c r="D16" s="8">
         <f>+'INGRESOS-EGRESOS'!S22</f>
@@ -5906,7 +6000,7 @@
       </c>
       <c r="E16" s="8">
         <f>+C16-D16</f>
-        <v>3320000</v>
+        <v>5080000</v>
       </c>
     </row>
   </sheetData>
@@ -5916,7 +6010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF31B6B6-9E38-4245-9BA5-51FF3C7F9B06}">
-  <dimension ref="A2:AB163"/>
+  <dimension ref="A2:AB165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.19921875" style="8"/>
@@ -6007,7 +6101,7 @@
     </row>
     <row r="11" spans="3:10">
       <c r="J11" s="146">
-        <f>+H27+H48+H62+H65+H67+J65+J78+H78+H96</f>
+        <f>+H27+H49+H63+H66+H69+J66+J80+H80+H98</f>
         <v>1727500</v>
       </c>
     </row>
@@ -6040,12 +6134,12 @@
     </row>
     <row r="19" spans="1:19">
       <c r="E19" s="101">
-        <f>SUM(E22:E56)</f>
-        <v>36594000</v>
+        <f>SUM(E22:E57)</f>
+        <v>36729000</v>
       </c>
       <c r="F19" s="101">
-        <f t="shared" ref="F19:G19" si="0">SUM(F22:F56)</f>
-        <v>13184000</v>
+        <f t="shared" ref="F19:G19" si="0">SUM(F22:F57)</f>
+        <v>13319000</v>
       </c>
       <c r="G19" s="101">
         <f t="shared" si="0"/>
@@ -6126,11 +6220,11 @@
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8">
-        <f t="shared" ref="F22:F47" si="1">+H22+J22+L22</f>
+        <f t="shared" ref="F22:F48" si="1">+H22+J22+L22</f>
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" ref="G22:G53" si="2">+E22-F22</f>
+        <f t="shared" ref="G22:G54" si="2">+E22-F22</f>
         <v>0</v>
       </c>
       <c r="H22" s="69"/>
@@ -6139,15 +6233,15 @@
       <c r="L22" s="69"/>
       <c r="M22" s="70"/>
       <c r="Q22" s="8">
-        <f>+SUMIFS(H22:H126,I22:I126,Q20)+SUMIFS(J22:J126,K22:K126,Q20)+SUMIFS(L22:L126,M22:M126,Q20)+SUMIFS(N22:N126,O22:O126,Q20)</f>
+        <f>+SUMIFS(H22:H128,I22:I128,Q20)+SUMIFS(J22:J128,K22:K128,Q20)+SUMIFS(L22:L128,M22:M128,Q20)+SUMIFS(N22:N128,O22:O128,Q20)</f>
         <v>2849000</v>
       </c>
       <c r="R22" s="8">
-        <f>+SUMIFS(H22:H133,I22:I133,R20)+SUMIFS(J22:J133,K22:K133,R20)+SUMIFS(L22:L133,M22:M133,R20)+SUMIFS(N22:N133,O22:O133,R20)</f>
-        <v>1635000</v>
+        <f>+SUMIFS(H22:H135,I22:I135,R20)+SUMIFS(J22:J135,K22:K135,R20)+SUMIFS(L22:L135,M22:M135,R20)+SUMIFS(N22:N135,O22:O135,R20)</f>
+        <v>2035000</v>
       </c>
       <c r="S22" s="8">
-        <f>+SUMIFS(H22:H138,I22:I138,S20)+SUMIFS(J22:J138,K22:K138,S20)+SUMIFS(L22:L138,M22:M138,S20)+SUMIFS(N22:N138,O22:O138,S20)</f>
+        <f>+SUMIFS(H22:H140,I22:I140,S20)+SUMIFS(J22:J140,K22:K140,S20)+SUMIFS(L22:L140,M22:M140,S20)+SUMIFS(N22:N140,O22:O140,S20)</f>
         <v>0</v>
       </c>
     </row>
@@ -6476,6 +6570,7 @@
         <v>400000</v>
       </c>
       <c r="H34" s="69">
+        <f>400000</f>
         <v>400000</v>
       </c>
       <c r="I34" s="70" t="s">
@@ -6490,24 +6585,24 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="E35" s="8">
-        <v>50000</v>
+        <v>135000</v>
       </c>
       <c r="F35" s="8">
-        <f t="shared" ref="F35:F36" si="8">+H35+J35+L35</f>
-        <v>50000</v>
+        <f t="shared" ref="F35" si="8">+H35+J35+L35</f>
+        <v>135000</v>
       </c>
       <c r="G35" s="8">
-        <f t="shared" ref="G35:G36" si="9">+E35-F35</f>
+        <f t="shared" ref="G35" si="9">+E35-F35</f>
         <v>0</v>
       </c>
       <c r="H35" s="69">
-        <v>50000</v>
+        <v>135000</v>
       </c>
       <c r="I35" s="70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" s="8"/>
       <c r="L35" s="69"/>
@@ -6518,17 +6613,17 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E36" s="8">
         <v>50000</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F36:F37" si="10">+H36+J36+L36</f>
         <v>50000</v>
       </c>
       <c r="G36" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="G36:G37" si="11">+E36-F36</f>
         <v>0</v>
       </c>
       <c r="H36" s="69">
@@ -6546,21 +6641,21 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E37" s="8">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="F37" s="8">
-        <f t="shared" ref="F37" si="10">+H37+J37+L37</f>
-        <v>300000</v>
+        <f t="shared" si="10"/>
+        <v>50000</v>
       </c>
       <c r="G37" s="8">
-        <f t="shared" ref="G37" si="11">+E37-F37</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H37" s="69">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="I37" s="70" t="s">
         <v>16</v>
@@ -6574,19 +6669,25 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" s="8"/>
+        <v>217</v>
+      </c>
+      <c r="E38" s="8">
+        <v>300000</v>
+      </c>
       <c r="F38" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="F38" si="12">+H38+J38+L38</f>
+        <v>300000</v>
       </c>
       <c r="G38" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="69"/>
-      <c r="I38" s="70"/>
+        <f t="shared" ref="G38" si="13">+E38-F38</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="69">
+        <v>300000</v>
+      </c>
+      <c r="I38" s="70" t="s">
+        <v>16</v>
+      </c>
       <c r="J38" s="8"/>
       <c r="L38" s="69"/>
       <c r="M38" s="70"/>
@@ -6596,25 +6697,19 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="8">
-        <v>900000</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E39" s="8"/>
       <c r="F39" s="8">
         <f t="shared" si="1"/>
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H39" s="69">
-        <v>900000</v>
-      </c>
-      <c r="I39" s="70" t="s">
-        <v>17</v>
-      </c>
+      <c r="H39" s="69"/>
+      <c r="I39" s="70"/>
       <c r="J39" s="8"/>
       <c r="L39" s="69"/>
       <c r="M39" s="70"/>
@@ -6624,21 +6719,26 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="E40" s="8">
+        <v>900000</v>
+      </c>
       <c r="F40" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="G40" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H40" s="69"/>
-      <c r="I40" s="70"/>
+      <c r="H40" s="69">
+        <v>900000</v>
+      </c>
+      <c r="I40" s="70" t="s">
+        <v>17</v>
+      </c>
       <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
       <c r="L40" s="69"/>
       <c r="M40" s="70"/>
     </row>
@@ -6647,7 +6747,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8">
@@ -6670,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8">
@@ -6684,6 +6784,7 @@
       <c r="H42" s="69"/>
       <c r="I42" s="70"/>
       <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
       <c r="L42" s="69"/>
       <c r="M42" s="70"/>
     </row>
@@ -6692,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8">
@@ -6706,7 +6807,6 @@
       <c r="H43" s="69"/>
       <c r="I43" s="70"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
       <c r="L43" s="69"/>
       <c r="M43" s="70"/>
     </row>
@@ -6715,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8">
@@ -6727,8 +6827,8 @@
         <v>0</v>
       </c>
       <c r="H44" s="69"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="56"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="69"/>
       <c r="M44" s="70"/>
@@ -6738,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8">
@@ -6750,8 +6850,8 @@
         <v>0</v>
       </c>
       <c r="H45" s="69"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="8"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="56"/>
       <c r="K45" s="8"/>
       <c r="L45" s="69"/>
       <c r="M45" s="70"/>
@@ -6761,26 +6861,21 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="8">
-        <v>735000</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E46" s="8"/>
       <c r="F46" s="8">
         <f t="shared" si="1"/>
-        <v>735000</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H46" s="69">
-        <v>735000</v>
-      </c>
-      <c r="I46" s="70" t="s">
-        <v>17</v>
-      </c>
+      <c r="H46" s="69"/>
+      <c r="I46" s="70"/>
       <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
       <c r="L46" s="69"/>
       <c r="M46" s="70"/>
     </row>
@@ -6789,19 +6884,25 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>46</v>
-      </c>
-      <c r="E47" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="E47" s="8">
+        <v>735000</v>
+      </c>
       <c r="F47" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>735000</v>
       </c>
       <c r="G47" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H47" s="69"/>
-      <c r="I47" s="70"/>
+      <c r="H47" s="69">
+        <v>735000</v>
+      </c>
+      <c r="I47" s="70" t="s">
+        <v>17</v>
+      </c>
       <c r="J47" s="8"/>
       <c r="L47" s="69"/>
       <c r="M47" s="70"/>
@@ -6811,83 +6912,70 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="8">
-        <v>129000</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E48" s="8"/>
       <c r="F48" s="8">
-        <f>+H48+J48+L48</f>
-        <v>129000</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G48" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H48" s="69">
-        <v>129000</v>
-      </c>
-      <c r="I48" s="70" t="s">
-        <v>16</v>
-      </c>
+      <c r="H48" s="69"/>
+      <c r="I48" s="70"/>
       <c r="J48" s="8"/>
       <c r="L48" s="69"/>
       <c r="M48" s="70"/>
     </row>
-    <row r="49" spans="2:27" s="8" customFormat="1">
+    <row r="49" spans="2:27">
       <c r="B49" s="8">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
-      </c>
-      <c r="D49" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="E49" s="8">
+        <v>129000</v>
+      </c>
       <c r="F49" s="8">
-        <f t="shared" ref="F49:F53" si="12">+H49+J49+L49</f>
-        <v>0</v>
+        <f>+H49+J49+L49</f>
+        <v>129000</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H49" s="69"/>
-      <c r="I49" s="70"/>
-      <c r="K49"/>
+      <c r="H49" s="69">
+        <v>129000</v>
+      </c>
+      <c r="I49" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="8"/>
       <c r="L49" s="69"/>
       <c r="M49" s="70"/>
-      <c r="N49"/>
     </row>
     <row r="50" spans="2:27" s="8" customFormat="1">
       <c r="B50" s="8">
         <v>1</v>
       </c>
-      <c r="C50" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="8">
-        <v>19950000</v>
-      </c>
+      <c r="C50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="2"/>
       <c r="F50" s="8">
-        <f t="shared" si="12"/>
-        <v>2800000</v>
+        <f t="shared" ref="F50:F54" si="14">+H50+J50+L50</f>
+        <v>0</v>
       </c>
       <c r="G50" s="8">
         <f t="shared" si="2"/>
-        <v>17150000</v>
-      </c>
-      <c r="H50" s="151">
-        <v>0</v>
-      </c>
-      <c r="I50" s="70" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="8">
-        <v>2800000</v>
-      </c>
-      <c r="K50" t="s">
-        <v>71</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H50" s="69"/>
+      <c r="I50" s="70"/>
+      <c r="K50"/>
       <c r="L50" s="69"/>
       <c r="M50" s="70"/>
       <c r="N50"/>
@@ -6896,33 +6984,47 @@
       <c r="B51" s="8">
         <v>1</v>
       </c>
-      <c r="C51" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" s="2"/>
+      <c r="C51" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="58"/>
+      <c r="E51" s="8">
+        <v>19950000</v>
+      </c>
       <c r="F51" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>2800000</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="69"/>
-      <c r="I51" s="70"/>
+        <v>17150000</v>
+      </c>
+      <c r="H51" s="151">
+        <v>0</v>
+      </c>
+      <c r="I51" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="8">
+        <v>2800000</v>
+      </c>
+      <c r="K51" t="s">
+        <v>71</v>
+      </c>
       <c r="L51" s="69"/>
       <c r="M51" s="70"/>
+      <c r="N51"/>
     </row>
     <row r="52" spans="2:27" s="8" customFormat="1">
       <c r="B52" s="8">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2"/>
       <c r="F52" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G52" s="8">
@@ -6939,11 +7041,11 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D53" s="2"/>
       <c r="F53" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G53" s="8">
@@ -6956,11 +7058,25 @@
       <c r="M53" s="70"/>
     </row>
     <row r="54" spans="2:27" s="8" customFormat="1">
-      <c r="C54"/>
+      <c r="B54" s="8">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>98</v>
+      </c>
       <c r="D54" s="2"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="M54"/>
+      <c r="F54" s="8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="69"/>
+      <c r="I54" s="70"/>
+      <c r="L54" s="69"/>
+      <c r="M54" s="70"/>
     </row>
     <row r="55" spans="2:27" s="8" customFormat="1">
       <c r="C55"/>
@@ -6969,42 +7085,42 @@
       <c r="J55"/>
       <c r="M55"/>
     </row>
-    <row r="56" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
-      <c r="B56" s="170"/>
-      <c r="C56" s="171"/>
-      <c r="D56" s="172"/>
-      <c r="E56" s="170"/>
-      <c r="F56" s="170"/>
-      <c r="G56" s="170"/>
-      <c r="H56" s="170"/>
-      <c r="I56" s="171"/>
-      <c r="J56" s="171"/>
-      <c r="K56" s="170"/>
-      <c r="L56" s="170"/>
-      <c r="M56" s="171"/>
-      <c r="N56" s="170"/>
-      <c r="O56" s="170"/>
-      <c r="P56" s="170"/>
-      <c r="Q56" s="170"/>
-      <c r="R56" s="170"/>
-      <c r="S56" s="170"/>
-      <c r="T56" s="170"/>
-      <c r="U56" s="170"/>
-      <c r="V56" s="170"/>
-      <c r="W56" s="170"/>
-      <c r="X56" s="170"/>
-      <c r="Y56" s="170"/>
-      <c r="Z56" s="170"/>
-      <c r="AA56" s="170"/>
-    </row>
-    <row r="57" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
-      <c r="C57"/>
-      <c r="D57" s="2"/>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="M57"/>
-    </row>
-    <row r="58" spans="2:27" s="8" customFormat="1">
+    <row r="56" spans="2:27" s="8" customFormat="1">
+      <c r="C56"/>
+      <c r="D56" s="2"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="M56"/>
+    </row>
+    <row r="57" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+      <c r="B57" s="170"/>
+      <c r="C57" s="171"/>
+      <c r="D57" s="172"/>
+      <c r="E57" s="170"/>
+      <c r="F57" s="170"/>
+      <c r="G57" s="170"/>
+      <c r="H57" s="170"/>
+      <c r="I57" s="171"/>
+      <c r="J57" s="171"/>
+      <c r="K57" s="170"/>
+      <c r="L57" s="170"/>
+      <c r="M57" s="171"/>
+      <c r="N57" s="170"/>
+      <c r="O57" s="170"/>
+      <c r="P57" s="170"/>
+      <c r="Q57" s="170"/>
+      <c r="R57" s="170"/>
+      <c r="S57" s="170"/>
+      <c r="T57" s="170"/>
+      <c r="U57" s="170"/>
+      <c r="V57" s="170"/>
+      <c r="W57" s="170"/>
+      <c r="X57" s="170"/>
+      <c r="Y57" s="170"/>
+      <c r="Z57" s="170"/>
+      <c r="AA57" s="170"/>
+    </row>
+    <row r="58" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
       <c r="C58"/>
       <c r="D58" s="2"/>
       <c r="I58"/>
@@ -7021,104 +7137,83 @@
     <row r="60" spans="2:27" s="8" customFormat="1">
       <c r="C60"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="101">
-        <f>SUM(E62:E71)</f>
-        <v>793000</v>
-      </c>
-      <c r="F60" s="101">
-        <f t="shared" ref="F60:G60" si="13">SUM(F62:F71)</f>
-        <v>793000</v>
-      </c>
-      <c r="G60" s="101">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="I60"/>
       <c r="J60"/>
       <c r="M60"/>
     </row>
-    <row r="61" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
-      <c r="C61" s="21" t="s">
+    <row r="61" spans="2:27" s="8" customFormat="1">
+      <c r="C61"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="101">
+        <f>SUM(E63:E73)</f>
+        <v>998000</v>
+      </c>
+      <c r="F61" s="101">
+        <f t="shared" ref="F61:G61" si="15">SUM(F63:F73)</f>
+        <v>998000</v>
+      </c>
+      <c r="G61" s="101">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="M61"/>
+    </row>
+    <row r="62" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+      <c r="C62" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="D61" s="57"/>
-      <c r="E61" s="73" t="s">
+      <c r="D62" s="57"/>
+      <c r="E62" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="F61" s="73" t="s">
+      <c r="F62" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="G61" s="73" t="s">
+      <c r="G62" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="H61" s="74" t="s">
+      <c r="H62" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="I61" s="75" t="s">
+      <c r="I62" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="J61" s="73" t="s">
+      <c r="J62" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="K61" s="73" t="s">
+      <c r="K62" s="73" t="s">
         <v>151</v>
       </c>
-      <c r="L61" s="74" t="s">
+      <c r="L62" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="M61" s="75" t="s">
+      <c r="M62" s="75" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="62" spans="2:27" s="8" customFormat="1">
-      <c r="B62" s="8">
-        <v>2</v>
-      </c>
-      <c r="C62" t="s">
-        <v>92</v>
-      </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="8">
-        <v>40000</v>
-      </c>
-      <c r="F62" s="8">
-        <f t="shared" ref="F62:F66" si="14">+H62+J62+L62</f>
-        <v>40000</v>
-      </c>
-      <c r="G62" s="8">
-        <f t="shared" ref="G62:G67" si="15">+E62-F62</f>
-        <v>0</v>
-      </c>
-      <c r="H62" s="69">
-        <v>40000</v>
-      </c>
-      <c r="I62" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="L62" s="69"/>
-      <c r="M62" s="70"/>
     </row>
     <row r="63" spans="2:27" s="8" customFormat="1">
       <c r="B63" s="8">
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>92</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="8">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="F63" s="8">
-        <f t="shared" ref="F63" si="16">+H63+J63+L63</f>
-        <v>24000</v>
+        <f t="shared" ref="F63:F67" si="16">+H63+J63+L63</f>
+        <v>40000</v>
       </c>
       <c r="G63" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="G63:G69" si="17">+E63-F63</f>
         <v>0</v>
       </c>
       <c r="H63" s="69">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="I63" s="70" t="s">
         <v>16</v>
@@ -7131,22 +7226,22 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="8">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="F64" s="8">
-        <f t="shared" si="14"/>
-        <v>19000</v>
+        <f t="shared" ref="F64" si="18">+H64+J64+L64</f>
+        <v>24000</v>
       </c>
       <c r="G64" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H64" s="69">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="I64" s="70" t="s">
         <v>16</v>
@@ -7159,30 +7254,24 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="8">
-        <v>500000</v>
+        <v>19000</v>
       </c>
       <c r="F65" s="8">
-        <f t="shared" si="14"/>
-        <v>500000</v>
+        <f t="shared" si="16"/>
+        <v>19000</v>
       </c>
       <c r="G65" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H65" s="69">
-        <v>300000</v>
+        <v>19000</v>
       </c>
       <c r="I65" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="8">
-        <v>200000</v>
-      </c>
-      <c r="K65" t="s">
         <v>16</v>
       </c>
       <c r="L65" s="69"/>
@@ -7193,65 +7282,117 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="8">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F66" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>500000</v>
       </c>
       <c r="G66" s="8">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="69"/>
-      <c r="I66" s="72"/>
-      <c r="J66" s="56"/>
-      <c r="K66"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="69">
+        <v>300000</v>
+      </c>
+      <c r="I66" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="8">
+        <v>200000</v>
+      </c>
+      <c r="K66" t="s">
+        <v>16</v>
+      </c>
       <c r="L66" s="69"/>
       <c r="M66" s="70"/>
     </row>
-    <row r="67" spans="2:28">
+    <row r="67" spans="2:28" s="8" customFormat="1">
       <c r="B67" s="8">
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D67" s="2"/>
       <c r="E67" s="8">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="F67" s="8">
-        <f>+H67+J67+L67</f>
-        <v>210000</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="G67" s="8">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="69">
-        <v>210000</v>
-      </c>
-      <c r="I67" s="70" t="s">
-        <v>16</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="69"/>
+      <c r="I67" s="72"/>
+      <c r="J67" s="56"/>
+      <c r="K67"/>
       <c r="L67" s="69"/>
       <c r="M67" s="70"/>
     </row>
-    <row r="68" spans="2:28">
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
+    <row r="68" spans="2:28" s="8" customFormat="1">
+      <c r="B68" s="8">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>258</v>
+      </c>
+      <c r="D68" s="2"/>
+      <c r="E68" s="8">
+        <v>205000</v>
+      </c>
+      <c r="F68" s="8">
+        <f t="shared" ref="F68" si="19">+H68+J68+L68</f>
+        <v>205000</v>
+      </c>
+      <c r="G68" s="8">
+        <f t="shared" ref="G68" si="20">+E68-F68</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="69">
+        <v>205000</v>
+      </c>
+      <c r="I68" s="216" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="56"/>
+      <c r="K68"/>
+      <c r="L68" s="69"/>
+      <c r="M68" s="70"/>
     </row>
     <row r="69" spans="2:28">
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
+      <c r="B69" s="8">
+        <v>2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>33</v>
+      </c>
+      <c r="E69" s="8">
+        <v>210000</v>
+      </c>
+      <c r="F69" s="8">
+        <f>+H69+J69+L69</f>
+        <v>210000</v>
+      </c>
+      <c r="G69" s="8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="69">
+        <v>210000</v>
+      </c>
+      <c r="I69" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="L69" s="69"/>
+      <c r="M69" s="70"/>
     </row>
     <row r="70" spans="2:28">
       <c r="E70" s="8"/>
@@ -7259,271 +7400,229 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="2:28" ht="14.4" thickBot="1">
-      <c r="B71" s="170"/>
-      <c r="C71" s="171"/>
-      <c r="D71" s="172"/>
-      <c r="E71" s="170"/>
-      <c r="F71" s="170"/>
-      <c r="G71" s="170"/>
-      <c r="H71" s="170"/>
-      <c r="I71" s="171"/>
-      <c r="J71" s="171"/>
-      <c r="K71" s="170"/>
-      <c r="L71" s="170"/>
-      <c r="M71" s="171"/>
-      <c r="N71" s="170"/>
-      <c r="O71" s="170"/>
-      <c r="P71" s="170"/>
-      <c r="Q71" s="170"/>
-      <c r="R71" s="170"/>
-      <c r="S71" s="170"/>
-      <c r="T71" s="170"/>
-      <c r="U71" s="170"/>
-      <c r="V71" s="170"/>
-      <c r="W71" s="170"/>
-      <c r="X71" s="170"/>
-      <c r="Y71" s="170"/>
-      <c r="Z71" s="170"/>
-      <c r="AA71" s="170"/>
-      <c r="AB71" s="8"/>
-    </row>
-    <row r="72" spans="2:28" s="8" customFormat="1" ht="14.4" thickTop="1">
-      <c r="C72"/>
-      <c r="D72" s="2"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72"/>
-      <c r="M72"/>
-    </row>
-    <row r="73" spans="2:28" s="8" customFormat="1">
-      <c r="C73"/>
-      <c r="D73" s="2"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73"/>
-      <c r="M73"/>
-    </row>
-    <row r="74" spans="2:28" s="8" customFormat="1">
+    <row r="71" spans="2:28">
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+    </row>
+    <row r="72" spans="2:28">
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+    </row>
+    <row r="73" spans="2:28" ht="14.4" thickBot="1">
+      <c r="B73" s="170"/>
+      <c r="C73" s="171"/>
+      <c r="D73" s="172"/>
+      <c r="E73" s="170"/>
+      <c r="F73" s="170"/>
+      <c r="G73" s="170"/>
+      <c r="H73" s="170"/>
+      <c r="I73" s="171"/>
+      <c r="J73" s="171"/>
+      <c r="K73" s="170"/>
+      <c r="L73" s="170"/>
+      <c r="M73" s="171"/>
+      <c r="N73" s="170"/>
+      <c r="O73" s="170"/>
+      <c r="P73" s="170"/>
+      <c r="Q73" s="170"/>
+      <c r="R73" s="170"/>
+      <c r="S73" s="170"/>
+      <c r="T73" s="170"/>
+      <c r="U73" s="170"/>
+      <c r="V73" s="170"/>
+      <c r="W73" s="170"/>
+      <c r="X73" s="170"/>
+      <c r="Y73" s="170"/>
+      <c r="Z73" s="170"/>
+      <c r="AA73" s="170"/>
+      <c r="AB73" s="8"/>
+    </row>
+    <row r="74" spans="2:28" s="8" customFormat="1" ht="14.4" thickTop="1">
       <c r="C74"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="101">
-        <f>SUM(E76:E86)</f>
-        <v>7217000</v>
-      </c>
-      <c r="F74" s="101">
-        <f t="shared" ref="F74:G74" si="17">SUM(F76:F86)</f>
-        <v>3187000</v>
-      </c>
-      <c r="G74" s="101">
-        <f t="shared" si="17"/>
-        <v>4030000</v>
-      </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74"/>
       <c r="M74"/>
     </row>
-    <row r="75" spans="2:28" s="8" customFormat="1" ht="14.4" thickBot="1">
-      <c r="C75" s="21" t="s">
+    <row r="75" spans="2:28" s="8" customFormat="1">
+      <c r="C75"/>
+      <c r="D75" s="2"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75"/>
+      <c r="M75"/>
+    </row>
+    <row r="76" spans="2:28" s="8" customFormat="1">
+      <c r="C76"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="101">
+        <f>SUM(E78:E88)</f>
+        <v>7217000</v>
+      </c>
+      <c r="F76" s="101">
+        <f t="shared" ref="F76:G76" si="21">SUM(F78:F88)</f>
+        <v>3187000</v>
+      </c>
+      <c r="G76" s="101">
+        <f t="shared" si="21"/>
+        <v>4030000</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76"/>
+      <c r="M76"/>
+    </row>
+    <row r="77" spans="2:28" s="8" customFormat="1" ht="14.4" thickBot="1">
+      <c r="C77" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D75" s="57"/>
-      <c r="E75" s="73" t="s">
+      <c r="D77" s="57"/>
+      <c r="E77" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="F75" s="73" t="s">
+      <c r="F77" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="G75" s="73" t="s">
+      <c r="G77" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="H75" s="74" t="s">
+      <c r="H77" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="I75" s="75" t="s">
+      <c r="I77" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="J75" s="74" t="s">
+      <c r="J77" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="K75" s="75" t="s">
+      <c r="K77" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="L75" s="74" t="s">
+      <c r="L77" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="M75" s="75" t="s">
+      <c r="M77" s="75" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" s="8" customFormat="1">
-      <c r="B76" s="8">
-        <v>3</v>
-      </c>
-      <c r="C76" t="s">
-        <v>38</v>
-      </c>
-      <c r="D76" s="2"/>
-      <c r="E76" s="8">
-        <v>3800000</v>
-      </c>
-      <c r="F76" s="8">
-        <f>+H76+J76+L76</f>
-        <v>1160000</v>
-      </c>
-      <c r="G76" s="8">
-        <f t="shared" ref="G76:G83" si="18">+E76-F76</f>
-        <v>2640000</v>
-      </c>
-      <c r="H76" s="69">
-        <v>900000</v>
-      </c>
-      <c r="I76" s="70" t="s">
-        <v>159</v>
-      </c>
-      <c r="J76" s="69">
-        <v>260000</v>
-      </c>
-      <c r="K76" s="70" t="s">
-        <v>176</v>
-      </c>
-      <c r="L76" s="69"/>
-      <c r="M76" s="70"/>
-    </row>
-    <row r="77" spans="2:28" s="8" customFormat="1">
-      <c r="B77" s="8">
-        <v>3</v>
-      </c>
-      <c r="C77" t="s">
-        <v>93</v>
-      </c>
-      <c r="D77" s="2"/>
-      <c r="E77" s="8">
-        <v>200000</v>
-      </c>
-      <c r="F77" s="8">
-        <f t="shared" ref="F77:F83" si="19">+H77+J77+L77</f>
-        <v>0</v>
-      </c>
-      <c r="G77" s="8">
-        <f t="shared" si="18"/>
-        <v>200000</v>
-      </c>
-      <c r="H77" s="69"/>
-      <c r="I77" s="70"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="70"/>
-      <c r="L77" s="69"/>
-      <c r="M77" s="70"/>
     </row>
     <row r="78" spans="2:28" s="8" customFormat="1">
       <c r="B78" s="8">
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="8">
-        <f>290000+377000</f>
-        <v>667000</v>
+        <v>3800000</v>
       </c>
       <c r="F78" s="8">
-        <f t="shared" si="19"/>
-        <v>667000</v>
+        <f>+H78+J78+L78</f>
+        <v>1160000</v>
       </c>
       <c r="G78" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" ref="G78:G85" si="22">+E78-F78</f>
+        <v>2640000</v>
       </c>
       <c r="H78" s="69">
-        <v>188500</v>
+        <v>900000</v>
       </c>
       <c r="I78" s="70" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="J78" s="69">
-        <v>290000</v>
+        <v>260000</v>
       </c>
       <c r="K78" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" s="69">
-        <v>188500</v>
-      </c>
-      <c r="M78" s="70" t="s">
-        <v>16</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="L78" s="69"/>
+      <c r="M78" s="70"/>
     </row>
     <row r="79" spans="2:28" s="8" customFormat="1">
       <c r="B79" s="8">
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D79" s="2"/>
+      <c r="E79" s="8">
+        <v>200000</v>
+      </c>
       <c r="F79" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F79:F85" si="23">+H79+J79+L79</f>
         <v>0</v>
       </c>
       <c r="G79" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>200000</v>
       </c>
       <c r="H79" s="69"/>
       <c r="I79" s="70"/>
       <c r="J79" s="69"/>
-      <c r="K79" s="71"/>
+      <c r="K79" s="70"/>
       <c r="L79" s="69"/>
-      <c r="M79" s="71"/>
+      <c r="M79" s="70"/>
     </row>
     <row r="80" spans="2:28" s="8" customFormat="1">
       <c r="B80" s="8">
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="8">
-        <v>1950000</v>
+        <f>290000+377000</f>
+        <v>667000</v>
       </c>
       <c r="F80" s="8">
-        <f t="shared" si="19"/>
-        <v>1360000</v>
+        <f t="shared" si="23"/>
+        <v>667000</v>
       </c>
       <c r="G80" s="8">
-        <f t="shared" si="18"/>
-        <v>590000</v>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="H80" s="69">
-        <f>470000+260000+630000</f>
-        <v>1360000</v>
+        <v>188500</v>
       </c>
       <c r="I80" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="J80" s="69"/>
-      <c r="K80" s="70"/>
-      <c r="L80" s="69"/>
-      <c r="M80" s="70"/>
+        <v>16</v>
+      </c>
+      <c r="J80" s="69">
+        <v>290000</v>
+      </c>
+      <c r="K80" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="L80" s="69">
+        <v>188500</v>
+      </c>
+      <c r="M80" s="70" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="81" spans="2:27" s="8" customFormat="1">
       <c r="B81" s="8">
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D81" s="2"/>
       <c r="F81" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="G81" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H81" s="69"/>
@@ -7538,107 +7637,147 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D82" s="2"/>
+      <c r="E82" s="8">
+        <v>1950000</v>
+      </c>
       <c r="F82" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1360000</v>
       </c>
       <c r="G82" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="69"/>
-      <c r="I82" s="70"/>
+        <f t="shared" si="22"/>
+        <v>590000</v>
+      </c>
+      <c r="H82" s="69">
+        <f>470000+260000+630000</f>
+        <v>1360000</v>
+      </c>
+      <c r="I82" s="70" t="s">
+        <v>66</v>
+      </c>
       <c r="J82" s="69"/>
-      <c r="K82" s="71"/>
+      <c r="K82" s="70"/>
       <c r="L82" s="69"/>
-      <c r="M82" s="71"/>
+      <c r="M82" s="70"/>
     </row>
     <row r="83" spans="2:27" s="8" customFormat="1">
       <c r="B83" s="8">
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D83" s="2"/>
-      <c r="E83" s="8">
-        <v>600000</v>
-      </c>
       <c r="F83" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="G83" s="8">
-        <f t="shared" si="18"/>
-        <v>600000</v>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="H83" s="69"/>
       <c r="I83" s="70"/>
       <c r="J83" s="69"/>
-      <c r="K83" s="70"/>
+      <c r="K83" s="71"/>
       <c r="L83" s="69"/>
-      <c r="M83" s="70"/>
+      <c r="M83" s="71"/>
     </row>
     <row r="84" spans="2:27" s="8" customFormat="1">
-      <c r="C84"/>
+      <c r="B84" s="8">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
+        <v>50</v>
+      </c>
       <c r="D84" s="2"/>
-      <c r="I84"/>
-      <c r="K84"/>
-      <c r="M84"/>
+      <c r="F84" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="69"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="69"/>
+      <c r="K84" s="71"/>
+      <c r="L84" s="69"/>
+      <c r="M84" s="71"/>
     </row>
     <row r="85" spans="2:27" s="8" customFormat="1">
-      <c r="C85"/>
+      <c r="B85" s="8">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>49</v>
+      </c>
       <c r="D85" s="2"/>
-      <c r="I85"/>
-      <c r="K85"/>
-      <c r="M85"/>
-    </row>
-    <row r="86" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
-      <c r="B86" s="170"/>
-      <c r="C86" s="171"/>
-      <c r="D86" s="172"/>
-      <c r="E86" s="170"/>
-      <c r="F86" s="170"/>
-      <c r="G86" s="170"/>
-      <c r="H86" s="170"/>
-      <c r="I86" s="171"/>
-      <c r="J86" s="171"/>
-      <c r="K86" s="170"/>
-      <c r="L86" s="170"/>
-      <c r="M86" s="171"/>
-      <c r="N86" s="170"/>
-      <c r="O86" s="170"/>
-      <c r="P86" s="170"/>
-      <c r="Q86" s="170"/>
-      <c r="R86" s="170"/>
-      <c r="S86" s="170"/>
-      <c r="T86" s="170"/>
-      <c r="U86" s="170"/>
-      <c r="V86" s="170"/>
-      <c r="W86" s="170"/>
-      <c r="X86" s="170"/>
-      <c r="Y86" s="170"/>
-      <c r="Z86" s="170"/>
-      <c r="AA86" s="170"/>
-    </row>
-    <row r="87" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
+      <c r="E85" s="8">
+        <v>600000</v>
+      </c>
+      <c r="F85" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="8">
+        <f t="shared" si="22"/>
+        <v>600000</v>
+      </c>
+      <c r="H85" s="69"/>
+      <c r="I85" s="70"/>
+      <c r="J85" s="69"/>
+      <c r="K85" s="70"/>
+      <c r="L85" s="69"/>
+      <c r="M85" s="70"/>
+    </row>
+    <row r="86" spans="2:27" s="8" customFormat="1">
+      <c r="C86"/>
+      <c r="D86" s="2"/>
+      <c r="I86"/>
+      <c r="K86"/>
+      <c r="M86"/>
+    </row>
+    <row r="87" spans="2:27" s="8" customFormat="1">
       <c r="C87"/>
       <c r="D87" s="2"/>
       <c r="I87"/>
       <c r="K87"/>
       <c r="M87"/>
     </row>
-    <row r="88" spans="2:27" s="8" customFormat="1">
-      <c r="C88"/>
-      <c r="D88" s="2"/>
-      <c r="I88"/>
-      <c r="K88"/>
-      <c r="M88"/>
-    </row>
-    <row r="89" spans="2:27" s="8" customFormat="1">
+    <row r="88" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+      <c r="B88" s="170"/>
+      <c r="C88" s="171"/>
+      <c r="D88" s="172"/>
+      <c r="E88" s="170"/>
+      <c r="F88" s="170"/>
+      <c r="G88" s="170"/>
+      <c r="H88" s="170"/>
+      <c r="I88" s="171"/>
+      <c r="J88" s="171"/>
+      <c r="K88" s="170"/>
+      <c r="L88" s="170"/>
+      <c r="M88" s="171"/>
+      <c r="N88" s="170"/>
+      <c r="O88" s="170"/>
+      <c r="P88" s="170"/>
+      <c r="Q88" s="170"/>
+      <c r="R88" s="170"/>
+      <c r="S88" s="170"/>
+      <c r="T88" s="170"/>
+      <c r="U88" s="170"/>
+      <c r="V88" s="170"/>
+      <c r="W88" s="170"/>
+      <c r="X88" s="170"/>
+      <c r="Y88" s="170"/>
+      <c r="Z88" s="170"/>
+      <c r="AA88" s="170"/>
+    </row>
+    <row r="89" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
       <c r="C89"/>
       <c r="D89" s="2"/>
       <c r="I89"/>
@@ -7648,120 +7787,90 @@
     <row r="90" spans="2:27" s="8" customFormat="1">
       <c r="C90"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="101">
-        <f>SUM(E92:E101)</f>
-        <v>40000</v>
-      </c>
-      <c r="F90" s="101">
-        <f t="shared" ref="F90:G90" si="20">SUM(F92:F101)</f>
-        <v>40000</v>
-      </c>
-      <c r="G90" s="101">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="I90"/>
-      <c r="J90"/>
       <c r="K90"/>
       <c r="M90"/>
     </row>
-    <row r="91" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
-      <c r="C91" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D91" s="57"/>
-      <c r="E91" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="F91" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="G91" s="73" t="s">
-        <v>149</v>
-      </c>
-      <c r="H91" s="74" t="s">
-        <v>148</v>
-      </c>
-      <c r="I91" s="75" t="s">
-        <v>150</v>
-      </c>
-      <c r="J91" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="K91" s="73" t="s">
-        <v>151</v>
-      </c>
-      <c r="L91" s="74" t="s">
-        <v>148</v>
-      </c>
-      <c r="M91" s="75" t="s">
-        <v>158</v>
-      </c>
+    <row r="91" spans="2:27" s="8" customFormat="1">
+      <c r="C91"/>
+      <c r="D91" s="2"/>
+      <c r="I91"/>
+      <c r="K91"/>
+      <c r="M91"/>
     </row>
     <row r="92" spans="2:27" s="8" customFormat="1">
-      <c r="B92" s="8">
-        <v>4</v>
-      </c>
-      <c r="C92" t="s">
-        <v>47</v>
-      </c>
+      <c r="C92"/>
       <c r="D92" s="2"/>
-      <c r="F92" s="8">
-        <f t="shared" ref="F92:F97" si="21">+H92+J92+L92</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="8">
-        <f t="shared" ref="G92:G97" si="22">+E92-F92</f>
-        <v>0</v>
-      </c>
-      <c r="H92" s="69"/>
-      <c r="I92" s="70"/>
+      <c r="E92" s="101">
+        <f>SUM(E94:E103)</f>
+        <v>100000</v>
+      </c>
+      <c r="F92" s="101">
+        <f t="shared" ref="F92:G92" si="24">SUM(F94:F103)</f>
+        <v>100000</v>
+      </c>
+      <c r="G92" s="101">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I92"/>
       <c r="J92"/>
       <c r="K92"/>
-      <c r="L92" s="69"/>
-      <c r="M92" s="70"/>
-    </row>
-    <row r="93" spans="2:27" s="8" customFormat="1">
-      <c r="B93" s="8">
-        <v>4</v>
-      </c>
-      <c r="C93" t="s">
-        <v>52</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="F93" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="G93" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H93" s="69"/>
-      <c r="I93" s="70"/>
-      <c r="J93"/>
-      <c r="L93" s="69"/>
-      <c r="M93" s="70"/>
+      <c r="M92"/>
+    </row>
+    <row r="93" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+      <c r="C93" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D93" s="57"/>
+      <c r="E93" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="F93" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="G93" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="H93" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="I93" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="J93" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="K93" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="L93" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="M93" s="75" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="94" spans="2:27" s="8" customFormat="1">
       <c r="B94" s="8">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D94" s="2"/>
       <c r="F94" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="F94:F99" si="25">+H94+J94+L94</f>
         <v>0</v>
       </c>
       <c r="G94" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G94:G99" si="26">+E94-F94</f>
         <v>0</v>
       </c>
       <c r="H94" s="69"/>
       <c r="I94" s="70"/>
       <c r="J94"/>
+      <c r="K94"/>
       <c r="L94" s="69"/>
       <c r="M94" s="70"/>
     </row>
@@ -7770,15 +7879,15 @@
         <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="D95" s="2"/>
       <c r="F95" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="G95" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H95" s="69"/>
@@ -7792,26 +7901,19 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D96" s="2"/>
-      <c r="E96" s="8">
-        <v>40000</v>
-      </c>
       <c r="F96" s="8">
-        <f t="shared" si="21"/>
-        <v>40000</v>
+        <f t="shared" si="25"/>
+        <v>0</v>
       </c>
       <c r="G96" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="69">
-        <v>40000</v>
-      </c>
-      <c r="I96" s="70" t="s">
-        <v>16</v>
-      </c>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H96" s="69"/>
+      <c r="I96" s="70"/>
       <c r="J96"/>
       <c r="L96" s="69"/>
       <c r="M96" s="70"/>
@@ -7821,36 +7923,80 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D97" s="2"/>
+      <c r="E97" s="8">
+        <v>60000</v>
+      </c>
       <c r="F97" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" si="25"/>
+        <v>60000</v>
       </c>
       <c r="G97" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="69"/>
-      <c r="I97" s="70"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="69">
+        <v>60000</v>
+      </c>
+      <c r="I97" s="70" t="s">
+        <v>17</v>
+      </c>
       <c r="J97"/>
       <c r="L97" s="69"/>
       <c r="M97" s="70"/>
     </row>
     <row r="98" spans="2:27" s="8" customFormat="1">
-      <c r="C98"/>
+      <c r="B98" s="8">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>97</v>
+      </c>
       <c r="D98" s="2"/>
-      <c r="I98"/>
+      <c r="E98" s="8">
+        <v>40000</v>
+      </c>
+      <c r="F98" s="8">
+        <f t="shared" si="25"/>
+        <v>40000</v>
+      </c>
+      <c r="G98" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="69">
+        <v>40000</v>
+      </c>
+      <c r="I98" s="70" t="s">
+        <v>16</v>
+      </c>
       <c r="J98"/>
-      <c r="M98"/>
+      <c r="L98" s="69"/>
+      <c r="M98" s="70"/>
     </row>
     <row r="99" spans="2:27" s="8" customFormat="1">
-      <c r="C99"/>
+      <c r="B99" s="8">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>87</v>
+      </c>
       <c r="D99" s="2"/>
-      <c r="I99"/>
+      <c r="F99" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="69"/>
+      <c r="I99" s="70"/>
       <c r="J99"/>
-      <c r="M99"/>
+      <c r="L99" s="69"/>
+      <c r="M99" s="70"/>
     </row>
     <row r="100" spans="2:27" s="8" customFormat="1">
       <c r="C100"/>
@@ -7859,49 +8005,49 @@
       <c r="J100"/>
       <c r="M100"/>
     </row>
-    <row r="101" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
-      <c r="B101" s="170"/>
-      <c r="C101" s="171"/>
-      <c r="D101" s="172"/>
-      <c r="E101" s="170"/>
-      <c r="F101" s="170"/>
-      <c r="G101" s="170"/>
-      <c r="H101" s="170"/>
-      <c r="I101" s="171"/>
-      <c r="J101" s="171"/>
-      <c r="K101" s="170"/>
-      <c r="L101" s="170"/>
-      <c r="M101" s="171"/>
-      <c r="N101" s="170"/>
-      <c r="O101" s="170"/>
-      <c r="P101" s="170"/>
-      <c r="Q101" s="170"/>
-      <c r="R101" s="170"/>
-      <c r="S101" s="170"/>
-      <c r="T101" s="170"/>
-      <c r="U101" s="170"/>
-      <c r="V101" s="170"/>
-      <c r="W101" s="170"/>
-      <c r="X101" s="170"/>
-      <c r="Y101" s="170"/>
-      <c r="Z101" s="170"/>
-      <c r="AA101" s="170"/>
-    </row>
-    <row r="102" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
+    <row r="101" spans="2:27" s="8" customFormat="1">
+      <c r="C101"/>
+      <c r="D101" s="2"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="M101"/>
+    </row>
+    <row r="102" spans="2:27" s="8" customFormat="1">
       <c r="C102"/>
       <c r="D102" s="2"/>
       <c r="I102"/>
       <c r="J102"/>
       <c r="M102"/>
     </row>
-    <row r="103" spans="2:27" s="8" customFormat="1">
-      <c r="C103"/>
-      <c r="D103" s="2"/>
-      <c r="I103"/>
-      <c r="J103"/>
-      <c r="M103"/>
-    </row>
-    <row r="104" spans="2:27" s="8" customFormat="1">
+    <row r="103" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+      <c r="B103" s="170"/>
+      <c r="C103" s="171"/>
+      <c r="D103" s="172"/>
+      <c r="E103" s="170"/>
+      <c r="F103" s="170"/>
+      <c r="G103" s="170"/>
+      <c r="H103" s="170"/>
+      <c r="I103" s="171"/>
+      <c r="J103" s="171"/>
+      <c r="K103" s="170"/>
+      <c r="L103" s="170"/>
+      <c r="M103" s="171"/>
+      <c r="N103" s="170"/>
+      <c r="O103" s="170"/>
+      <c r="P103" s="170"/>
+      <c r="Q103" s="170"/>
+      <c r="R103" s="170"/>
+      <c r="S103" s="170"/>
+      <c r="T103" s="170"/>
+      <c r="U103" s="170"/>
+      <c r="V103" s="170"/>
+      <c r="W103" s="170"/>
+      <c r="X103" s="170"/>
+      <c r="Y103" s="170"/>
+      <c r="Z103" s="170"/>
+      <c r="AA103" s="170"/>
+    </row>
+    <row r="104" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
       <c r="C104"/>
       <c r="D104" s="2"/>
       <c r="I104"/>
@@ -7911,237 +8057,237 @@
     <row r="105" spans="2:27" s="8" customFormat="1">
       <c r="C105"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="101">
-        <f>SUM(E107:E111)</f>
-        <v>6023160</v>
-      </c>
-      <c r="F105" s="101">
-        <f t="shared" ref="F105:G105" si="23">SUM(F107:F111)</f>
-        <v>0</v>
-      </c>
-      <c r="G105" s="101">
-        <f t="shared" si="23"/>
-        <v>6023160</v>
-      </c>
       <c r="I105"/>
       <c r="J105"/>
       <c r="M105"/>
     </row>
-    <row r="106" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="106" spans="2:27" s="8" customFormat="1">
       <c r="C106"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="F106" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="G106" s="73" t="s">
-        <v>149</v>
-      </c>
-      <c r="H106" s="74" t="s">
-        <v>148</v>
-      </c>
-      <c r="I106" s="75" t="s">
-        <v>150</v>
-      </c>
-      <c r="J106" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="K106" s="73" t="s">
-        <v>151</v>
-      </c>
-      <c r="L106" s="74" t="s">
-        <v>148</v>
-      </c>
-      <c r="M106" s="75" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="107" spans="2:27">
-      <c r="B107" s="8">
-        <v>4680</v>
-      </c>
-      <c r="C107" t="s">
-        <v>45</v>
-      </c>
-      <c r="D107" s="2">
-        <f>+ESCUELITAS!E9</f>
-        <v>1287</v>
-      </c>
-      <c r="E107" s="8">
-        <f>+D107*B107</f>
-        <v>6023160</v>
-      </c>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8">
-        <f>+E107-F107</f>
-        <v>6023160</v>
-      </c>
-      <c r="H107" s="69"/>
-      <c r="I107" s="70"/>
-      <c r="L107" s="69"/>
-      <c r="M107" s="70"/>
-    </row>
-    <row r="108" spans="2:27" s="8" customFormat="1">
+      <c r="I106"/>
+      <c r="J106"/>
+      <c r="M106"/>
+    </row>
+    <row r="107" spans="2:27" s="8" customFormat="1">
+      <c r="C107"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="101">
+        <f>SUM(E109:E113)</f>
+        <v>6037200</v>
+      </c>
+      <c r="F107" s="101">
+        <f t="shared" ref="F107:G107" si="27">SUM(F109:F113)</f>
+        <v>0</v>
+      </c>
+      <c r="G107" s="101">
+        <f t="shared" si="27"/>
+        <v>6037200</v>
+      </c>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="M107"/>
+    </row>
+    <row r="108" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
       <c r="C108"/>
       <c r="D108" s="2"/>
-      <c r="I108"/>
-      <c r="J108"/>
-      <c r="M108"/>
-    </row>
-    <row r="109" spans="2:27" s="8" customFormat="1">
-      <c r="C109"/>
-      <c r="D109" s="2"/>
-      <c r="I109"/>
-      <c r="J109"/>
-      <c r="M109"/>
-    </row>
-    <row r="111" spans="2:27" ht="14.4" thickBot="1">
-      <c r="B111" s="170"/>
-      <c r="C111" s="171"/>
-      <c r="D111" s="172"/>
-      <c r="E111" s="170"/>
-      <c r="F111" s="170"/>
-      <c r="G111" s="170"/>
-      <c r="H111" s="170"/>
-      <c r="I111" s="171"/>
-      <c r="J111" s="171"/>
-      <c r="K111" s="170"/>
-      <c r="L111" s="170"/>
-      <c r="M111" s="171"/>
-      <c r="N111" s="170"/>
-      <c r="O111" s="170"/>
-      <c r="P111" s="170"/>
-      <c r="Q111" s="170"/>
-      <c r="R111" s="170"/>
-      <c r="S111" s="170"/>
-      <c r="T111" s="170"/>
-      <c r="U111" s="170"/>
-      <c r="V111" s="170"/>
-      <c r="W111" s="170"/>
-      <c r="X111" s="170"/>
-      <c r="Y111" s="170"/>
-      <c r="Z111" s="170"/>
-      <c r="AA111" s="170"/>
-    </row>
-    <row r="112" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
-      <c r="C112"/>
-      <c r="D112" s="2"/>
-      <c r="I112"/>
-      <c r="J112"/>
-      <c r="M112"/>
-    </row>
-    <row r="113" spans="3:13" s="8" customFormat="1">
-      <c r="C113"/>
-      <c r="D113" s="2"/>
-      <c r="I113"/>
-      <c r="J113"/>
-      <c r="M113"/>
-    </row>
-    <row r="114" spans="3:13" s="8" customFormat="1">
+      <c r="E108" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="G108" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="H108" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="I108" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="J108" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="K108" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="L108" s="74" t="s">
+        <v>148</v>
+      </c>
+      <c r="M108" s="75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="109" spans="2:27">
+      <c r="B109" s="8">
+        <v>4680</v>
+      </c>
+      <c r="C109" t="s">
+        <v>45</v>
+      </c>
+      <c r="D109" s="2">
+        <f>+ESCUELITAS!E9</f>
+        <v>1290</v>
+      </c>
+      <c r="E109" s="8">
+        <f>+D109*B109</f>
+        <v>6037200</v>
+      </c>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8">
+        <f>+E109-F109</f>
+        <v>6037200</v>
+      </c>
+      <c r="H109" s="69"/>
+      <c r="I109" s="70"/>
+      <c r="L109" s="69"/>
+      <c r="M109" s="70"/>
+    </row>
+    <row r="110" spans="2:27" s="8" customFormat="1">
+      <c r="C110"/>
+      <c r="D110" s="2"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="M110"/>
+    </row>
+    <row r="111" spans="2:27" s="8" customFormat="1">
+      <c r="C111"/>
+      <c r="D111" s="2"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="M111"/>
+    </row>
+    <row r="113" spans="2:27" ht="14.4" thickBot="1">
+      <c r="B113" s="170"/>
+      <c r="C113" s="171"/>
+      <c r="D113" s="172"/>
+      <c r="E113" s="170"/>
+      <c r="F113" s="170"/>
+      <c r="G113" s="170"/>
+      <c r="H113" s="170"/>
+      <c r="I113" s="171"/>
+      <c r="J113" s="171"/>
+      <c r="K113" s="170"/>
+      <c r="L113" s="170"/>
+      <c r="M113" s="171"/>
+      <c r="N113" s="170"/>
+      <c r="O113" s="170"/>
+      <c r="P113" s="170"/>
+      <c r="Q113" s="170"/>
+      <c r="R113" s="170"/>
+      <c r="S113" s="170"/>
+      <c r="T113" s="170"/>
+      <c r="U113" s="170"/>
+      <c r="V113" s="170"/>
+      <c r="W113" s="170"/>
+      <c r="X113" s="170"/>
+      <c r="Y113" s="170"/>
+      <c r="Z113" s="170"/>
+      <c r="AA113" s="170"/>
+    </row>
+    <row r="114" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
       <c r="C114"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="56"/>
-      <c r="H114" s="56"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
+      <c r="I114"/>
+      <c r="J114"/>
       <c r="M114"/>
     </row>
-    <row r="115" spans="3:13" s="8" customFormat="1">
+    <row r="115" spans="2:27" s="8" customFormat="1">
       <c r="C115"/>
       <c r="D115" s="2"/>
       <c r="I115"/>
       <c r="J115"/>
       <c r="M115"/>
     </row>
-    <row r="116" spans="3:13" s="8" customFormat="1">
+    <row r="116" spans="2:27" s="8" customFormat="1">
       <c r="C116"/>
       <c r="D116" s="2"/>
-      <c r="I116"/>
-      <c r="J116"/>
+      <c r="E116" s="56"/>
+      <c r="F116" s="56"/>
+      <c r="G116" s="56"/>
+      <c r="H116" s="56"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
       <c r="M116"/>
     </row>
-    <row r="117" spans="3:13" s="8" customFormat="1">
+    <row r="117" spans="2:27" s="8" customFormat="1">
       <c r="C117"/>
       <c r="D117" s="2"/>
       <c r="I117"/>
       <c r="J117"/>
       <c r="M117"/>
     </row>
-    <row r="118" spans="3:13" s="8" customFormat="1">
+    <row r="118" spans="2:27" s="8" customFormat="1">
       <c r="C118"/>
       <c r="D118" s="2"/>
       <c r="I118"/>
       <c r="J118"/>
       <c r="M118"/>
     </row>
-    <row r="119" spans="3:13" s="8" customFormat="1">
+    <row r="119" spans="2:27" s="8" customFormat="1">
       <c r="C119"/>
       <c r="D119" s="2"/>
       <c r="I119"/>
       <c r="J119"/>
       <c r="M119"/>
     </row>
-    <row r="120" spans="3:13" s="8" customFormat="1">
+    <row r="120" spans="2:27" s="8" customFormat="1">
       <c r="C120"/>
       <c r="D120" s="2"/>
       <c r="I120"/>
       <c r="J120"/>
       <c r="M120"/>
     </row>
-    <row r="121" spans="3:13" s="8" customFormat="1">
+    <row r="121" spans="2:27" s="8" customFormat="1">
       <c r="C121"/>
       <c r="D121" s="2"/>
       <c r="I121"/>
       <c r="J121"/>
       <c r="M121"/>
     </row>
-    <row r="122" spans="3:13" s="8" customFormat="1">
+    <row r="122" spans="2:27" s="8" customFormat="1">
       <c r="C122"/>
       <c r="D122" s="2"/>
       <c r="I122"/>
       <c r="J122"/>
       <c r="M122"/>
     </row>
-    <row r="123" spans="3:13" s="8" customFormat="1">
+    <row r="123" spans="2:27" s="8" customFormat="1">
       <c r="C123"/>
       <c r="D123" s="2"/>
       <c r="I123"/>
       <c r="J123"/>
       <c r="M123"/>
     </row>
-    <row r="124" spans="3:13" s="8" customFormat="1">
+    <row r="124" spans="2:27" s="8" customFormat="1">
       <c r="C124"/>
       <c r="D124" s="2"/>
       <c r="I124"/>
       <c r="J124"/>
       <c r="M124"/>
     </row>
-    <row r="125" spans="3:13" s="8" customFormat="1">
+    <row r="125" spans="2:27" s="8" customFormat="1">
       <c r="C125"/>
       <c r="D125" s="2"/>
       <c r="I125"/>
       <c r="J125"/>
       <c r="M125"/>
     </row>
-    <row r="126" spans="3:13" s="8" customFormat="1">
+    <row r="126" spans="2:27" s="8" customFormat="1">
       <c r="C126"/>
       <c r="D126" s="2"/>
       <c r="I126"/>
       <c r="J126"/>
       <c r="M126"/>
     </row>
-    <row r="127" spans="3:13" s="8" customFormat="1">
+    <row r="127" spans="2:27" s="8" customFormat="1">
       <c r="C127"/>
       <c r="D127" s="2"/>
       <c r="I127"/>
       <c r="J127"/>
       <c r="M127"/>
     </row>
-    <row r="128" spans="3:13" s="8" customFormat="1">
+    <row r="128" spans="2:27" s="8" customFormat="1">
       <c r="C128"/>
       <c r="D128" s="2"/>
       <c r="I128"/>
@@ -8340,10 +8486,6 @@
     <row r="156" spans="3:13" s="8" customFormat="1">
       <c r="C156"/>
       <c r="D156" s="2"/>
-      <c r="E156"/>
-      <c r="F156"/>
-      <c r="G156"/>
-      <c r="H156"/>
       <c r="I156"/>
       <c r="J156"/>
       <c r="M156"/>
@@ -8351,10 +8493,6 @@
     <row r="157" spans="3:13" s="8" customFormat="1">
       <c r="C157"/>
       <c r="D157" s="2"/>
-      <c r="E157"/>
-      <c r="F157"/>
-      <c r="G157"/>
-      <c r="H157"/>
       <c r="I157"/>
       <c r="J157"/>
       <c r="M157"/>
@@ -8403,40 +8541,62 @@
       <c r="J161"/>
       <c r="M161"/>
     </row>
-    <row r="162" spans="3:14">
-      <c r="K162" s="8"/>
-      <c r="N162" s="8"/>
-    </row>
-    <row r="163" spans="3:14">
-      <c r="K163" s="8"/>
-      <c r="N163" s="8"/>
+    <row r="162" spans="3:14" s="8" customFormat="1">
+      <c r="C162"/>
+      <c r="D162" s="2"/>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162"/>
+      <c r="H162"/>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="M162"/>
+    </row>
+    <row r="163" spans="3:14" s="8" customFormat="1">
+      <c r="C163"/>
+      <c r="D163" s="2"/>
+      <c r="E163"/>
+      <c r="F163"/>
+      <c r="G163"/>
+      <c r="H163"/>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="M163"/>
+    </row>
+    <row r="164" spans="3:14">
+      <c r="K164" s="8"/>
+      <c r="N164" s="8"/>
+    </row>
+    <row r="165" spans="3:14">
+      <c r="K165" s="8"/>
+      <c r="N165" s="8"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:K96">
-    <sortCondition ref="B22:B96"/>
-    <sortCondition ref="C22:C96"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:K98">
+    <sortCondition ref="B22:B98"/>
+    <sortCondition ref="C22:C98"/>
   </sortState>
-  <conditionalFormatting sqref="E22:E53 E62:E70">
+  <conditionalFormatting sqref="E63:E72 E22:E54">
     <cfRule type="expression" dxfId="13" priority="7">
       <formula>G22&lt;=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E85 E87:E89">
+  <conditionalFormatting sqref="E78:E87 E89:E91">
     <cfRule type="expression" dxfId="12" priority="13">
-      <formula>G76&lt;=0</formula>
+      <formula>G78&lt;=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E92:E99">
+  <conditionalFormatting sqref="E94:E101">
     <cfRule type="expression" dxfId="11" priority="4">
-      <formula>G92&lt;=0</formula>
+      <formula>G94&lt;=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E107">
+  <conditionalFormatting sqref="E109">
     <cfRule type="expression" dxfId="10" priority="3">
-      <formula>G107&lt;=0</formula>
+      <formula>G109&lt;=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G53 G62:G70">
+  <conditionalFormatting sqref="G63:G72 G22:G54">
     <cfRule type="cellIs" dxfId="9" priority="8" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -8444,7 +8604,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G76:G85 G87:G89">
+  <conditionalFormatting sqref="G78:G87 G89:G91">
     <cfRule type="cellIs" dxfId="7" priority="17" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -8452,7 +8612,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G92:G99">
+  <conditionalFormatting sqref="G94:G101">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -8460,7 +8620,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G107">
+  <conditionalFormatting sqref="G109">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -9857,7 +10017,7 @@
       </c>
       <c r="G12" s="56">
         <f>SUM(E14:E17)</f>
-        <v>45023160</v>
+        <v>45037200</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -9865,7 +10025,7 @@
         <v>25</v>
       </c>
       <c r="E14" s="8">
-        <f>+'INGRESOS-EGRESOS'!G19+'INGRESOS-EGRESOS'!G60+'INGRESOS-EGRESOS'!G74+'INGRESOS-EGRESOS'!G90</f>
+        <f>+'INGRESOS-EGRESOS'!G19+'INGRESOS-EGRESOS'!G61+'INGRESOS-EGRESOS'!G76+'INGRESOS-EGRESOS'!G92</f>
         <v>27440000</v>
       </c>
     </row>
@@ -9888,8 +10048,8 @@
         <v>45</v>
       </c>
       <c r="E17" s="8">
-        <f>+'INGRESOS-EGRESOS'!G105</f>
-        <v>6023160</v>
+        <f>+'INGRESOS-EGRESOS'!G107</f>
+        <v>6037200</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -9898,7 +10058,7 @@
       </c>
       <c r="G19" s="56">
         <f>SUM(D21:D24)</f>
-        <v>77980000</v>
+        <v>78160000</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -9907,7 +10067,7 @@
       </c>
       <c r="D21" s="8">
         <f>+ESCUELITAS!F9-ESCUELITAS!H9</f>
-        <v>76780000</v>
+        <v>76960000</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -9935,7 +10095,7 @@
       </c>
       <c r="G26" s="56">
         <f>SUM(D27:D32)</f>
-        <v>67177160</v>
+        <v>67591200</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -9943,8 +10103,8 @@
         <v>25</v>
       </c>
       <c r="D27" s="8">
-        <f>+'INGRESOS-EGRESOS'!E19+'INGRESOS-EGRESOS'!E60+'INGRESOS-EGRESOS'!E74+'INGRESOS-EGRESOS'!E90</f>
-        <v>44644000</v>
+        <f>+'INGRESOS-EGRESOS'!E19+'INGRESOS-EGRESOS'!E61+'INGRESOS-EGRESOS'!E76+'INGRESOS-EGRESOS'!E92</f>
+        <v>45044000</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -9987,8 +10147,8 @@
         <v>45</v>
       </c>
       <c r="D32" s="8">
-        <f>+'INGRESOS-EGRESOS'!E105</f>
-        <v>6023160</v>
+        <f>+'INGRESOS-EGRESOS'!E107</f>
+        <v>6037200</v>
       </c>
     </row>
   </sheetData>

--- a/TORNEO-2026.xlsx
+++ b/TORNEO-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Mundialito-WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86823327-EFA2-455D-8A5B-783DCE6249CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7CAF70-72A1-4BFB-B504-7FAE95398CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="927" xr2:uid="{5D8C40F9-B180-4AD9-A109-1285E937C9AC}"/>
   </bookViews>
@@ -66,7 +66,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>javif:</t>
         </r>
@@ -75,7 +75,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 260.000+400.000
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="275">
   <si>
     <t>Escuela de Futbol</t>
   </si>
@@ -909,9 +909,6 @@
     <t>CAMILA</t>
   </si>
   <si>
-    <t>AGUSRTINA</t>
-  </si>
-  <si>
     <t>LAUTI</t>
   </si>
   <si>
@@ -943,6 +940,9 @@
   </si>
   <si>
     <t>BRAIAN</t>
+  </si>
+  <si>
+    <t>AGUSTINA</t>
   </si>
 </sst>
 </file>
@@ -954,7 +954,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -991,12 +991,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1004,6 +1006,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1012,6 +1015,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1019,17 +1023,20 @@
       <u/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1043,6 +1050,7 @@
       <sz val="22"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1050,20 +1058,14 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2552,7 +2554,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5793D5D-C0F4-4F64-9D5A-A8B352024822}">
   <dimension ref="A1:AB60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="5.19921875" customWidth="1"/>
@@ -2575,7 +2577,7 @@
     <col min="24" max="24" width="19.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" hidden="1">
+    <row r="1" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>113</v>
       </c>
@@ -2584,15 +2586,15 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
     </row>
-    <row r="2" spans="1:28" hidden="1">
+    <row r="2" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
     </row>
-    <row r="3" spans="1:28" hidden="1">
+    <row r="3" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:28" hidden="1">
+    <row r="4" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>19</v>
       </c>
@@ -2607,13 +2609,13 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:28" hidden="1">
+    <row r="5" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>181</v>
       </c>
       <c r="F5" s="161">
         <f>+F10</f>
-        <v>89640000</v>
+        <v>89820000</v>
       </c>
       <c r="H5" s="162">
         <f>-H10</f>
@@ -2623,11 +2625,11 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:28" hidden="1">
+    <row r="6" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:28" hidden="1">
+    <row r="7" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="F7" s="162"/>
       <c r="G7" s="162"/>
       <c r="I7" s="4"/>
@@ -2650,7 +2652,7 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F8" s="162"/>
       <c r="G8" s="162"/>
       <c r="H8" s="3">
@@ -2674,7 +2676,7 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
     </row>
-    <row r="9" spans="1:28" ht="25.8" customHeight="1">
+    <row r="9" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="19" t="s">
         <v>227</v>
       </c>
@@ -2683,7 +2685,7 @@
       </c>
       <c r="E9" s="3">
         <f>+E10+37</f>
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="F9" s="162"/>
       <c r="G9" s="162"/>
@@ -2708,7 +2710,7 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
     </row>
-    <row r="10" spans="1:28" s="19" customFormat="1" ht="14.4" thickBot="1">
+    <row r="10" spans="1:28" s="19" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="28"/>
       <c r="C10" s="19" t="s">
@@ -2716,15 +2718,15 @@
       </c>
       <c r="D10" s="179">
         <f t="shared" ref="D10:P10" si="0">SUM(D13:D46)</f>
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="E10" s="22">
         <f t="shared" si="0"/>
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="F10" s="60">
         <f t="shared" si="0"/>
-        <v>89640000</v>
+        <v>89820000</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
@@ -2760,15 +2762,15 @@
       </c>
       <c r="O10" s="28">
         <f t="shared" si="0"/>
-        <v>100550000</v>
+        <v>100730000</v>
       </c>
       <c r="P10" s="28">
         <f t="shared" si="0"/>
-        <v>29990000</v>
+        <v>22170000</v>
       </c>
       <c r="Q10" s="28"/>
     </row>
-    <row r="11" spans="1:28" s="19" customFormat="1" ht="59.4" customHeight="1" thickBot="1">
+    <row r="11" spans="1:28" s="19" customFormat="1" ht="59.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25"/>
       <c r="B11" s="28"/>
       <c r="C11" s="20" t="s">
@@ -2825,7 +2827,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -2896,7 +2898,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="43">
         <v>1</v>
       </c>
@@ -2937,7 +2939,7 @@
       <c r="X13" s="30"/>
       <c r="Z13" s="8">
         <f>+SUMIFS(Q13:Q46,R13:R46,Z11)+SUMIFS(S13:S46,T13:T46,Z11)+SUMIFS(U13:U46,V13:V46,Z11)+SUMIFS(W13:W46,X13:X46,Z11)</f>
-        <v>29140000</v>
+        <v>37140000</v>
       </c>
       <c r="AA13" s="8">
         <f>+SUMIFS(Q13:Q46,R13:R46,AA11)+SUMIFS(S13:S46,T13:T46,AA11)+SUMIFS(U13:U46,V13:V46,AA11)+SUMIFS(W13:W46,X13:X46,AA11)</f>
@@ -2948,7 +2950,7 @@
         <v>5080000</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="43">
         <f>+A13+1</f>
         <v>2</v>
@@ -2992,7 +2994,7 @@
       <c r="W14" s="154"/>
       <c r="X14" s="30"/>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="43">
         <f t="shared" ref="A15:A46" si="1">+A14+1</f>
         <v>3</v>
@@ -3063,7 +3065,7 @@
       <c r="X15" s="31"/>
       <c r="Y15" s="23"/>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -3129,7 +3131,7 @@
       <c r="X16" s="30"/>
       <c r="Y16" s="23"/>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -3194,7 +3196,7 @@
       <c r="X17" s="31"/>
       <c r="Y17" s="23"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -3263,7 +3265,7 @@
       <c r="X18" s="31"/>
       <c r="Y18" s="23"/>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -3335,7 +3337,7 @@
       <c r="X19" s="31"/>
       <c r="Y19" s="23"/>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -3400,7 +3402,7 @@
       <c r="X20" s="30"/>
       <c r="Y20" s="23"/>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="43">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -3470,7 +3472,7 @@
       <c r="X21" s="30"/>
       <c r="Y21" s="23"/>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="43">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -3483,14 +3485,14 @@
       </c>
       <c r="D22" s="49">
         <f t="shared" si="3"/>
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E22" s="202">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F22" s="66">
         <f>+E22*Precios!$C$5</f>
-        <v>8460000</v>
+        <v>8640000</v>
       </c>
       <c r="G22" s="49"/>
       <c r="H22" s="90"/>
@@ -3513,16 +3515,18 @@
       </c>
       <c r="O22" s="177">
         <f t="shared" si="2"/>
-        <v>8460000</v>
+        <v>8640000</v>
       </c>
       <c r="P22" s="167">
         <f t="shared" si="4"/>
-        <v>8460000</v>
+        <v>640000</v>
       </c>
       <c r="Q22" s="52">
-        <v>0</v>
-      </c>
-      <c r="R22" s="48"/>
+        <v>8000000</v>
+      </c>
+      <c r="R22" s="48" t="s">
+        <v>16</v>
+      </c>
       <c r="S22" s="47">
         <v>0</v>
       </c>
@@ -3535,7 +3539,7 @@
       <c r="X22" s="31"/>
       <c r="Y22" s="23"/>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="43">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -3604,7 +3608,7 @@
       <c r="X23" s="31"/>
       <c r="Y23" s="23"/>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -3678,7 +3682,7 @@
       <c r="X24" s="31"/>
       <c r="Y24" s="23"/>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="43">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -3746,7 +3750,7 @@
       <c r="X25" s="31"/>
       <c r="Y25" s="23"/>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="43">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -3813,7 +3817,7 @@
       <c r="X26" s="31"/>
       <c r="Y26" s="23"/>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="43">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -3883,7 +3887,7 @@
       <c r="X27" s="31"/>
       <c r="Y27" s="23"/>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="43">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -3950,7 +3954,7 @@
       <c r="X28" s="31"/>
       <c r="Y28" s="23"/>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="43">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -4020,7 +4024,7 @@
       <c r="X29" s="31"/>
       <c r="Y29" s="23"/>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -4088,7 +4092,7 @@
       <c r="X30" s="31"/>
       <c r="Y30" s="23"/>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="43">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -4155,7 +4159,7 @@
       <c r="X31" s="31"/>
       <c r="Y31" s="23"/>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="43">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -4222,7 +4226,7 @@
       <c r="X32" s="31"/>
       <c r="Y32" s="23"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="43">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -4285,7 +4289,7 @@
       <c r="X33" s="31"/>
       <c r="Y33" s="23"/>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="e">
         <f>+#REF!+1</f>
         <v>#REF!</v>
@@ -4354,7 +4358,7 @@
       <c r="X34" s="31"/>
       <c r="Y34" s="23"/>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4424,7 +4428,7 @@
       <c r="X35" s="31"/>
       <c r="Y35" s="23"/>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4493,7 +4497,7 @@
       <c r="X36" s="31"/>
       <c r="Y36" s="23"/>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4562,7 +4566,7 @@
       <c r="X37" s="31"/>
       <c r="Y37" s="23"/>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4627,7 +4631,7 @@
       <c r="X38" s="31"/>
       <c r="Y38" s="23"/>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4690,7 +4694,7 @@
       <c r="X39" s="31"/>
       <c r="Y39" s="23"/>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4759,7 +4763,7 @@
       <c r="X40" s="31"/>
       <c r="Y40" s="23"/>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4831,7 +4835,7 @@
       <c r="X41" s="31"/>
       <c r="Y41" s="23"/>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4900,7 +4904,7 @@
       <c r="X42" s="31"/>
       <c r="Y42" s="23"/>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -4965,7 +4969,7 @@
       <c r="X43" s="31"/>
       <c r="Y43" s="23"/>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -5037,7 +5041,7 @@
       <c r="X44" s="31"/>
       <c r="Y44" s="23"/>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -5098,7 +5102,7 @@
       <c r="X45" s="31"/>
       <c r="Y45" s="23"/>
     </row>
-    <row r="46" spans="1:25" ht="14.4" thickBot="1">
+    <row r="46" spans="1:25" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="43" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
@@ -5167,35 +5171,35 @@
       <c r="X46" s="32"/>
       <c r="Y46" s="23"/>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
     </row>
-    <row r="49" spans="6:16">
+    <row r="49" spans="6:16" x14ac:dyDescent="0.25">
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
     </row>
-    <row r="50" spans="6:16">
+    <row r="50" spans="6:16" x14ac:dyDescent="0.25">
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
     </row>
-    <row r="51" spans="6:16">
+    <row r="51" spans="6:16" x14ac:dyDescent="0.25">
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
     </row>
-    <row r="52" spans="6:16">
+    <row r="52" spans="6:16" x14ac:dyDescent="0.25">
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
     </row>
-    <row r="53" spans="6:16">
+    <row r="53" spans="6:16" x14ac:dyDescent="0.25">
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
     </row>
-    <row r="54" spans="6:16">
+    <row r="54" spans="6:16" x14ac:dyDescent="0.25">
       <c r="G54" s="3" t="s">
         <v>111</v>
       </c>
@@ -5208,28 +5212,28 @@
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
     </row>
-    <row r="55" spans="6:16">
+    <row r="55" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G55" s="161">
         <f>+F10-H10</f>
-        <v>87970000</v>
+        <v>88150000</v>
       </c>
       <c r="H55" s="161">
         <f>+P10-H56</f>
-        <v>17410000</v>
+        <v>9590000</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="8">
         <f>+G55-H55</f>
-        <v>70560000</v>
+        <v>78560000</v>
       </c>
       <c r="K55" s="8"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
     </row>
-    <row r="56" spans="6:16">
+    <row r="56" spans="6:16" x14ac:dyDescent="0.25">
       <c r="F56" s="3" t="s">
         <v>19</v>
       </c>
@@ -5250,7 +5254,7 @@
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
     </row>
-    <row r="60" spans="6:16">
+    <row r="60" spans="6:16" x14ac:dyDescent="0.25">
       <c r="H60" s="161"/>
     </row>
   </sheetData>
@@ -5284,13 +5288,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A986A5C-F164-46CB-A573-6A1253400527}">
   <dimension ref="A2:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.19921875" customWidth="1"/>
     <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>25</v>
       </c>
@@ -5304,17 +5308,17 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>166</v>
       </c>
@@ -5327,14 +5331,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA77DD3B-4609-4DA1-90BE-1F7CDFE5DF1B}">
   <dimension ref="B3:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.296875" customWidth="1"/>
     <col min="3" max="3" width="15.796875" customWidth="1"/>
     <col min="4" max="4" width="16.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -5348,10 +5352,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C4" s="8">
         <f>+ESCUELITAS!Z13+DUPLEX!O11</f>
-        <v>29190000</v>
+        <v>37190000</v>
       </c>
       <c r="D4" s="8">
         <f>+'INGRESOS-EGRESOS'!Q22+'NEGOCIADOS- EL NORTE'!N116</f>
@@ -5359,10 +5363,10 @@
       </c>
       <c r="E4" s="8">
         <f>+C4-D4</f>
-        <v>17341000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <v>25341000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -5376,7 +5380,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C9" s="8">
         <f>+ESCUELITAS!AA13+DUPLEX!P11</f>
         <v>18030000</v>
@@ -5390,7 +5394,7 @@
         <v>-1480000</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>45</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C16" s="8">
         <f>+ESCUELITAS!AB13+DUPLEX!Q11</f>
         <v>5080000</v>
@@ -5426,7 +5430,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF31B6B6-9E38-4245-9BA5-51FF3C7F9B06}">
   <dimension ref="A2:AB181"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" style="8"/>
     <col min="3" max="3" width="31.5" customWidth="1"/>
@@ -5440,7 +5444,7 @@
     <col min="13" max="13" width="18.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C2" s="21" t="s">
         <v>142</v>
       </c>
@@ -5453,7 +5457,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="3:10">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>29</v>
       </c>
@@ -5465,7 +5469,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="4" spans="3:10">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>30</v>
       </c>
@@ -5477,7 +5481,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="5" spans="3:10">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>31</v>
       </c>
@@ -5489,7 +5493,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="3:10">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" s="21" t="s">
         <v>143</v>
       </c>
@@ -5504,50 +5508,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:10">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="3:10">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="J11" s="146">
         <f>+H27+H65+H79+H82+H85+J82+J96+H96+H114</f>
         <v>1727500</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D12" s="57"/>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" s="23" t="s">
         <v>100</v>
       </c>
       <c r="D13" s="58"/>
     </row>
-    <row r="14" spans="3:10">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="3:10">
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="E19" s="101">
         <f>SUM(E22:E73)</f>
         <v>42184000</v>
@@ -5561,7 +5565,7 @@
         <v>8690000</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="14.4" thickBot="1">
+    <row r="20" spans="1:19" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="21" t="s">
         <v>145</v>
       </c>
@@ -5611,7 +5615,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C21" s="21" t="s">
         <v>25</v>
       </c>
@@ -5626,7 +5630,7 @@
       <c r="L21" s="69"/>
       <c r="M21" s="70"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B22" s="8">
         <v>1</v>
       </c>
@@ -5660,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>275000</v>
       </c>
@@ -5691,7 +5695,7 @@
       <c r="L23" s="69"/>
       <c r="M23" s="70"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>275000</v>
       </c>
@@ -5736,14 +5740,14 @@
       <c r="M24" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="8">
         <v>900000</v>
       </c>
       <c r="O24" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>280000</v>
       </c>
@@ -5774,7 +5778,7 @@
       <c r="L25" s="69"/>
       <c r="M25" s="70"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>70000</v>
       </c>
@@ -5806,7 +5810,7 @@
       <c r="L26" s="69"/>
       <c r="M26" s="70"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B27" s="8">
         <v>1</v>
       </c>
@@ -5838,7 +5842,7 @@
       <c r="L27" s="69"/>
       <c r="M27" s="70"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B28" s="8">
         <v>1</v>
       </c>
@@ -5867,7 +5871,7 @@
       <c r="L28" s="69"/>
       <c r="M28" s="70"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B29" s="8">
         <v>1</v>
       </c>
@@ -5895,7 +5899,7 @@
       <c r="L29" s="69"/>
       <c r="M29" s="70"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B30" s="8">
         <v>1</v>
       </c>
@@ -5917,7 +5921,7 @@
       <c r="L30" s="69"/>
       <c r="M30" s="70"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B31" s="8">
         <v>1</v>
       </c>
@@ -5941,7 +5945,7 @@
       <c r="L31" s="69"/>
       <c r="M31" s="70"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>100000</v>
       </c>
@@ -5972,7 +5976,7 @@
       <c r="L32" s="69"/>
       <c r="M32" s="70"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B33" s="8">
         <v>1</v>
       </c>
@@ -5995,7 +5999,7 @@
       <c r="L33" s="69"/>
       <c r="M33" s="70"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B34" s="8">
         <v>1</v>
       </c>
@@ -6024,7 +6028,7 @@
       <c r="L34" s="69"/>
       <c r="M34" s="70"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B35" s="8">
         <v>1</v>
       </c>
@@ -6052,7 +6056,7 @@
       <c r="L35" s="69"/>
       <c r="M35" s="70"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B36" s="8">
         <v>1</v>
       </c>
@@ -6080,7 +6084,7 @@
       <c r="L36" s="69"/>
       <c r="M36" s="70"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B37" s="8">
         <v>1</v>
       </c>
@@ -6108,7 +6112,7 @@
       <c r="L37" s="69"/>
       <c r="M37" s="70"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B38" s="8">
         <v>1</v>
       </c>
@@ -6136,7 +6140,7 @@
       <c r="L38" s="69"/>
       <c r="M38" s="70"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B39" s="8">
         <v>1</v>
       </c>
@@ -6160,7 +6164,7 @@
       <c r="L39" s="69"/>
       <c r="M39" s="70"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B40" s="8">
         <v>1</v>
       </c>
@@ -6188,7 +6192,7 @@
       <c r="L40" s="69"/>
       <c r="M40" s="70"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B41" s="8">
         <v>1</v>
       </c>
@@ -6213,7 +6217,7 @@
       <c r="L41" s="69"/>
       <c r="M41" s="70"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B42" s="8">
         <v>1</v>
       </c>
@@ -6238,7 +6242,7 @@
       <c r="L42" s="69"/>
       <c r="M42" s="70"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B43" s="8">
         <v>1</v>
       </c>
@@ -6262,7 +6266,7 @@
       <c r="L43" s="69"/>
       <c r="M43" s="70"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B44" s="8">
         <v>1</v>
       </c>
@@ -6287,7 +6291,7 @@
       <c r="L44" s="69"/>
       <c r="M44" s="70"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B45" s="8">
         <v>1</v>
       </c>
@@ -6312,7 +6316,7 @@
       <c r="L45" s="69"/>
       <c r="M45" s="70"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B46" s="8">
         <v>1</v>
       </c>
@@ -6337,7 +6341,7 @@
       <c r="L46" s="69"/>
       <c r="M46" s="70"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -6356,7 +6360,10 @@
       <c r="L47" s="69"/>
       <c r="M47" s="70"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>260</v>
+      </c>
       <c r="C48" t="s">
         <v>262</v>
       </c>
@@ -6372,9 +6379,12 @@
       <c r="L48" s="69"/>
       <c r="M48" s="70"/>
     </row>
-    <row r="49" spans="2:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>260</v>
+      </c>
       <c r="C49" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E49" s="8">
         <v>200000</v>
@@ -6388,9 +6398,12 @@
       <c r="L49" s="69"/>
       <c r="M49" s="70"/>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>260</v>
+      </c>
       <c r="C50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E50" s="8">
         <v>200000</v>
@@ -6404,9 +6417,12 @@
       <c r="L50" s="69"/>
       <c r="M50" s="70"/>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>260</v>
+      </c>
       <c r="C51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E51" s="8">
         <v>200000</v>
@@ -6420,9 +6436,12 @@
       <c r="L51" s="69"/>
       <c r="M51" s="70"/>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>260</v>
+      </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E52" s="8">
         <v>200000</v>
@@ -6436,9 +6455,12 @@
       <c r="L52" s="69"/>
       <c r="M52" s="70"/>
     </row>
-    <row r="53" spans="2:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>260</v>
+      </c>
       <c r="C53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E53" s="8">
         <v>200000</v>
@@ -6452,9 +6474,12 @@
       <c r="L53" s="69"/>
       <c r="M53" s="70"/>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>260</v>
+      </c>
       <c r="C54" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E54" s="8">
         <v>200000</v>
@@ -6468,9 +6493,12 @@
       <c r="L54" s="69"/>
       <c r="M54" s="70"/>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>260</v>
+      </c>
       <c r="C55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E55" s="8">
         <v>200000</v>
@@ -6484,9 +6512,12 @@
       <c r="L55" s="69"/>
       <c r="M55" s="70"/>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>260</v>
+      </c>
       <c r="C56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E56" s="8">
         <v>200000</v>
@@ -6500,9 +6531,12 @@
       <c r="L56" s="69"/>
       <c r="M56" s="70"/>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>260</v>
+      </c>
       <c r="C57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E57" s="8">
         <v>200000</v>
@@ -6516,9 +6550,9 @@
       <c r="L57" s="69"/>
       <c r="M57" s="70"/>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E58" s="8">
         <v>200000</v>
@@ -6532,9 +6566,9 @@
       <c r="L58" s="69"/>
       <c r="M58" s="70"/>
     </row>
-    <row r="59" spans="2:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E59" s="8">
         <v>200000</v>
@@ -6548,9 +6582,9 @@
       <c r="L59" s="69"/>
       <c r="M59" s="70"/>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E60" s="8">
         <v>200000</v>
@@ -6564,7 +6598,7 @@
       <c r="L60" s="69"/>
       <c r="M60" s="70"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
@@ -6575,7 +6609,7 @@
       <c r="L61" s="69"/>
       <c r="M61" s="70"/>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
@@ -6586,7 +6620,7 @@
       <c r="L62" s="69"/>
       <c r="M62" s="70"/>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B63" s="8">
         <v>1</v>
       </c>
@@ -6614,7 +6648,7 @@
       <c r="L63" s="69"/>
       <c r="M63" s="70"/>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B64" s="8">
         <v>1</v>
       </c>
@@ -6636,7 +6670,7 @@
       <c r="L64" s="69"/>
       <c r="M64" s="70"/>
     </row>
-    <row r="65" spans="2:27">
+    <row r="65" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B65" s="8">
         <v>1</v>
       </c>
@@ -6664,7 +6698,7 @@
       <c r="L65" s="69"/>
       <c r="M65" s="70"/>
     </row>
-    <row r="66" spans="2:27" s="8" customFormat="1">
+    <row r="66" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="8">
         <v>1</v>
       </c>
@@ -6687,7 +6721,7 @@
       <c r="M66" s="70"/>
       <c r="N66"/>
     </row>
-    <row r="67" spans="2:27" s="8" customFormat="1">
+    <row r="67" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="8">
         <v>1</v>
       </c>
@@ -6722,7 +6756,7 @@
       <c r="M67" s="70"/>
       <c r="N67"/>
     </row>
-    <row r="68" spans="2:27" s="8" customFormat="1">
+    <row r="68" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="8">
         <v>1</v>
       </c>
@@ -6743,7 +6777,7 @@
       <c r="L68" s="69"/>
       <c r="M68" s="70"/>
     </row>
-    <row r="69" spans="2:27" s="8" customFormat="1">
+    <row r="69" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="8">
         <v>1</v>
       </c>
@@ -6764,7 +6798,7 @@
       <c r="L69" s="69"/>
       <c r="M69" s="70"/>
     </row>
-    <row r="70" spans="2:27" s="8" customFormat="1">
+    <row r="70" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="8">
         <v>1</v>
       </c>
@@ -6785,21 +6819,21 @@
       <c r="L70" s="69"/>
       <c r="M70" s="70"/>
     </row>
-    <row r="71" spans="2:27" s="8" customFormat="1">
+    <row r="71" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C71"/>
       <c r="D71" s="2"/>
       <c r="I71"/>
       <c r="J71"/>
       <c r="M71"/>
     </row>
-    <row r="72" spans="2:27" s="8" customFormat="1">
+    <row r="72" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C72"/>
       <c r="D72" s="2"/>
       <c r="I72"/>
       <c r="J72"/>
       <c r="M72"/>
     </row>
-    <row r="73" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="73" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="169"/>
       <c r="C73" s="170"/>
       <c r="D73" s="171"/>
@@ -6827,28 +6861,28 @@
       <c r="Z73" s="169"/>
       <c r="AA73" s="169"/>
     </row>
-    <row r="74" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
+    <row r="74" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C74"/>
       <c r="D74" s="2"/>
       <c r="I74"/>
       <c r="J74"/>
       <c r="M74"/>
     </row>
-    <row r="75" spans="2:27" s="8" customFormat="1">
+    <row r="75" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C75"/>
       <c r="D75" s="2"/>
       <c r="I75"/>
       <c r="J75"/>
       <c r="M75"/>
     </row>
-    <row r="76" spans="2:27" s="8" customFormat="1">
+    <row r="76" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C76"/>
       <c r="D76" s="2"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="M76"/>
     </row>
-    <row r="77" spans="2:27" s="8" customFormat="1">
+    <row r="77" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C77"/>
       <c r="D77" s="2"/>
       <c r="E77" s="101">
@@ -6867,7 +6901,7 @@
       <c r="J77"/>
       <c r="M77"/>
     </row>
-    <row r="78" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="78" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C78" s="21" t="s">
         <v>151</v>
       </c>
@@ -6900,7 +6934,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="2:27" s="8" customFormat="1">
+    <row r="79" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="8">
         <v>2</v>
       </c>
@@ -6928,7 +6962,7 @@
       <c r="L79" s="69"/>
       <c r="M79" s="70"/>
     </row>
-    <row r="80" spans="2:27" s="8" customFormat="1">
+    <row r="80" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="8">
         <v>2</v>
       </c>
@@ -6956,7 +6990,7 @@
       <c r="L80" s="69"/>
       <c r="M80" s="70"/>
     </row>
-    <row r="81" spans="2:28" s="8" customFormat="1">
+    <row r="81" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="8">
         <v>2</v>
       </c>
@@ -6984,7 +7018,7 @@
       <c r="L81" s="69"/>
       <c r="M81" s="70"/>
     </row>
-    <row r="82" spans="2:28" s="8" customFormat="1">
+    <row r="82" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="8">
         <v>2</v>
       </c>
@@ -7018,7 +7052,7 @@
       <c r="L82" s="69"/>
       <c r="M82" s="70"/>
     </row>
-    <row r="83" spans="2:28" s="8" customFormat="1">
+    <row r="83" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="8">
         <v>2</v>
       </c>
@@ -7044,7 +7078,7 @@
       <c r="L83" s="69"/>
       <c r="M83" s="70"/>
     </row>
-    <row r="84" spans="2:28" s="8" customFormat="1">
+    <row r="84" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="8">
         <v>2</v>
       </c>
@@ -7074,7 +7108,7 @@
       <c r="L84" s="69"/>
       <c r="M84" s="70"/>
     </row>
-    <row r="85" spans="2:28">
+    <row r="85" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B85" s="8">
         <v>2</v>
       </c>
@@ -7101,25 +7135,25 @@
       <c r="L85" s="69"/>
       <c r="M85" s="70"/>
     </row>
-    <row r="86" spans="2:28">
+    <row r="86" spans="2:28" x14ac:dyDescent="0.25">
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="2:28">
+    <row r="87" spans="2:28" x14ac:dyDescent="0.25">
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="2:28">
+    <row r="88" spans="2:28" x14ac:dyDescent="0.25">
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="2:28" ht="14.4" thickBot="1">
+    <row r="89" spans="2:28" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="169"/>
       <c r="C89" s="170"/>
       <c r="D89" s="171"/>
@@ -7148,7 +7182,7 @@
       <c r="AA89" s="169"/>
       <c r="AB89" s="8"/>
     </row>
-    <row r="90" spans="2:28" s="8" customFormat="1" ht="14.4" thickTop="1">
+    <row r="90" spans="2:28" s="8" customFormat="1" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C90"/>
       <c r="D90" s="2"/>
       <c r="I90" s="1"/>
@@ -7156,7 +7190,7 @@
       <c r="K90"/>
       <c r="M90"/>
     </row>
-    <row r="91" spans="2:28" s="8" customFormat="1">
+    <row r="91" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C91"/>
       <c r="D91" s="2"/>
       <c r="I91" s="1"/>
@@ -7164,7 +7198,7 @@
       <c r="K91"/>
       <c r="M91"/>
     </row>
-    <row r="92" spans="2:28" s="8" customFormat="1">
+    <row r="92" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C92"/>
       <c r="D92" s="2"/>
       <c r="E92" s="101">
@@ -7184,7 +7218,7 @@
       <c r="K92"/>
       <c r="M92"/>
     </row>
-    <row r="93" spans="2:28" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="93" spans="2:28" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C93" s="21" t="s">
         <v>8</v>
       </c>
@@ -7217,7 +7251,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="94" spans="2:28" s="8" customFormat="1">
+    <row r="94" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="8">
         <v>3</v>
       </c>
@@ -7251,7 +7285,7 @@
       <c r="L94" s="69"/>
       <c r="M94" s="70"/>
     </row>
-    <row r="95" spans="2:28" s="8" customFormat="1">
+    <row r="95" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="8">
         <v>3</v>
       </c>
@@ -7277,7 +7311,7 @@
       <c r="L95" s="69"/>
       <c r="M95" s="70"/>
     </row>
-    <row r="96" spans="2:28" s="8" customFormat="1">
+    <row r="96" spans="2:28" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="8">
         <v>3</v>
       </c>
@@ -7316,7 +7350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="2:27" s="8" customFormat="1">
+    <row r="97" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="8">
         <v>3</v>
       </c>
@@ -7339,7 +7373,7 @@
       <c r="L97" s="69"/>
       <c r="M97" s="71"/>
     </row>
-    <row r="98" spans="2:27" s="8" customFormat="1">
+    <row r="98" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="8">
         <v>3</v>
       </c>
@@ -7370,7 +7404,7 @@
       <c r="L98" s="69"/>
       <c r="M98" s="70"/>
     </row>
-    <row r="99" spans="2:27" s="8" customFormat="1">
+    <row r="99" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="8">
         <v>3</v>
       </c>
@@ -7393,7 +7427,7 @@
       <c r="L99" s="69"/>
       <c r="M99" s="71"/>
     </row>
-    <row r="100" spans="2:27" s="8" customFormat="1">
+    <row r="100" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="8">
         <v>3</v>
       </c>
@@ -7416,7 +7450,7 @@
       <c r="L100" s="69"/>
       <c r="M100" s="71"/>
     </row>
-    <row r="101" spans="2:27" s="8" customFormat="1">
+    <row r="101" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="8">
         <v>3</v>
       </c>
@@ -7442,21 +7476,21 @@
       <c r="L101" s="69"/>
       <c r="M101" s="70"/>
     </row>
-    <row r="102" spans="2:27" s="8" customFormat="1">
+    <row r="102" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C102"/>
       <c r="D102" s="2"/>
       <c r="I102"/>
       <c r="K102"/>
       <c r="M102"/>
     </row>
-    <row r="103" spans="2:27" s="8" customFormat="1">
+    <row r="103" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C103"/>
       <c r="D103" s="2"/>
       <c r="I103"/>
       <c r="K103"/>
       <c r="M103"/>
     </row>
-    <row r="104" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="104" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="169"/>
       <c r="C104" s="170"/>
       <c r="D104" s="171"/>
@@ -7484,28 +7518,28 @@
       <c r="Z104" s="169"/>
       <c r="AA104" s="169"/>
     </row>
-    <row r="105" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
+    <row r="105" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C105"/>
       <c r="D105" s="2"/>
       <c r="I105"/>
       <c r="K105"/>
       <c r="M105"/>
     </row>
-    <row r="106" spans="2:27" s="8" customFormat="1">
+    <row r="106" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C106"/>
       <c r="D106" s="2"/>
       <c r="I106"/>
       <c r="K106"/>
       <c r="M106"/>
     </row>
-    <row r="107" spans="2:27" s="8" customFormat="1">
+    <row r="107" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C107"/>
       <c r="D107" s="2"/>
       <c r="I107"/>
       <c r="K107"/>
       <c r="M107"/>
     </row>
-    <row r="108" spans="2:27" s="8" customFormat="1">
+    <row r="108" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C108"/>
       <c r="D108" s="2"/>
       <c r="E108" s="101">
@@ -7525,7 +7559,7 @@
       <c r="K108"/>
       <c r="M108"/>
     </row>
-    <row r="109" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="109" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C109" s="21" t="s">
         <v>152</v>
       </c>
@@ -7558,7 +7592,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="110" spans="2:27" s="8" customFormat="1">
+    <row r="110" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B110" s="8">
         <v>4</v>
       </c>
@@ -7581,7 +7615,7 @@
       <c r="L110" s="69"/>
       <c r="M110" s="70"/>
     </row>
-    <row r="111" spans="2:27" s="8" customFormat="1">
+    <row r="111" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B111" s="8">
         <v>4</v>
       </c>
@@ -7603,7 +7637,7 @@
       <c r="L111" s="69"/>
       <c r="M111" s="70"/>
     </row>
-    <row r="112" spans="2:27" s="8" customFormat="1">
+    <row r="112" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="8">
         <v>4</v>
       </c>
@@ -7625,7 +7659,7 @@
       <c r="L112" s="69"/>
       <c r="M112" s="70"/>
     </row>
-    <row r="113" spans="2:27" s="8" customFormat="1">
+    <row r="113" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B113" s="8">
         <v>4</v>
       </c>
@@ -7659,7 +7693,7 @@
       <c r="L113" s="69"/>
       <c r="M113" s="70"/>
     </row>
-    <row r="114" spans="2:27" s="8" customFormat="1">
+    <row r="114" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B114" s="8">
         <v>4</v>
       </c>
@@ -7688,7 +7722,7 @@
       <c r="L114" s="69"/>
       <c r="M114" s="70"/>
     </row>
-    <row r="115" spans="2:27" s="8" customFormat="1">
+    <row r="115" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B115" s="8">
         <v>4</v>
       </c>
@@ -7710,28 +7744,28 @@
       <c r="L115" s="69"/>
       <c r="M115" s="70"/>
     </row>
-    <row r="116" spans="2:27" s="8" customFormat="1">
+    <row r="116" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C116"/>
       <c r="D116" s="2"/>
       <c r="I116"/>
       <c r="J116"/>
       <c r="M116"/>
     </row>
-    <row r="117" spans="2:27" s="8" customFormat="1">
+    <row r="117" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C117"/>
       <c r="D117" s="2"/>
       <c r="I117"/>
       <c r="J117"/>
       <c r="M117"/>
     </row>
-    <row r="118" spans="2:27" s="8" customFormat="1">
+    <row r="118" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C118"/>
       <c r="D118" s="2"/>
       <c r="I118"/>
       <c r="J118"/>
       <c r="M118"/>
     </row>
-    <row r="119" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="119" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B119" s="169"/>
       <c r="C119" s="170"/>
       <c r="D119" s="171"/>
@@ -7759,33 +7793,33 @@
       <c r="Z119" s="169"/>
       <c r="AA119" s="169"/>
     </row>
-    <row r="120" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
+    <row r="120" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C120"/>
       <c r="D120" s="2"/>
       <c r="I120"/>
       <c r="J120"/>
       <c r="M120"/>
     </row>
-    <row r="121" spans="2:27" s="8" customFormat="1">
+    <row r="121" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C121"/>
       <c r="D121" s="2"/>
       <c r="I121"/>
       <c r="J121"/>
       <c r="M121"/>
     </row>
-    <row r="122" spans="2:27" s="8" customFormat="1">
+    <row r="122" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C122"/>
       <c r="D122" s="2"/>
       <c r="I122"/>
       <c r="J122"/>
       <c r="M122"/>
     </row>
-    <row r="123" spans="2:27" s="8" customFormat="1">
+    <row r="123" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C123"/>
       <c r="D123" s="2"/>
       <c r="E123" s="101">
         <f>SUM(E125:E129)</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="F123" s="101">
         <f t="shared" ref="F123:G123" si="26">SUM(F125:F129)</f>
@@ -7793,13 +7827,13 @@
       </c>
       <c r="G123" s="101">
         <f t="shared" si="26"/>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="I123"/>
       <c r="J123"/>
       <c r="M123"/>
     </row>
-    <row r="124" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1">
+    <row r="124" spans="2:27" s="8" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C124"/>
       <c r="D124" s="2"/>
       <c r="E124" s="73" t="s">
@@ -7830,7 +7864,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="125" spans="2:27">
+    <row r="125" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B125" s="8">
         <v>4680</v>
       </c>
@@ -7839,37 +7873,37 @@
       </c>
       <c r="D125" s="2">
         <f>+ESCUELITAS!E10</f>
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="E125" s="8">
         <f>+D125*B125</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="8">
         <f>+E125-F125</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="H125" s="69"/>
       <c r="I125" s="70"/>
       <c r="L125" s="69"/>
       <c r="M125" s="70"/>
     </row>
-    <row r="126" spans="2:27" s="8" customFormat="1">
+    <row r="126" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C126"/>
       <c r="D126" s="2"/>
       <c r="I126"/>
       <c r="J126"/>
       <c r="M126"/>
     </row>
-    <row r="127" spans="2:27" s="8" customFormat="1">
+    <row r="127" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C127"/>
       <c r="D127" s="2"/>
       <c r="I127"/>
       <c r="J127"/>
       <c r="M127"/>
     </row>
-    <row r="129" spans="2:27" ht="14.4" thickBot="1">
+    <row r="129" spans="2:27" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B129" s="169"/>
       <c r="C129" s="170"/>
       <c r="D129" s="171"/>
@@ -7897,21 +7931,21 @@
       <c r="Z129" s="169"/>
       <c r="AA129" s="169"/>
     </row>
-    <row r="130" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1">
+    <row r="130" spans="2:27" s="8" customFormat="1" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C130"/>
       <c r="D130" s="2"/>
       <c r="I130"/>
       <c r="J130"/>
       <c r="M130"/>
     </row>
-    <row r="131" spans="2:27" s="8" customFormat="1">
+    <row r="131" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C131"/>
       <c r="D131" s="2"/>
       <c r="I131"/>
       <c r="J131"/>
       <c r="M131"/>
     </row>
-    <row r="132" spans="2:27" s="8" customFormat="1">
+    <row r="132" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C132"/>
       <c r="D132" s="2"/>
       <c r="E132" s="56"/>
@@ -7922,294 +7956,294 @@
       <c r="J132" s="1"/>
       <c r="M132"/>
     </row>
-    <row r="133" spans="2:27" s="8" customFormat="1">
+    <row r="133" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C133"/>
       <c r="D133" s="2"/>
       <c r="I133"/>
       <c r="J133"/>
       <c r="M133"/>
     </row>
-    <row r="134" spans="2:27" s="8" customFormat="1">
+    <row r="134" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C134"/>
       <c r="D134" s="2"/>
       <c r="I134"/>
       <c r="J134"/>
       <c r="M134"/>
     </row>
-    <row r="135" spans="2:27" s="8" customFormat="1">
+    <row r="135" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C135"/>
       <c r="D135" s="2"/>
       <c r="I135"/>
       <c r="J135"/>
       <c r="M135"/>
     </row>
-    <row r="136" spans="2:27" s="8" customFormat="1">
+    <row r="136" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C136"/>
       <c r="D136" s="2"/>
       <c r="I136"/>
       <c r="J136"/>
       <c r="M136"/>
     </row>
-    <row r="137" spans="2:27" s="8" customFormat="1">
+    <row r="137" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C137"/>
       <c r="D137" s="2"/>
       <c r="I137"/>
       <c r="J137"/>
       <c r="M137"/>
     </row>
-    <row r="138" spans="2:27" s="8" customFormat="1">
+    <row r="138" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C138"/>
       <c r="D138" s="2"/>
       <c r="I138"/>
       <c r="J138"/>
       <c r="M138"/>
     </row>
-    <row r="139" spans="2:27" s="8" customFormat="1">
+    <row r="139" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C139"/>
       <c r="D139" s="2"/>
       <c r="I139"/>
       <c r="J139"/>
       <c r="M139"/>
     </row>
-    <row r="140" spans="2:27" s="8" customFormat="1">
+    <row r="140" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C140"/>
       <c r="D140" s="2"/>
       <c r="I140"/>
       <c r="J140"/>
       <c r="M140"/>
     </row>
-    <row r="141" spans="2:27" s="8" customFormat="1">
+    <row r="141" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C141"/>
       <c r="D141" s="2"/>
       <c r="I141"/>
       <c r="J141"/>
       <c r="M141"/>
     </row>
-    <row r="142" spans="2:27" s="8" customFormat="1">
+    <row r="142" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C142"/>
       <c r="D142" s="2"/>
       <c r="I142"/>
       <c r="J142"/>
       <c r="M142"/>
     </row>
-    <row r="143" spans="2:27" s="8" customFormat="1">
+    <row r="143" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C143"/>
       <c r="D143" s="2"/>
       <c r="I143"/>
       <c r="J143"/>
       <c r="M143"/>
     </row>
-    <row r="144" spans="2:27" s="8" customFormat="1">
+    <row r="144" spans="2:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C144"/>
       <c r="D144" s="2"/>
       <c r="I144"/>
       <c r="J144"/>
       <c r="M144"/>
     </row>
-    <row r="145" spans="3:13" s="8" customFormat="1">
+    <row r="145" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C145"/>
       <c r="D145" s="2"/>
       <c r="I145"/>
       <c r="J145"/>
       <c r="M145"/>
     </row>
-    <row r="146" spans="3:13" s="8" customFormat="1">
+    <row r="146" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C146"/>
       <c r="D146" s="2"/>
       <c r="I146"/>
       <c r="J146"/>
       <c r="M146"/>
     </row>
-    <row r="147" spans="3:13" s="8" customFormat="1">
+    <row r="147" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C147"/>
       <c r="D147" s="2"/>
       <c r="I147"/>
       <c r="J147"/>
       <c r="M147"/>
     </row>
-    <row r="148" spans="3:13" s="8" customFormat="1">
+    <row r="148" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C148"/>
       <c r="D148" s="2"/>
       <c r="I148"/>
       <c r="J148"/>
       <c r="M148"/>
     </row>
-    <row r="149" spans="3:13" s="8" customFormat="1">
+    <row r="149" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C149"/>
       <c r="D149" s="2"/>
       <c r="I149"/>
       <c r="J149"/>
       <c r="M149"/>
     </row>
-    <row r="150" spans="3:13" s="8" customFormat="1">
+    <row r="150" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C150"/>
       <c r="D150" s="2"/>
       <c r="I150"/>
       <c r="J150"/>
       <c r="M150"/>
     </row>
-    <row r="151" spans="3:13" s="8" customFormat="1">
+    <row r="151" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C151"/>
       <c r="D151" s="2"/>
       <c r="I151"/>
       <c r="J151"/>
       <c r="M151"/>
     </row>
-    <row r="152" spans="3:13" s="8" customFormat="1">
+    <row r="152" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C152"/>
       <c r="D152" s="2"/>
       <c r="I152"/>
       <c r="J152"/>
       <c r="M152"/>
     </row>
-    <row r="153" spans="3:13" s="8" customFormat="1">
+    <row r="153" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C153"/>
       <c r="D153" s="2"/>
       <c r="I153"/>
       <c r="J153"/>
       <c r="M153"/>
     </row>
-    <row r="154" spans="3:13" s="8" customFormat="1">
+    <row r="154" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C154"/>
       <c r="D154" s="2"/>
       <c r="I154"/>
       <c r="J154"/>
       <c r="M154"/>
     </row>
-    <row r="155" spans="3:13" s="8" customFormat="1">
+    <row r="155" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C155"/>
       <c r="D155" s="2"/>
       <c r="I155"/>
       <c r="J155"/>
       <c r="M155"/>
     </row>
-    <row r="156" spans="3:13" s="8" customFormat="1">
+    <row r="156" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C156"/>
       <c r="D156" s="2"/>
       <c r="I156"/>
       <c r="J156"/>
       <c r="M156"/>
     </row>
-    <row r="157" spans="3:13" s="8" customFormat="1">
+    <row r="157" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C157"/>
       <c r="D157" s="2"/>
       <c r="I157"/>
       <c r="J157"/>
       <c r="M157"/>
     </row>
-    <row r="158" spans="3:13" s="8" customFormat="1">
+    <row r="158" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C158"/>
       <c r="D158" s="2"/>
       <c r="I158"/>
       <c r="J158"/>
       <c r="M158"/>
     </row>
-    <row r="159" spans="3:13" s="8" customFormat="1">
+    <row r="159" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C159"/>
       <c r="D159" s="2"/>
       <c r="I159"/>
       <c r="J159"/>
       <c r="M159"/>
     </row>
-    <row r="160" spans="3:13" s="8" customFormat="1">
+    <row r="160" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C160"/>
       <c r="D160" s="2"/>
       <c r="I160"/>
       <c r="J160"/>
       <c r="M160"/>
     </row>
-    <row r="161" spans="3:13" s="8" customFormat="1">
+    <row r="161" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C161"/>
       <c r="D161" s="2"/>
       <c r="I161"/>
       <c r="J161"/>
       <c r="M161"/>
     </row>
-    <row r="162" spans="3:13" s="8" customFormat="1">
+    <row r="162" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C162"/>
       <c r="D162" s="2"/>
       <c r="I162"/>
       <c r="J162"/>
       <c r="M162"/>
     </row>
-    <row r="163" spans="3:13" s="8" customFormat="1">
+    <row r="163" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C163"/>
       <c r="D163" s="2"/>
       <c r="I163"/>
       <c r="J163"/>
       <c r="M163"/>
     </row>
-    <row r="164" spans="3:13" s="8" customFormat="1">
+    <row r="164" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C164"/>
       <c r="D164" s="2"/>
       <c r="I164"/>
       <c r="J164"/>
       <c r="M164"/>
     </row>
-    <row r="165" spans="3:13" s="8" customFormat="1">
+    <row r="165" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C165"/>
       <c r="D165" s="2"/>
       <c r="I165"/>
       <c r="J165"/>
       <c r="M165"/>
     </row>
-    <row r="166" spans="3:13" s="8" customFormat="1">
+    <row r="166" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C166"/>
       <c r="D166" s="2"/>
       <c r="I166"/>
       <c r="J166"/>
       <c r="M166"/>
     </row>
-    <row r="167" spans="3:13" s="8" customFormat="1">
+    <row r="167" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C167"/>
       <c r="D167" s="2"/>
       <c r="I167"/>
       <c r="J167"/>
       <c r="M167"/>
     </row>
-    <row r="168" spans="3:13" s="8" customFormat="1">
+    <row r="168" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C168"/>
       <c r="D168" s="2"/>
       <c r="I168"/>
       <c r="J168"/>
       <c r="M168"/>
     </row>
-    <row r="169" spans="3:13" s="8" customFormat="1">
+    <row r="169" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C169"/>
       <c r="D169" s="2"/>
       <c r="I169"/>
       <c r="J169"/>
       <c r="M169"/>
     </row>
-    <row r="170" spans="3:13" s="8" customFormat="1">
+    <row r="170" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C170"/>
       <c r="D170" s="2"/>
       <c r="I170"/>
       <c r="J170"/>
       <c r="M170"/>
     </row>
-    <row r="171" spans="3:13" s="8" customFormat="1">
+    <row r="171" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C171"/>
       <c r="D171" s="2"/>
       <c r="I171"/>
       <c r="J171"/>
       <c r="M171"/>
     </row>
-    <row r="172" spans="3:13" s="8" customFormat="1">
+    <row r="172" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C172"/>
       <c r="D172" s="2"/>
       <c r="I172"/>
       <c r="J172"/>
       <c r="M172"/>
     </row>
-    <row r="173" spans="3:13" s="8" customFormat="1">
+    <row r="173" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C173"/>
       <c r="D173" s="2"/>
       <c r="I173"/>
       <c r="J173"/>
       <c r="M173"/>
     </row>
-    <row r="174" spans="3:13" s="8" customFormat="1">
+    <row r="174" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C174"/>
       <c r="D174" s="2"/>
       <c r="E174"/>
@@ -8220,7 +8254,7 @@
       <c r="J174"/>
       <c r="M174"/>
     </row>
-    <row r="175" spans="3:13" s="8" customFormat="1">
+    <row r="175" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C175"/>
       <c r="D175" s="2"/>
       <c r="E175"/>
@@ -8231,7 +8265,7 @@
       <c r="J175"/>
       <c r="M175"/>
     </row>
-    <row r="176" spans="3:13" s="8" customFormat="1">
+    <row r="176" spans="3:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C176"/>
       <c r="D176" s="2"/>
       <c r="E176"/>
@@ -8242,7 +8276,7 @@
       <c r="J176"/>
       <c r="M176"/>
     </row>
-    <row r="177" spans="3:14" s="8" customFormat="1">
+    <row r="177" spans="3:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C177"/>
       <c r="D177" s="2"/>
       <c r="E177"/>
@@ -8253,7 +8287,7 @@
       <c r="J177"/>
       <c r="M177"/>
     </row>
-    <row r="178" spans="3:14" s="8" customFormat="1">
+    <row r="178" spans="3:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C178"/>
       <c r="D178" s="2"/>
       <c r="E178"/>
@@ -8264,7 +8298,7 @@
       <c r="J178"/>
       <c r="M178"/>
     </row>
-    <row r="179" spans="3:14" s="8" customFormat="1">
+    <row r="179" spans="3:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C179"/>
       <c r="D179" s="2"/>
       <c r="E179"/>
@@ -8275,11 +8309,11 @@
       <c r="J179"/>
       <c r="M179"/>
     </row>
-    <row r="180" spans="3:14">
+    <row r="180" spans="3:14" x14ac:dyDescent="0.25">
       <c r="K180" s="8"/>
       <c r="N180" s="8"/>
     </row>
-    <row r="181" spans="3:14">
+    <row r="181" spans="3:14" x14ac:dyDescent="0.25">
       <c r="K181" s="8"/>
       <c r="N181" s="8"/>
     </row>
@@ -8347,7 +8381,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54D47CA-E570-4941-BC8B-CDF2CCCB0000}">
   <dimension ref="B1:S119"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.09765625" customWidth="1"/>
     <col min="2" max="2" width="1.3984375" customWidth="1"/>
@@ -8362,7 +8396,7 @@
     <col min="13" max="13" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="42" customHeight="1">
+    <row r="1" spans="2:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="143"/>
       <c r="C1" s="15"/>
       <c r="D1" s="209" t="s">
@@ -8375,7 +8409,7 @@
       <c r="I1" s="15"/>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="2:10" ht="6" customHeight="1" thickBot="1">
+    <row r="2" spans="2:10" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="136"/>
       <c r="C2" s="137"/>
       <c r="D2" s="137"/>
@@ -8386,7 +8420,7 @@
       <c r="I2" s="137"/>
       <c r="J2" s="132"/>
     </row>
-    <row r="3" spans="2:10" ht="6" customHeight="1">
+    <row r="3" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="82"/>
       <c r="C3" s="92"/>
       <c r="D3" s="93"/>
@@ -8397,7 +8431,7 @@
       <c r="I3" s="94"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="2:10" ht="28.2" customHeight="1">
+    <row r="4" spans="2:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="82"/>
       <c r="C4" s="81"/>
       <c r="D4" s="210" t="s">
@@ -8410,13 +8444,13 @@
       <c r="I4" s="70"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="82"/>
       <c r="C5" s="81"/>
       <c r="I5" s="70"/>
       <c r="J5" s="11"/>
     </row>
-    <row r="6" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1">
+    <row r="6" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="138"/>
       <c r="C6" s="95"/>
       <c r="D6" s="96" t="s">
@@ -8434,7 +8468,7 @@
       <c r="I6" s="97"/>
       <c r="J6" s="139"/>
     </row>
-    <row r="7" spans="2:10" s="19" customFormat="1" ht="22.2" customHeight="1">
+    <row r="7" spans="2:10" s="19" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="138"/>
       <c r="C7" s="95"/>
       <c r="D7" s="145" t="s">
@@ -8446,7 +8480,7 @@
       <c r="I7" s="97"/>
       <c r="J7" s="139"/>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="82"/>
       <c r="C8" s="81"/>
       <c r="D8" t="s">
@@ -8463,7 +8497,7 @@
       <c r="I8" s="70"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="82"/>
       <c r="C9" s="81"/>
       <c r="D9" t="s">
@@ -8480,14 +8514,14 @@
       <c r="I9" s="70"/>
       <c r="J9" s="11"/>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="82"/>
       <c r="C10" s="81"/>
       <c r="G10" s="8"/>
       <c r="I10" s="70"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="82"/>
       <c r="C11" s="81"/>
       <c r="D11" s="1" t="s">
@@ -8497,7 +8531,7 @@
       <c r="I11" s="70"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="82"/>
       <c r="C12" s="81"/>
       <c r="D12" t="s">
@@ -8514,7 +8548,7 @@
       <c r="I12" s="70"/>
       <c r="J12" s="11"/>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="82"/>
       <c r="C13" s="81"/>
       <c r="D13" t="s">
@@ -8531,21 +8565,21 @@
       <c r="I13" s="70"/>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="82"/>
       <c r="C14" s="81"/>
       <c r="G14" s="8"/>
       <c r="I14" s="70"/>
       <c r="J14" s="11"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="82"/>
       <c r="C15" s="81"/>
       <c r="G15" s="8"/>
       <c r="I15" s="70"/>
       <c r="J15" s="11"/>
     </row>
-    <row r="16" spans="2:10" s="19" customFormat="1" ht="28.2" customHeight="1">
+    <row r="16" spans="2:10" s="19" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="138"/>
       <c r="C16" s="95"/>
       <c r="D16" s="98" t="s">
@@ -8560,20 +8594,20 @@
       <c r="I16" s="97"/>
       <c r="J16" s="139"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="82"/>
       <c r="C17" s="81"/>
       <c r="G17" s="101"/>
       <c r="I17" s="70"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="82"/>
       <c r="C18" s="81"/>
       <c r="I18" s="70"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1">
+    <row r="19" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="138"/>
       <c r="C19" s="95"/>
       <c r="D19" s="96" t="s">
@@ -8594,7 +8628,7 @@
       <c r="I19" s="102"/>
       <c r="J19" s="139"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="82"/>
       <c r="C20" s="81"/>
       <c r="D20" s="103"/>
@@ -8604,7 +8638,7 @@
       <c r="I20" s="70"/>
       <c r="J20" s="11"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="82"/>
       <c r="C21" s="81"/>
       <c r="D21" s="121" t="s">
@@ -8620,7 +8654,7 @@
       <c r="I21" s="71"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="82"/>
       <c r="C22" s="81"/>
       <c r="D22" s="23" t="s">
@@ -8630,7 +8664,7 @@
       <c r="I22" s="70"/>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="82"/>
       <c r="C23" s="81"/>
       <c r="D23" s="23" t="s">
@@ -8640,7 +8674,7 @@
       <c r="I23" s="70"/>
       <c r="J23" s="11"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="82"/>
       <c r="C24" s="81"/>
       <c r="D24" s="23" t="s">
@@ -8650,14 +8684,14 @@
       <c r="I24" s="70"/>
       <c r="J24" s="11"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="82"/>
       <c r="C25" s="81"/>
       <c r="G25" s="8"/>
       <c r="I25" s="70"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="82"/>
       <c r="C26" s="81"/>
       <c r="D26" s="76" t="s">
@@ -8673,7 +8707,7 @@
       <c r="I26" s="70"/>
       <c r="J26" s="11"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="82"/>
       <c r="C27" s="81"/>
       <c r="D27" s="19" t="s">
@@ -8683,14 +8717,14 @@
       <c r="I27" s="70"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="82"/>
       <c r="C28" s="81"/>
       <c r="G28" s="8"/>
       <c r="I28" s="70"/>
       <c r="J28" s="11"/>
     </row>
-    <row r="29" spans="2:10" s="19" customFormat="1" ht="28.2" customHeight="1">
+    <row r="29" spans="2:10" s="19" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="138"/>
       <c r="C29" s="95"/>
       <c r="D29" s="98" t="s">
@@ -8706,7 +8740,7 @@
       <c r="I29" s="97"/>
       <c r="J29" s="139"/>
     </row>
-    <row r="30" spans="2:10" s="19" customFormat="1" ht="15.6" customHeight="1">
+    <row r="30" spans="2:10" s="19" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="138"/>
       <c r="C30" s="95"/>
       <c r="D30" s="76"/>
@@ -8714,7 +8748,7 @@
       <c r="I30" s="97"/>
       <c r="J30" s="139"/>
     </row>
-    <row r="31" spans="2:10" s="19" customFormat="1" ht="28.2" customHeight="1">
+    <row r="31" spans="2:10" s="19" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="138"/>
       <c r="C31" s="95"/>
       <c r="D31" s="98" t="s">
@@ -8730,14 +8764,14 @@
       <c r="I31" s="108"/>
       <c r="J31" s="139"/>
     </row>
-    <row r="32" spans="2:10" s="91" customFormat="1">
+    <row r="32" spans="2:10" s="91" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="140"/>
       <c r="C32" s="109"/>
       <c r="G32" s="110"/>
       <c r="I32" s="111"/>
       <c r="J32" s="141"/>
     </row>
-    <row r="33" spans="2:10" s="91" customFormat="1">
+    <row r="33" spans="2:10" s="91" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="140"/>
       <c r="C33" s="109"/>
       <c r="D33" s="91" t="s">
@@ -8751,14 +8785,14 @@
       <c r="I33" s="111"/>
       <c r="J33" s="141"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="82"/>
       <c r="C34" s="81"/>
       <c r="G34" s="8"/>
       <c r="I34" s="70"/>
       <c r="J34" s="11"/>
     </row>
-    <row r="35" spans="2:10" ht="31.2" customHeight="1">
+    <row r="35" spans="2:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="82"/>
       <c r="C35" s="81"/>
       <c r="D35" s="112" t="s">
@@ -8777,14 +8811,14 @@
       <c r="I35" s="70"/>
       <c r="J35" s="11"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="82"/>
       <c r="C36" s="81"/>
       <c r="G36" s="8"/>
       <c r="I36" s="70"/>
       <c r="J36" s="11"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="82"/>
       <c r="C37" s="81"/>
       <c r="D37" t="s">
@@ -8805,7 +8839,7 @@
       <c r="I37" s="70"/>
       <c r="J37" s="11"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="82"/>
       <c r="C38" s="81"/>
       <c r="D38" t="s">
@@ -8826,7 +8860,7 @@
       <c r="I38" s="70"/>
       <c r="J38" s="11"/>
     </row>
-    <row r="39" spans="2:10" ht="8.4" customHeight="1" thickBot="1">
+    <row r="39" spans="2:10" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="82"/>
       <c r="C39" s="117"/>
       <c r="D39" s="118"/>
@@ -8837,12 +8871,12 @@
       <c r="I39" s="120"/>
       <c r="J39" s="11"/>
     </row>
-    <row r="40" spans="2:10" ht="14.4" thickBot="1">
+    <row r="40" spans="2:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="82"/>
       <c r="E40" s="115"/>
       <c r="J40" s="11"/>
     </row>
-    <row r="41" spans="2:10" ht="6.6" customHeight="1">
+    <row r="41" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="82"/>
       <c r="C41" s="92"/>
       <c r="D41" s="93"/>
@@ -8853,7 +8887,7 @@
       <c r="I41" s="94"/>
       <c r="J41" s="11"/>
     </row>
-    <row r="42" spans="2:10" ht="28.2">
+    <row r="42" spans="2:10" ht="28.8" x14ac:dyDescent="0.25">
       <c r="B42" s="82"/>
       <c r="C42" s="81"/>
       <c r="D42" s="210" t="s">
@@ -8866,13 +8900,13 @@
       <c r="I42" s="70"/>
       <c r="J42" s="11"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="82"/>
       <c r="C43" s="81"/>
       <c r="I43" s="70"/>
       <c r="J43" s="11"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="82"/>
       <c r="C44" s="125"/>
       <c r="D44" s="1"/>
@@ -8880,7 +8914,7 @@
       <c r="I44" s="70"/>
       <c r="J44" s="11"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="82"/>
       <c r="C45" s="126" t="s">
         <v>164</v>
@@ -8895,7 +8929,7 @@
       <c r="I45" s="70"/>
       <c r="J45" s="11"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="82"/>
       <c r="C46" s="126"/>
       <c r="D46" s="127" t="s">
@@ -8913,7 +8947,7 @@
       <c r="I46" s="70"/>
       <c r="J46" s="11"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="82"/>
       <c r="C47" s="81"/>
       <c r="D47" t="s">
@@ -8931,7 +8965,7 @@
       <c r="I47" s="70"/>
       <c r="J47" s="11"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="82"/>
       <c r="C48" s="81"/>
       <c r="D48" s="23" t="s">
@@ -8949,7 +8983,7 @@
       <c r="I48" s="70"/>
       <c r="J48" s="11"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="82"/>
       <c r="C49" s="81"/>
       <c r="D49" s="23" t="s">
@@ -8967,7 +9001,7 @@
       <c r="I49" s="70"/>
       <c r="J49" s="11"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="82"/>
       <c r="C50" s="81"/>
       <c r="D50" s="23" t="s">
@@ -8984,14 +9018,14 @@
       <c r="I50" s="70"/>
       <c r="J50" s="11"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="82"/>
       <c r="C51" s="81"/>
       <c r="D51" s="23"/>
       <c r="I51" s="70"/>
       <c r="J51" s="11"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="82"/>
       <c r="C52" s="81"/>
       <c r="D52" s="127" t="s">
@@ -9005,7 +9039,7 @@
       <c r="I52" s="70"/>
       <c r="J52" s="11"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="82"/>
       <c r="C53" s="81"/>
       <c r="D53" s="23" t="s">
@@ -9018,7 +9052,7 @@
       <c r="I53" s="70"/>
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="82"/>
       <c r="C54" s="81"/>
       <c r="D54" s="23" t="s">
@@ -9031,7 +9065,7 @@
       <c r="I54" s="70"/>
       <c r="J54" s="11"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="82"/>
       <c r="C55" s="81"/>
       <c r="D55" s="23" t="s">
@@ -9044,14 +9078,14 @@
       <c r="I55" s="70"/>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="82"/>
       <c r="C56" s="81"/>
       <c r="D56" s="23"/>
       <c r="I56" s="70"/>
       <c r="J56" s="11"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="82"/>
       <c r="C57" s="81"/>
       <c r="D57" s="127" t="s">
@@ -9065,7 +9099,7 @@
       <c r="I57" s="70"/>
       <c r="J57" s="11"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="82"/>
       <c r="C58" s="81"/>
       <c r="D58" s="23" t="s">
@@ -9078,7 +9112,7 @@
       <c r="I58" s="70"/>
       <c r="J58" s="11"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="82"/>
       <c r="C59" s="81"/>
       <c r="D59" s="23" t="s">
@@ -9091,7 +9125,7 @@
       <c r="I59" s="70"/>
       <c r="J59" s="11"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="82"/>
       <c r="C60" s="81"/>
       <c r="D60" s="23" t="s">
@@ -9104,14 +9138,14 @@
       <c r="I60" s="70"/>
       <c r="J60" s="11"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="82"/>
       <c r="C61" s="81"/>
       <c r="D61" s="23"/>
       <c r="I61" s="70"/>
       <c r="J61" s="11"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="82"/>
       <c r="C62" s="81"/>
       <c r="D62" s="127" t="s">
@@ -9126,7 +9160,7 @@
       <c r="I62" s="70"/>
       <c r="J62" s="11"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="82"/>
       <c r="C63" s="81"/>
       <c r="D63" t="s">
@@ -9140,7 +9174,7 @@
       <c r="I63" s="70"/>
       <c r="J63" s="11"/>
     </row>
-    <row r="64" spans="2:10">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="82"/>
       <c r="C64" s="81"/>
       <c r="D64" s="23" t="s">
@@ -9153,7 +9187,7 @@
       <c r="I64" s="70"/>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="82"/>
       <c r="C65" s="81"/>
       <c r="D65" s="23" t="s">
@@ -9167,7 +9201,7 @@
       <c r="I65" s="70"/>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="82"/>
       <c r="C66" s="81"/>
       <c r="D66" s="23" t="s">
@@ -9180,14 +9214,14 @@
       <c r="I66" s="70"/>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="82"/>
       <c r="C67" s="81"/>
       <c r="D67" s="23"/>
       <c r="I67" s="70"/>
       <c r="J67" s="11"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="82"/>
       <c r="C68" s="81"/>
       <c r="D68" s="148" t="s">
@@ -9196,7 +9230,7 @@
       <c r="I68" s="70"/>
       <c r="J68" s="11"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="82"/>
       <c r="C69" s="81"/>
       <c r="D69" s="23" t="s">
@@ -9210,7 +9244,7 @@
       <c r="I69" s="70"/>
       <c r="J69" s="11"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="82"/>
       <c r="C70" s="81"/>
       <c r="D70" s="23" t="s">
@@ -9224,7 +9258,7 @@
       <c r="I70" s="70"/>
       <c r="J70" s="11"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="82"/>
       <c r="C71" s="81"/>
       <c r="D71" s="23" t="s">
@@ -9238,14 +9272,14 @@
       <c r="I71" s="70"/>
       <c r="J71" s="11"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="82"/>
       <c r="C72" s="81"/>
       <c r="D72" s="23"/>
       <c r="I72" s="70"/>
       <c r="J72" s="11"/>
     </row>
-    <row r="73" spans="2:10" ht="28.8" customHeight="1">
+    <row r="73" spans="2:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="82"/>
       <c r="C73" s="81"/>
       <c r="D73" s="123" t="s">
@@ -9261,7 +9295,7 @@
       <c r="I73" s="70"/>
       <c r="J73" s="11"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="82"/>
       <c r="C74" s="81"/>
       <c r="D74" s="23"/>
@@ -9269,14 +9303,14 @@
       <c r="I74" s="70"/>
       <c r="J74" s="11"/>
     </row>
-    <row r="75" spans="2:10">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="82"/>
       <c r="C75" s="81"/>
       <c r="D75" s="23"/>
       <c r="I75" s="70"/>
       <c r="J75" s="11"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="82"/>
       <c r="C76" s="81"/>
       <c r="D76" s="21" t="s">
@@ -9290,7 +9324,7 @@
       <c r="I76" s="70"/>
       <c r="J76" s="11"/>
     </row>
-    <row r="77" spans="2:10" ht="6.6" customHeight="1" thickBot="1">
+    <row r="77" spans="2:10" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="82"/>
       <c r="C77" s="117"/>
       <c r="D77" s="131"/>
@@ -9301,12 +9335,12 @@
       <c r="I77" s="120"/>
       <c r="J77" s="11"/>
     </row>
-    <row r="78" spans="2:10" ht="14.4" thickBot="1">
+    <row r="78" spans="2:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="82"/>
       <c r="D78" s="23"/>
       <c r="J78" s="11"/>
     </row>
-    <row r="79" spans="2:10" ht="5.4" customHeight="1">
+    <row r="79" spans="2:10" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="82"/>
       <c r="C79" s="92"/>
       <c r="D79" s="133"/>
@@ -9317,7 +9351,7 @@
       <c r="I79" s="94"/>
       <c r="J79" s="11"/>
     </row>
-    <row r="80" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1">
+    <row r="80" spans="2:10" s="19" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="138"/>
       <c r="C80" s="95"/>
       <c r="D80" s="210" t="s">
@@ -9330,7 +9364,7 @@
       <c r="I80" s="97"/>
       <c r="J80" s="139"/>
     </row>
-    <row r="81" spans="2:10">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="82"/>
       <c r="C81" s="81"/>
       <c r="D81" s="17" t="s">
@@ -9343,7 +9377,7 @@
       <c r="I81" s="70"/>
       <c r="J81" s="11"/>
     </row>
-    <row r="82" spans="2:10">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="82"/>
       <c r="C82" s="81"/>
       <c r="D82" s="10" t="s">
@@ -9357,7 +9391,7 @@
       <c r="I82" s="70"/>
       <c r="J82" s="11"/>
     </row>
-    <row r="83" spans="2:10">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="82"/>
       <c r="C83" s="81"/>
       <c r="D83" s="10" t="s">
@@ -9370,7 +9404,7 @@
       <c r="I83" s="70"/>
       <c r="J83" s="11"/>
     </row>
-    <row r="84" spans="2:10">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="82"/>
       <c r="C84" s="81"/>
       <c r="D84" s="10" t="s">
@@ -9383,7 +9417,7 @@
       <c r="I84" s="70"/>
       <c r="J84" s="11"/>
     </row>
-    <row r="85" spans="2:10">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="82"/>
       <c r="C85" s="81"/>
       <c r="D85" s="10"/>
@@ -9392,7 +9426,7 @@
       <c r="I85" s="70"/>
       <c r="J85" s="11"/>
     </row>
-    <row r="86" spans="2:10">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="82"/>
       <c r="C86" s="81"/>
       <c r="D86" s="12"/>
@@ -9406,14 +9440,14 @@
       <c r="I86" s="70"/>
       <c r="J86" s="11"/>
     </row>
-    <row r="87" spans="2:10">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="82"/>
       <c r="C87" s="81"/>
       <c r="D87" s="1"/>
       <c r="I87" s="70"/>
       <c r="J87" s="11"/>
     </row>
-    <row r="88" spans="2:10" ht="28.2" customHeight="1">
+    <row r="88" spans="2:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="82"/>
       <c r="C88" s="81"/>
       <c r="D88" s="123" t="s">
@@ -9429,7 +9463,7 @@
       <c r="I88" s="70"/>
       <c r="J88" s="11"/>
     </row>
-    <row r="89" spans="2:10" ht="6.6" customHeight="1" thickBot="1">
+    <row r="89" spans="2:10" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="82"/>
       <c r="C89" s="117"/>
       <c r="D89" s="118"/>
@@ -9440,11 +9474,11 @@
       <c r="I89" s="120"/>
       <c r="J89" s="11"/>
     </row>
-    <row r="90" spans="2:10" ht="14.4" thickBot="1">
+    <row r="90" spans="2:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="82"/>
       <c r="J90" s="11"/>
     </row>
-    <row r="91" spans="2:10" ht="6.6" customHeight="1">
+    <row r="91" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="82"/>
       <c r="C91" s="92"/>
       <c r="D91" s="93"/>
@@ -9455,7 +9489,7 @@
       <c r="I91" s="94"/>
       <c r="J91" s="11"/>
     </row>
-    <row r="92" spans="2:10">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="82"/>
       <c r="C92" s="81"/>
       <c r="D92" s="211" t="s">
@@ -9468,13 +9502,13 @@
       <c r="I92" s="70"/>
       <c r="J92" s="11"/>
     </row>
-    <row r="93" spans="2:10">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="82"/>
       <c r="C93" s="81"/>
       <c r="I93" s="70"/>
       <c r="J93" s="11"/>
     </row>
-    <row r="94" spans="2:10">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="82"/>
       <c r="C94" s="81"/>
       <c r="D94" s="21" t="s">
@@ -9490,7 +9524,7 @@
       <c r="I94" s="70"/>
       <c r="J94" s="11"/>
     </row>
-    <row r="95" spans="2:10">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="82"/>
       <c r="C95" s="81"/>
       <c r="D95" s="21"/>
@@ -9501,7 +9535,7 @@
       <c r="I95" s="70"/>
       <c r="J95" s="11"/>
     </row>
-    <row r="96" spans="2:10">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="82"/>
       <c r="C96" s="81"/>
       <c r="D96" s="21" t="s">
@@ -9517,7 +9551,7 @@
       <c r="I96" s="70"/>
       <c r="J96" s="11"/>
     </row>
-    <row r="97" spans="2:10" ht="5.4" customHeight="1" thickBot="1">
+    <row r="97" spans="2:10" ht="5.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="82"/>
       <c r="C97" s="117"/>
       <c r="D97" s="118"/>
@@ -9528,7 +9562,7 @@
       <c r="I97" s="120"/>
       <c r="J97" s="11"/>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="142"/>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -9539,7 +9573,7 @@
       <c r="I98" s="13"/>
       <c r="J98" s="14"/>
     </row>
-    <row r="114" spans="4:19">
+    <row r="114" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E114" t="s">
         <v>170</v>
       </c>
@@ -9574,7 +9608,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="115" spans="4:19">
+    <row r="115" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D115" t="s">
         <v>231</v>
       </c>
@@ -9587,7 +9621,7 @@
       <c r="P115" s="200"/>
       <c r="Q115" s="200"/>
     </row>
-    <row r="116" spans="4:19">
+    <row r="116" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D116" t="s">
         <v>120</v>
       </c>
@@ -9630,7 +9664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="4:19">
+    <row r="117" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
@@ -9640,7 +9674,7 @@
       <c r="P117" s="200"/>
       <c r="Q117" s="200"/>
     </row>
-    <row r="118" spans="4:19">
+    <row r="118" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D118" t="s">
         <v>241</v>
       </c>
@@ -9661,7 +9695,7 @@
       <c r="P118" s="200"/>
       <c r="Q118" s="200"/>
     </row>
-    <row r="119" spans="4:19">
+    <row r="119" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
@@ -9691,7 +9725,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D963DE-649A-406C-ABA1-C01122495537}">
   <dimension ref="B2:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
@@ -9700,56 +9734,56 @@
     <col min="8" max="8" width="11.19921875" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>231</v>
       </c>
       <c r="G12" s="56">
         <f>SUM(E14:E17)</f>
-        <v>22541920</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7">
+        <v>22555960</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -9758,12 +9792,12 @@
         <v>12720000</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>249</v>
       </c>
@@ -9772,34 +9806,34 @@
         <v>2830000</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="8">
         <f>+'INGRESOS-EGRESOS'!G123</f>
-        <v>6991920</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
+        <v>7005960</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G19" s="56">
         <f>SUM(D21:D24)</f>
-        <v>89170000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
+        <v>89350000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="8">
         <f>+ESCUELITAS!F10-ESCUELITAS!H10</f>
-        <v>87970000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
+        <v>88150000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>223</v>
       </c>
@@ -9808,26 +9842,26 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>176</v>
       </c>
       <c r="G26" s="56">
         <f>SUM(D27:D32)</f>
-        <v>74370920</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
+        <v>74384960</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>25</v>
       </c>
@@ -9836,7 +9870,7 @@
         <v>50599000</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>245</v>
       </c>
@@ -9844,7 +9878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>246</v>
       </c>
@@ -9853,7 +9887,7 @@
         <v>6780000</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>247</v>
       </c>
@@ -9862,7 +9896,7 @@
         <v>5800000</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>248</v>
       </c>
@@ -9871,13 +9905,13 @@
         <v>4200000</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>45</v>
       </c>
       <c r="D32" s="8">
         <f>+'INGRESOS-EGRESOS'!E123</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
     </row>
   </sheetData>
@@ -9888,7 +9922,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C290A6-41D9-4B5E-A9F2-65750A3120D0}">
   <dimension ref="C1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.8984375" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -9900,24 +9934,24 @@
     <col min="17" max="17" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17">
+    <row r="1" spans="3:17" x14ac:dyDescent="0.25">
       <c r="N1" s="212">
         <f>+N2-O2</f>
         <v>14790000</v>
       </c>
       <c r="O1" s="213"/>
     </row>
-    <row r="2" spans="3:17">
+    <row r="2" spans="3:17" x14ac:dyDescent="0.25">
       <c r="N2" s="4">
         <f>+N4+N9+N15+N29+N35</f>
-        <v>165408920</v>
+        <v>165602960</v>
       </c>
       <c r="O2" s="4">
         <f>+O4+O9+O15+O29+O35</f>
-        <v>150618920</v>
-      </c>
-    </row>
-    <row r="3" spans="3:17">
+        <v>150812960</v>
+      </c>
+    </row>
+    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F3" s="157" t="s">
         <v>221</v>
       </c>
@@ -9934,7 +9968,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="3:17">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C4" s="21" t="s">
         <v>218</v>
       </c>
@@ -9947,7 +9981,7 @@
       <c r="M4" s="187"/>
       <c r="N4" s="193">
         <f>SUM(N5:N7)</f>
-        <v>52300000</v>
+        <v>60300000</v>
       </c>
       <c r="O4" s="194">
         <f>SUM(O5:O7)</f>
@@ -9955,16 +9989,16 @@
       </c>
       <c r="P4" s="183">
         <f>+N4-O4</f>
-        <v>20941000</v>
-      </c>
-    </row>
-    <row r="5" spans="3:17">
+        <v>28941000</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="159">
         <f>+DIVIDENDOS!E4</f>
-        <v>17341000</v>
+        <v>25341000</v>
       </c>
       <c r="G5" s="160"/>
       <c r="L5" t="s">
@@ -9972,7 +10006,7 @@
       </c>
       <c r="N5" s="159">
         <f>+DIVIDENDOS!C4</f>
-        <v>29190000</v>
+        <v>37190000</v>
       </c>
       <c r="O5" s="160">
         <f>+DIVIDENDOS!D4</f>
@@ -9980,10 +10014,10 @@
       </c>
       <c r="Q5" s="4">
         <f>+N5-O5</f>
-        <v>17341000</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17">
+        <v>25341000</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>17</v>
       </c>
@@ -10004,7 +10038,7 @@
         <v>19510000</v>
       </c>
     </row>
-    <row r="7" spans="3:17">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>45</v>
       </c>
@@ -10025,13 +10059,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:17">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F8" s="159"/>
       <c r="G8" s="160"/>
       <c r="N8" s="159"/>
       <c r="O8" s="160"/>
     </row>
-    <row r="9" spans="3:17">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="21" t="s">
         <v>219</v>
       </c>
@@ -10044,7 +10078,7 @@
       <c r="M9" s="187"/>
       <c r="N9" s="193">
         <f>SUM(N10:N12)</f>
-        <v>32868000</v>
+        <v>25048000</v>
       </c>
       <c r="O9" s="194">
         <f>SUM(O10:O12)</f>
@@ -10052,16 +10086,16 @@
       </c>
       <c r="P9" s="197">
         <f>+N9-O9</f>
-        <v>32868000</v>
-      </c>
-    </row>
-    <row r="10" spans="3:17">
+        <v>25048000</v>
+      </c>
+    </row>
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="159">
         <f>+ESCUELITAS!P10</f>
-        <v>29990000</v>
+        <v>22170000</v>
       </c>
       <c r="G10" s="160"/>
       <c r="L10" t="s">
@@ -10069,11 +10103,11 @@
       </c>
       <c r="N10" s="159">
         <f>+ESCUELITAS!P10</f>
-        <v>29990000</v>
+        <v>22170000</v>
       </c>
       <c r="O10" s="160"/>
     </row>
-    <row r="11" spans="3:17">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>223</v>
       </c>
@@ -10092,7 +10126,7 @@
       <c r="O11" s="160"/>
       <c r="Q11" s="198"/>
     </row>
-    <row r="12" spans="3:17">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>19</v>
       </c>
@@ -10110,19 +10144,19 @@
       </c>
       <c r="O12" s="160"/>
     </row>
-    <row r="13" spans="3:17">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F13" s="159"/>
       <c r="G13" s="160"/>
       <c r="N13" s="159"/>
       <c r="O13" s="160"/>
     </row>
-    <row r="14" spans="3:17">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F14" s="159"/>
       <c r="G14" s="160"/>
       <c r="N14" s="159"/>
       <c r="O14" s="160"/>
     </row>
-    <row r="15" spans="3:17">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="21" t="s">
         <v>220</v>
       </c>
@@ -10139,14 +10173,14 @@
       </c>
       <c r="O15" s="192">
         <f>SUM(O16:O23)</f>
-        <v>26741920</v>
+        <v>26755960</v>
       </c>
       <c r="P15" s="186">
         <f>+O15-N15</f>
-        <v>26741920</v>
-      </c>
-    </row>
-    <row r="16" spans="3:17">
+        <v>26755960</v>
+      </c>
+    </row>
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="21"/>
       <c r="D16" t="s">
         <v>25</v>
@@ -10166,7 +10200,7 @@
         <v>8690000</v>
       </c>
     </row>
-    <row r="17" spans="3:17">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="21"/>
       <c r="D17" t="s">
         <v>8</v>
@@ -10186,7 +10220,7 @@
         <v>4030000</v>
       </c>
     </row>
-    <row r="18" spans="3:17">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="21"/>
       <c r="D18" t="s">
         <v>151</v>
@@ -10206,7 +10240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:17">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>152</v>
       </c>
@@ -10224,14 +10258,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:17">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="159"/>
       <c r="G20" s="160">
         <f>+'INGRESOS-EGRESOS'!G123</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="L20" t="s">
         <v>45</v>
@@ -10239,10 +10273,10 @@
       <c r="N20" s="159"/>
       <c r="O20" s="160">
         <f>+'INGRESOS-EGRESOS'!G123</f>
-        <v>6991920</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17">
+        <v>7005960</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F21" s="159"/>
       <c r="G21" s="160"/>
       <c r="L21" t="s">
@@ -10255,7 +10289,7 @@
       </c>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="3:17">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F22" s="159"/>
       <c r="G22" s="160"/>
       <c r="L22" t="s">
@@ -10266,7 +10300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:17">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F23" s="159"/>
       <c r="G23" s="160"/>
       <c r="L23" t="s">
@@ -10278,14 +10312,14 @@
         <v>2830000</v>
       </c>
     </row>
-    <row r="24" spans="3:17">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F24" s="159"/>
       <c r="G24" s="160"/>
       <c r="N24" s="159"/>
       <c r="O24" s="160"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="3:17">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F25" s="159"/>
       <c r="G25" s="160"/>
       <c r="K25" t="s">
@@ -10294,7 +10328,7 @@
       <c r="N25" s="180"/>
       <c r="O25" s="160"/>
     </row>
-    <row r="26" spans="3:17">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="21" t="s">
         <v>154</v>
       </c>
@@ -10303,20 +10337,20 @@
       <c r="N26" s="159"/>
       <c r="O26" s="160"/>
     </row>
-    <row r="27" spans="3:17">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="159"/>
       <c r="G27" s="160">
         <f>+ESCUELITAS!O10</f>
-        <v>100550000</v>
+        <v>100730000</v>
       </c>
       <c r="N27" s="159"/>
       <c r="O27" s="160"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="3:17">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
         <v>223</v>
       </c>
@@ -10329,7 +10363,7 @@
       <c r="O28" s="160"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="3:17">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
         <v>19</v>
       </c>
@@ -10349,15 +10383,15 @@
       </c>
       <c r="O29" s="192">
         <f>SUM(O30:O33)</f>
-        <v>92518000</v>
+        <v>92698000</v>
       </c>
       <c r="P29" s="196">
         <f>+O29-N29</f>
-        <v>90848000</v>
+        <v>91028000</v>
       </c>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="3:17">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
         <v>99</v>
       </c>
@@ -10375,10 +10409,10 @@
       </c>
       <c r="O30" s="160">
         <f>+ESCUELITAS!F10</f>
-        <v>89640000</v>
-      </c>
-    </row>
-    <row r="31" spans="3:17">
+        <v>89820000</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="F31" s="159"/>
       <c r="G31" s="160"/>
       <c r="L31" t="s">
@@ -10390,7 +10424,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="32" spans="3:17">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="21" t="s">
         <v>176</v>
       </c>
@@ -10405,7 +10439,7 @@
         <v>1678000</v>
       </c>
     </row>
-    <row r="33" spans="3:16">
+    <row r="33" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C33" s="21"/>
       <c r="D33" t="s">
         <v>25</v>
@@ -10423,7 +10457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:16">
+    <row r="34" spans="3:16" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>8</v>
       </c>
@@ -10435,7 +10469,7 @@
       <c r="N34" s="159"/>
       <c r="O34" s="160"/>
     </row>
-    <row r="35" spans="3:16">
+    <row r="35" spans="3:16" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
         <v>151</v>
       </c>
@@ -10451,7 +10485,7 @@
       <c r="M35" s="187"/>
       <c r="N35" s="193">
         <f>SUM(N36:N43)</f>
-        <v>78570920</v>
+        <v>78584960</v>
       </c>
       <c r="O35" s="194">
         <f>SUM(O36:O43)</f>
@@ -10459,10 +10493,10 @@
       </c>
       <c r="P35" s="197">
         <f>+N35-O35</f>
-        <v>78570920</v>
-      </c>
-    </row>
-    <row r="36" spans="3:16">
+        <v>78584960</v>
+      </c>
+    </row>
+    <row r="36" spans="3:16" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
         <v>152</v>
       </c>
@@ -10481,13 +10515,13 @@
       </c>
       <c r="O36" s="160"/>
     </row>
-    <row r="37" spans="3:16">
+    <row r="37" spans="3:16" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
         <v>45</v>
       </c>
       <c r="F37" s="159">
         <f>+'INGRESOS-EGRESOS'!E123</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="G37" s="160"/>
       <c r="L37" t="s">
@@ -10499,7 +10533,7 @@
       </c>
       <c r="O37" s="160"/>
     </row>
-    <row r="38" spans="3:16">
+    <row r="38" spans="3:16" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
         <v>229</v>
       </c>
@@ -10514,7 +10548,7 @@
       </c>
       <c r="O38" s="160"/>
     </row>
-    <row r="39" spans="3:16">
+    <row r="39" spans="3:16" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
         <v>230</v>
       </c>
@@ -10529,7 +10563,7 @@
       </c>
       <c r="O39" s="160"/>
     </row>
-    <row r="40" spans="3:16">
+    <row r="40" spans="3:16" x14ac:dyDescent="0.25">
       <c r="F40" s="159"/>
       <c r="G40" s="160"/>
       <c r="L40" t="s">
@@ -10537,18 +10571,18 @@
       </c>
       <c r="N40" s="159">
         <f>+'INGRESOS-EGRESOS'!E123</f>
-        <v>6991920</v>
+        <v>7005960</v>
       </c>
       <c r="O40" s="160"/>
     </row>
-    <row r="41" spans="3:16">
+    <row r="41" spans="3:16" x14ac:dyDescent="0.25">
       <c r="F41" s="180">
         <f>SUM(F5:F38)</f>
-        <v>123671920</v>
+        <v>123865960</v>
       </c>
       <c r="G41" s="181">
         <f>SUM(G5:G38)</f>
-        <v>123139920</v>
+        <v>123333960</v>
       </c>
       <c r="L41" t="s">
         <v>233</v>
@@ -10559,7 +10593,7 @@
       </c>
       <c r="O41" s="160"/>
     </row>
-    <row r="42" spans="3:16">
+    <row r="42" spans="3:16" x14ac:dyDescent="0.25">
       <c r="F42" s="157"/>
       <c r="G42" s="158"/>
       <c r="L42" t="s">
@@ -10570,7 +10604,7 @@
       </c>
       <c r="O42" s="160"/>
     </row>
-    <row r="43" spans="3:16">
+    <row r="43" spans="3:16" x14ac:dyDescent="0.25">
       <c r="F43" s="214">
         <f>+F41-G41</f>
         <v>532000</v>
@@ -10585,21 +10619,21 @@
       </c>
       <c r="O43" s="160"/>
     </row>
-    <row r="44" spans="3:16">
+    <row r="44" spans="3:16" x14ac:dyDescent="0.25">
       <c r="F44" s="157"/>
       <c r="G44" s="158"/>
       <c r="N44" s="157"/>
       <c r="O44" s="158"/>
     </row>
-    <row r="45" spans="3:16">
+    <row r="45" spans="3:16" x14ac:dyDescent="0.25">
       <c r="N45" s="157"/>
       <c r="O45" s="158"/>
     </row>
-    <row r="46" spans="3:16">
+    <row r="46" spans="3:16" x14ac:dyDescent="0.25">
       <c r="N46" s="157"/>
       <c r="O46" s="158"/>
     </row>
-    <row r="47" spans="3:16">
+    <row r="47" spans="3:16" x14ac:dyDescent="0.25">
       <c r="N47" s="157"/>
       <c r="O47" s="158"/>
     </row>
@@ -10616,7 +10650,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DB0F2D-0E2C-4DF9-89D5-0BCB7B84FFF5}">
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.3984375" customWidth="1"/>
     <col min="2" max="2" width="11.19921875" style="2"/>
@@ -10625,12 +10659,12 @@
     <col min="7" max="7" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H2" t="s">
         <v>238</v>
       </c>
@@ -10641,7 +10675,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H3" s="8">
         <f>+E8</f>
         <v>4200000</v>
@@ -10654,7 +10688,7 @@
         <v>4200000</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
@@ -10662,7 +10696,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D5" s="3" t="s">
         <v>104</v>
       </c>
@@ -10671,7 +10705,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="76" customFormat="1" ht="34.799999999999997" customHeight="1">
+    <row r="8" spans="1:17" s="76" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="22" t="s">
         <v>166</v>
       </c>
@@ -10693,7 +10727,7 @@
         <v>4150000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="19" customFormat="1" ht="55.8" thickBot="1">
+    <row r="9" spans="1:17" s="19" customFormat="1" ht="42" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="77" t="s">
         <v>169</v>
       </c>
@@ -10740,7 +10774,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>1</v>
       </c>
@@ -10763,7 +10797,7 @@
       <c r="K10" s="11"/>
       <c r="M10" s="70"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>2</v>
       </c>
@@ -10790,7 +10824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>3</v>
       </c>
@@ -10805,7 +10839,7 @@
       <c r="K12" s="11"/>
       <c r="M12" s="70"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>4</v>
       </c>
@@ -10820,7 +10854,7 @@
       <c r="K13" s="11"/>
       <c r="M13" s="70"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>16</v>
       </c>
@@ -10850,7 +10884,7 @@
       <c r="K14" s="11"/>
       <c r="M14" s="70"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>199</v>
       </c>
@@ -10880,7 +10914,7 @@
       <c r="K15" s="11"/>
       <c r="M15" s="70"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>200</v>
       </c>
@@ -10910,7 +10944,7 @@
       <c r="K16" s="11"/>
       <c r="M16" s="70"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>201</v>
       </c>
@@ -10940,7 +10974,7 @@
       <c r="K17" s="11"/>
       <c r="M17" s="70"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>202</v>
       </c>
@@ -10970,7 +11004,7 @@
       <c r="K18" s="11"/>
       <c r="M18" s="70"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>203</v>
       </c>
@@ -11000,7 +11034,7 @@
       <c r="K19" s="11"/>
       <c r="M19" s="70"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>204</v>
       </c>
@@ -11030,7 +11064,7 @@
       <c r="K20" s="11"/>
       <c r="M20" s="70"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>205</v>
       </c>
@@ -11060,7 +11094,7 @@
       <c r="K21" s="11"/>
       <c r="M21" s="70"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>206</v>
       </c>
@@ -11090,7 +11124,7 @@
       <c r="K22" s="11"/>
       <c r="M22" s="70"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>207</v>
       </c>
@@ -11125,7 +11159,7 @@
       <c r="K23" s="11"/>
       <c r="M23" s="70"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="174" t="s">
         <v>225</v>
       </c>
@@ -11155,7 +11189,7 @@
       <c r="K24" s="11"/>
       <c r="M24" s="70"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="175" t="s">
         <v>226</v>
       </c>
@@ -11185,7 +11219,7 @@
       <c r="K25" s="11"/>
       <c r="M25" s="70"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <v>17</v>
       </c>
@@ -11197,7 +11231,7 @@
       <c r="K26" s="11"/>
       <c r="M26" s="70"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <v>18</v>
       </c>
@@ -11209,7 +11243,7 @@
       <c r="K27" s="11"/>
       <c r="M27" s="70"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>19</v>
       </c>
@@ -11221,7 +11255,7 @@
       <c r="K28" s="11"/>
       <c r="M28" s="70"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <v>20</v>
       </c>
@@ -11233,7 +11267,7 @@
       <c r="K29" s="11"/>
       <c r="M29" s="70"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>223</v>
       </c>
@@ -11246,7 +11280,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14.4" thickBot="1">
+    <row r="35" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E35" s="2" t="s">
         <v>170</v>
       </c>
@@ -11275,7 +11309,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -11293,7 +11327,7 @@
       <c r="J36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -11312,7 +11346,7 @@
       <c r="J37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -11346,12 +11380,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CB58C0-D726-4391-A0D0-C6DECD556176}">
   <dimension ref="B4:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="26" t="s">
         <v>131</v>
       </c>
@@ -11359,7 +11393,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>129</v>
       </c>
@@ -11367,7 +11401,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="6" spans="2:3">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>209</v>
       </c>
@@ -11375,7 +11409,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="7" spans="2:3">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>130</v>
       </c>
@@ -11383,7 +11417,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="8" spans="2:3">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>132</v>
       </c>
@@ -11391,7 +11425,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="9" spans="2:3">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>133</v>
       </c>
@@ -11399,7 +11433,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="10" spans="2:3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>134</v>
       </c>
@@ -11407,7 +11441,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="2:3">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>29</v>
       </c>
@@ -11415,7 +11449,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="12" spans="2:3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>30</v>
       </c>
@@ -11423,7 +11457,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="13" spans="2:3">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>31</v>
       </c>
@@ -11431,31 +11465,31 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="14" spans="2:3">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C14" s="8"/>
     </row>
-    <row r="15" spans="2:3">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C15" s="8"/>
     </row>
-    <row r="16" spans="2:3">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C16" s="8"/>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="3:3">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="3:3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="3:3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="3:3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" s="8"/>
     </row>
   </sheetData>
@@ -11466,7 +11500,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C83A04-846A-4BEC-8AE5-BE027106A818}">
   <dimension ref="A2:O28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="11.59765625" style="3" customWidth="1"/>
     <col min="5" max="5" width="19.59765625" bestFit="1" customWidth="1"/>
@@ -11474,14 +11508,14 @@
     <col min="12" max="12" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="213" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="213"/>
       <c r="C2" s="213"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -11507,7 +11541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
         <v>1</v>
       </c>
@@ -11522,7 +11556,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>2</v>
       </c>
@@ -11543,7 +11577,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -11570,7 +11604,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E8" s="5" t="s">
         <v>89</v>
       </c>
@@ -11585,7 +11619,7 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E10" s="9" t="s">
         <v>88</v>
       </c>
@@ -11600,7 +11634,7 @@
         <v>425000</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E12" s="5" t="s">
         <v>90</v>
       </c>
@@ -11611,12 +11645,12 @@
         <v>705000</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
         <v>1</v>
       </c>
@@ -11624,7 +11658,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
         <v>7</v>
       </c>
@@ -11632,7 +11666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>87</v>
       </c>
@@ -11640,11 +11674,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E20" s="1" t="s">
         <v>12</v>
       </c>
@@ -11658,7 +11692,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="E21" s="7" t="s">
         <v>16</v>
@@ -11667,7 +11701,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22"/>
       <c r="E22" s="7" t="s">
         <v>17</v>
@@ -11676,19 +11710,19 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23"/>
       <c r="E23" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="E24" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E25" s="7" t="s">
         <v>20</v>
       </c>
@@ -11696,12 +11730,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E26" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E27" s="7" t="s">
         <v>22</v>
       </c>
@@ -11709,7 +11743,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E28" s="7" t="s">
         <v>23</v>
       </c>
@@ -11726,7 +11760,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC2962C-F16B-4237-991E-24E7BA0F0516}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
